--- a/docs/requerimiento-5/I.S.F.D. y T. N° 93_ Inscripción a Carreras 2021 (solo 1).xlsx
+++ b/docs/requerimiento-5/I.S.F.D. y T. N° 93_ Inscripción a Carreras 2021 (solo 1).xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">Marca temporal</t>
   </si>
@@ -88,34 +88,28 @@
     <t xml:space="preserve">Contacto emergencia</t>
   </si>
   <si>
-    <t>acunaagustina74@gmail.com</t>
+    <t>alejofsarmiento@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Administración con Orientación en Marketing</t>
+    <t xml:space="preserve">Analista Programador</t>
   </si>
   <si>
-    <t>Acuña</t>
+    <t>Sarmiento</t>
   </si>
   <si>
-    <t xml:space="preserve">Agustina Alejandra</t>
+    <t xml:space="preserve">Alejo Fernando</t>
   </si>
   <si>
-    <t>Femenino</t>
+    <t>Masculino</t>
   </si>
   <si>
-    <t>Guernica</t>
+    <t xml:space="preserve">San Vicente</t>
   </si>
   <si>
-    <t>Soltera</t>
+    <t>Soltero</t>
   </si>
   <si>
-    <t xml:space="preserve">Campbell 834</t>
-  </si>
-  <si>
-    <t>Glew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Almirante Brown</t>
+    <t xml:space="preserve">Bolivar 9983</t>
   </si>
   <si>
     <t xml:space="preserve">Buenos Aires</t>
@@ -137,10 +131,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.000000"/>
       <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10.000000"/>
+      <color theme="10"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -170,12 +170,14 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="3" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -774,59 +776,59 @@
       <c r="A2" s="2">
         <v>44228.926002650463</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="F2" s="1">
-        <v>43785394</v>
-      </c>
-      <c r="G2" s="1" t="s">
+        <v>42887583</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="3">
-        <v>37201</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="H2" s="5">
+        <v>36924</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="4" t="s">
         <v>28</v>
       </c>
       <c r="K2" s="1">
         <v>1161305919</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="1">
+        <v>1865</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="Q2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O2" s="1">
-        <v>1856</v>
-      </c>
-      <c r="P2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="T2" t="s">
         <v>33</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="T2" t="s">
-        <v>35</v>
       </c>
       <c r="U2">
         <v>321312</v>
@@ -848,7 +850,7 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="3"/>
+      <c r="H3" s="5"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -857,7 +859,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
-      <c r="Q3" s="4"/>
+      <c r="Q3" s="6"/>
       <c r="R3" s="1"/>
     </row>
     <row r="4" ht="12.75">
@@ -870,16 +872,16 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="3"/>
+      <c r="H4" s="5"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="5"/>
+      <c r="K4" s="7"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
-      <c r="Q4" s="4"/>
+      <c r="Q4" s="6"/>
       <c r="R4" s="1"/>
     </row>
     <row r="5" ht="12.75">
@@ -892,7 +894,7 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="3"/>
+      <c r="H5" s="5"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -901,7 +903,7 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
-      <c r="Q5" s="4"/>
+      <c r="Q5" s="6"/>
       <c r="R5" s="1"/>
     </row>
     <row r="6" ht="12.75">
@@ -912,9 +914,9 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="6"/>
+      <c r="F6" s="8"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="3"/>
+      <c r="H6" s="5"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -923,7 +925,7 @@
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="4"/>
+      <c r="Q6" s="6"/>
       <c r="R6" s="1"/>
     </row>
     <row r="7" ht="12.75">
@@ -936,7 +938,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="3"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -945,7 +947,7 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
-      <c r="Q7" s="4"/>
+      <c r="Q7" s="6"/>
       <c r="R7" s="1"/>
     </row>
     <row r="8" ht="12.75">
@@ -958,7 +960,7 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="3"/>
+      <c r="H8" s="5"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -967,7 +969,7 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
-      <c r="Q8" s="4"/>
+      <c r="Q8" s="6"/>
       <c r="R8" s="1"/>
     </row>
     <row r="9" ht="12.75">
@@ -980,16 +982,16 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="3"/>
+      <c r="H9" s="5"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-      <c r="K9" s="5"/>
+      <c r="K9" s="7"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
-      <c r="Q9" s="4"/>
+      <c r="Q9" s="6"/>
       <c r="R9" s="1"/>
     </row>
     <row r="10" ht="12.75">
@@ -1002,7 +1004,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="5"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -1011,7 +1013,7 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
-      <c r="Q10" s="4"/>
+      <c r="Q10" s="6"/>
       <c r="R10" s="1"/>
     </row>
     <row r="11" ht="12.75">
@@ -1024,7 +1026,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="3"/>
+      <c r="H11" s="5"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -1033,7 +1035,7 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
-      <c r="Q11" s="4"/>
+      <c r="Q11" s="6"/>
       <c r="R11" s="1"/>
     </row>
     <row r="12" ht="12.75">
@@ -1046,7 +1048,7 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="3"/>
+      <c r="H12" s="5"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1055,7 +1057,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
-      <c r="Q12" s="4"/>
+      <c r="Q12" s="6"/>
       <c r="R12" s="1"/>
     </row>
     <row r="13" ht="12.75">
@@ -1068,7 +1070,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="3"/>
+      <c r="H13" s="5"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1077,7 +1079,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="Q13" s="4"/>
+      <c r="Q13" s="6"/>
       <c r="R13" s="1"/>
     </row>
     <row r="14" ht="12.75">
@@ -1090,16 +1092,16 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-      <c r="H14" s="3"/>
+      <c r="H14" s="5"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
-      <c r="K14" s="5"/>
+      <c r="K14" s="7"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-      <c r="Q14" s="4"/>
+      <c r="Q14" s="6"/>
       <c r="R14" s="1"/>
     </row>
     <row r="15" ht="12.75">
@@ -1112,7 +1114,7 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-      <c r="H15" s="3"/>
+      <c r="H15" s="5"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1121,7 +1123,7 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="Q15" s="4"/>
+      <c r="Q15" s="6"/>
       <c r="R15" s="1"/>
     </row>
     <row r="16" ht="12.75">
@@ -1134,7 +1136,7 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-      <c r="H16" s="3"/>
+      <c r="H16" s="5"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1143,7 +1145,7 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-      <c r="Q16" s="4"/>
+      <c r="Q16" s="6"/>
       <c r="R16" s="1"/>
     </row>
     <row r="17" ht="12.75">
@@ -1156,7 +1158,7 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
-      <c r="H17" s="3"/>
+      <c r="H17" s="5"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1165,7 +1167,7 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
-      <c r="Q17" s="4"/>
+      <c r="Q17" s="6"/>
       <c r="R17" s="1"/>
     </row>
     <row r="18" ht="12.75">
@@ -1178,7 +1180,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
-      <c r="H18" s="3"/>
+      <c r="H18" s="5"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -1187,7 +1189,7 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
-      <c r="Q18" s="4"/>
+      <c r="Q18" s="6"/>
       <c r="R18" s="1"/>
     </row>
     <row r="19" ht="12.75">
@@ -1200,7 +1202,7 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
-      <c r="H19" s="3"/>
+      <c r="H19" s="5"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -1209,7 +1211,7 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
-      <c r="Q19" s="4"/>
+      <c r="Q19" s="6"/>
       <c r="R19" s="1"/>
     </row>
     <row r="20" ht="12.75">
@@ -1222,16 +1224,16 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
-      <c r="H20" s="3"/>
+      <c r="H20" s="5"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
-      <c r="K20" s="5"/>
+      <c r="K20" s="7"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
-      <c r="Q20" s="4"/>
+      <c r="Q20" s="6"/>
       <c r="R20" s="1"/>
     </row>
     <row r="21" ht="12.75">
@@ -1244,7 +1246,7 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
-      <c r="H21" s="3"/>
+      <c r="H21" s="5"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -1253,7 +1255,7 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
-      <c r="Q21" s="4"/>
+      <c r="Q21" s="6"/>
       <c r="R21" s="1"/>
     </row>
     <row r="22" ht="12.75">
@@ -1266,7 +1268,7 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
-      <c r="H22" s="3"/>
+      <c r="H22" s="5"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -1275,7 +1277,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
-      <c r="Q22" s="4"/>
+      <c r="Q22" s="6"/>
       <c r="R22" s="1"/>
     </row>
     <row r="23" ht="12.75">
@@ -1288,7 +1290,7 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="H23" s="3"/>
+      <c r="H23" s="5"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -1297,7 +1299,7 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="4"/>
+      <c r="Q23" s="6"/>
       <c r="R23" s="1"/>
     </row>
     <row r="24" ht="12.75">
@@ -1310,7 +1312,7 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
-      <c r="H24" s="3"/>
+      <c r="H24" s="5"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -1319,7 +1321,7 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
-      <c r="Q24" s="4"/>
+      <c r="Q24" s="6"/>
       <c r="R24" s="1"/>
     </row>
     <row r="25" ht="12.75">
@@ -1332,7 +1334,7 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="3"/>
+      <c r="H25" s="5"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -1341,7 +1343,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
-      <c r="Q25" s="4"/>
+      <c r="Q25" s="6"/>
       <c r="R25" s="1"/>
     </row>
     <row r="26" ht="12.75">
@@ -1354,7 +1356,7 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
-      <c r="H26" s="3"/>
+      <c r="H26" s="5"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -1363,7 +1365,7 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
-      <c r="Q26" s="4"/>
+      <c r="Q26" s="6"/>
       <c r="R26" s="1"/>
     </row>
     <row r="27" ht="12.75">
@@ -1376,7 +1378,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="3"/>
+      <c r="H27" s="5"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -1385,7 +1387,7 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
-      <c r="Q27" s="4"/>
+      <c r="Q27" s="6"/>
       <c r="R27" s="1"/>
     </row>
     <row r="28" ht="12.75">
@@ -1398,7 +1400,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="3"/>
+      <c r="H28" s="5"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -1407,7 +1409,7 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
-      <c r="Q28" s="4"/>
+      <c r="Q28" s="6"/>
       <c r="R28" s="1"/>
     </row>
     <row r="29" ht="12.75">
@@ -1420,7 +1422,7 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="3"/>
+      <c r="H29" s="5"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -1429,7 +1431,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
-      <c r="Q29" s="4"/>
+      <c r="Q29" s="6"/>
       <c r="R29" s="1"/>
     </row>
     <row r="30" ht="12.75">
@@ -1442,7 +1444,7 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="3"/>
+      <c r="H30" s="5"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -1451,7 +1453,7 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
-      <c r="Q30" s="4"/>
+      <c r="Q30" s="6"/>
       <c r="R30" s="1"/>
     </row>
     <row r="31" ht="12.75">
@@ -1464,7 +1466,7 @@
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="H31" s="3"/>
+      <c r="H31" s="5"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -1473,7 +1475,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
-      <c r="Q31" s="4"/>
+      <c r="Q31" s="6"/>
       <c r="R31" s="1"/>
     </row>
     <row r="32" ht="12.75">
@@ -1486,7 +1488,7 @@
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
-      <c r="H32" s="3"/>
+      <c r="H32" s="5"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -1495,7 +1497,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
-      <c r="Q32" s="4"/>
+      <c r="Q32" s="6"/>
       <c r="R32" s="1"/>
     </row>
     <row r="33" ht="12.75">
@@ -1508,7 +1510,7 @@
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
-      <c r="H33" s="3"/>
+      <c r="H33" s="5"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -1517,7 +1519,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-      <c r="Q33" s="4"/>
+      <c r="Q33" s="6"/>
       <c r="R33" s="1"/>
     </row>
     <row r="34" ht="12.75">
@@ -1530,7 +1532,7 @@
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="H34" s="3"/>
+      <c r="H34" s="5"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -1539,7 +1541,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-      <c r="Q34" s="4"/>
+      <c r="Q34" s="6"/>
       <c r="R34" s="1"/>
     </row>
     <row r="35" ht="12.75">
@@ -1552,7 +1554,7 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-      <c r="H35" s="3"/>
+      <c r="H35" s="5"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -1561,7 +1563,7 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
-      <c r="Q35" s="4"/>
+      <c r="Q35" s="6"/>
       <c r="R35" s="1"/>
     </row>
     <row r="36" ht="12.75">
@@ -1574,7 +1576,7 @@
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-      <c r="H36" s="3"/>
+      <c r="H36" s="5"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -1583,7 +1585,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
-      <c r="Q36" s="4"/>
+      <c r="Q36" s="6"/>
       <c r="R36" s="1"/>
     </row>
     <row r="37" ht="12.75">
@@ -1596,7 +1598,7 @@
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
-      <c r="H37" s="3"/>
+      <c r="H37" s="5"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -1605,7 +1607,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
-      <c r="Q37" s="4"/>
+      <c r="Q37" s="6"/>
       <c r="R37" s="1"/>
     </row>
     <row r="38" ht="12.75">
@@ -1618,7 +1620,7 @@
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
-      <c r="H38" s="3"/>
+      <c r="H38" s="5"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -1627,7 +1629,7 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
-      <c r="Q38" s="4"/>
+      <c r="Q38" s="6"/>
       <c r="R38" s="1"/>
     </row>
     <row r="39" ht="12.75">
@@ -1640,7 +1642,7 @@
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
-      <c r="H39" s="3"/>
+      <c r="H39" s="5"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -1649,7 +1651,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
-      <c r="Q39" s="4"/>
+      <c r="Q39" s="6"/>
       <c r="R39" s="1"/>
     </row>
     <row r="40" ht="12.75">
@@ -1662,7 +1664,7 @@
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
-      <c r="H40" s="3"/>
+      <c r="H40" s="5"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -1671,7 +1673,7 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
-      <c r="Q40" s="4"/>
+      <c r="Q40" s="6"/>
       <c r="R40" s="1"/>
     </row>
     <row r="41" ht="12.75">
@@ -1684,7 +1686,7 @@
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
-      <c r="H41" s="3"/>
+      <c r="H41" s="5"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -1693,7 +1695,7 @@
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
-      <c r="Q41" s="4"/>
+      <c r="Q41" s="6"/>
       <c r="R41" s="1"/>
     </row>
     <row r="42" ht="12.75">
@@ -1706,7 +1708,7 @@
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
-      <c r="H42" s="3"/>
+      <c r="H42" s="5"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -1715,7 +1717,7 @@
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
-      <c r="Q42" s="4"/>
+      <c r="Q42" s="6"/>
       <c r="R42" s="1"/>
     </row>
     <row r="43" ht="12.75">
@@ -1728,16 +1730,16 @@
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
-      <c r="H43" s="3"/>
+      <c r="H43" s="5"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
-      <c r="K43" s="5"/>
+      <c r="K43" s="7"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
-      <c r="Q43" s="4"/>
+      <c r="Q43" s="6"/>
       <c r="R43" s="1"/>
     </row>
     <row r="44" ht="12.75">
@@ -1750,16 +1752,16 @@
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
-      <c r="H44" s="3"/>
+      <c r="H44" s="5"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
-      <c r="K44" s="5"/>
+      <c r="K44" s="7"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
-      <c r="Q44" s="4"/>
+      <c r="Q44" s="6"/>
       <c r="R44" s="1"/>
     </row>
     <row r="45" ht="12.75">
@@ -1772,16 +1774,16 @@
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
-      <c r="H45" s="3"/>
+      <c r="H45" s="5"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
-      <c r="K45" s="5"/>
+      <c r="K45" s="7"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
-      <c r="Q45" s="4"/>
+      <c r="Q45" s="6"/>
       <c r="R45" s="1"/>
     </row>
     <row r="46" ht="12.75">
@@ -1794,16 +1796,16 @@
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
-      <c r="H46" s="3"/>
+      <c r="H46" s="5"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
-      <c r="K46" s="5"/>
+      <c r="K46" s="7"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
-      <c r="Q46" s="4"/>
+      <c r="Q46" s="6"/>
       <c r="R46" s="1"/>
     </row>
     <row r="47" ht="12.75">
@@ -1816,7 +1818,7 @@
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
-      <c r="H47" s="3"/>
+      <c r="H47" s="5"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -1825,7 +1827,7 @@
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
-      <c r="Q47" s="4"/>
+      <c r="Q47" s="6"/>
       <c r="R47" s="1"/>
     </row>
     <row r="48" ht="12.75">
@@ -1838,7 +1840,7 @@
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
-      <c r="H48" s="3"/>
+      <c r="H48" s="5"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -1847,7 +1849,7 @@
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
-      <c r="Q48" s="4"/>
+      <c r="Q48" s="6"/>
       <c r="R48" s="1"/>
     </row>
     <row r="49" ht="12.75">
@@ -1860,7 +1862,7 @@
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="3"/>
+      <c r="H49" s="5"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -1869,7 +1871,7 @@
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
-      <c r="Q49" s="4"/>
+      <c r="Q49" s="6"/>
       <c r="R49" s="1"/>
     </row>
     <row r="50" ht="12.75">
@@ -1882,16 +1884,16 @@
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
-      <c r="H50" s="3"/>
+      <c r="H50" s="5"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
-      <c r="L50" s="5"/>
+      <c r="L50" s="7"/>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
-      <c r="Q50" s="4"/>
+      <c r="Q50" s="6"/>
       <c r="R50" s="1"/>
     </row>
     <row r="51" ht="12.75">
@@ -1904,7 +1906,7 @@
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
-      <c r="H51" s="3"/>
+      <c r="H51" s="5"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -1913,7 +1915,7 @@
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
-      <c r="Q51" s="4"/>
+      <c r="Q51" s="6"/>
       <c r="R51" s="1"/>
     </row>
     <row r="52" ht="12.75">
@@ -1926,16 +1928,16 @@
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
-      <c r="H52" s="3"/>
+      <c r="H52" s="5"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
-      <c r="L52" s="5"/>
+      <c r="L52" s="7"/>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
       <c r="P52" s="1"/>
-      <c r="Q52" s="4"/>
+      <c r="Q52" s="6"/>
       <c r="R52" s="1"/>
     </row>
     <row r="53" ht="12.75">
@@ -1948,16 +1950,16 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
-      <c r="H53" s="3"/>
+      <c r="H53" s="5"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
-      <c r="K53" s="5"/>
+      <c r="K53" s="7"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
       <c r="P53" s="1"/>
-      <c r="Q53" s="4"/>
+      <c r="Q53" s="6"/>
       <c r="R53" s="1"/>
     </row>
     <row r="54" ht="12.75">
@@ -1970,7 +1972,7 @@
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
-      <c r="H54" s="3"/>
+      <c r="H54" s="5"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
@@ -1979,7 +1981,7 @@
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
       <c r="P54" s="1"/>
-      <c r="Q54" s="4"/>
+      <c r="Q54" s="6"/>
       <c r="R54" s="1"/>
     </row>
     <row r="55" ht="12.75">
@@ -1992,7 +1994,7 @@
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
-      <c r="H55" s="3"/>
+      <c r="H55" s="5"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
@@ -2001,7 +2003,7 @@
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
       <c r="P55" s="1"/>
-      <c r="Q55" s="4"/>
+      <c r="Q55" s="6"/>
       <c r="R55" s="1"/>
     </row>
     <row r="56" ht="12.75">
@@ -2014,7 +2016,7 @@
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
-      <c r="H56" s="3"/>
+      <c r="H56" s="5"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
@@ -2023,7 +2025,7 @@
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
       <c r="P56" s="1"/>
-      <c r="Q56" s="4"/>
+      <c r="Q56" s="6"/>
       <c r="R56" s="1"/>
     </row>
     <row r="57" ht="12.75">
@@ -2036,7 +2038,7 @@
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
-      <c r="H57" s="3"/>
+      <c r="H57" s="5"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
@@ -2045,7 +2047,7 @@
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
       <c r="P57" s="1"/>
-      <c r="Q57" s="4"/>
+      <c r="Q57" s="6"/>
       <c r="R57" s="1"/>
     </row>
     <row r="58" ht="12.75">
@@ -2058,7 +2060,7 @@
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
-      <c r="H58" s="3"/>
+      <c r="H58" s="5"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
@@ -2067,7 +2069,7 @@
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
       <c r="P58" s="1"/>
-      <c r="Q58" s="4"/>
+      <c r="Q58" s="6"/>
       <c r="R58" s="1"/>
     </row>
     <row r="59" ht="12.75">
@@ -2080,7 +2082,7 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
-      <c r="H59" s="3"/>
+      <c r="H59" s="5"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
@@ -2089,7 +2091,7 @@
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
       <c r="P59" s="1"/>
-      <c r="Q59" s="4"/>
+      <c r="Q59" s="6"/>
       <c r="R59" s="1"/>
     </row>
     <row r="60" ht="12.75">
@@ -2102,7 +2104,7 @@
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
-      <c r="H60" s="3"/>
+      <c r="H60" s="5"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
@@ -2111,7 +2113,7 @@
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
       <c r="P60" s="1"/>
-      <c r="Q60" s="4"/>
+      <c r="Q60" s="6"/>
       <c r="R60" s="1"/>
     </row>
     <row r="61" ht="12.75">
@@ -2124,7 +2126,7 @@
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
-      <c r="H61" s="3"/>
+      <c r="H61" s="5"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
@@ -2133,7 +2135,7 @@
       <c r="N61" s="1"/>
       <c r="O61" s="1"/>
       <c r="P61" s="1"/>
-      <c r="Q61" s="4"/>
+      <c r="Q61" s="6"/>
       <c r="R61" s="1"/>
     </row>
     <row r="62" ht="12.75">
@@ -2146,7 +2148,7 @@
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
-      <c r="H62" s="3"/>
+      <c r="H62" s="5"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
@@ -2155,7 +2157,7 @@
       <c r="N62" s="1"/>
       <c r="O62" s="1"/>
       <c r="P62" s="1"/>
-      <c r="Q62" s="4"/>
+      <c r="Q62" s="6"/>
       <c r="R62" s="1"/>
     </row>
     <row r="63" ht="12.75">
@@ -2168,7 +2170,7 @@
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
-      <c r="H63" s="3"/>
+      <c r="H63" s="5"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -2177,7 +2179,7 @@
       <c r="N63" s="1"/>
       <c r="O63" s="1"/>
       <c r="P63" s="1"/>
-      <c r="Q63" s="4"/>
+      <c r="Q63" s="6"/>
       <c r="R63" s="1"/>
     </row>
     <row r="64" ht="12.75">
@@ -2190,7 +2192,7 @@
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
-      <c r="H64" s="3"/>
+      <c r="H64" s="5"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
@@ -2199,7 +2201,7 @@
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
       <c r="P64" s="1"/>
-      <c r="Q64" s="4"/>
+      <c r="Q64" s="6"/>
       <c r="R64" s="1"/>
     </row>
     <row r="65" ht="12.75">
@@ -2212,7 +2214,7 @@
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
-      <c r="H65" s="3"/>
+      <c r="H65" s="5"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
@@ -2221,7 +2223,7 @@
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
       <c r="P65" s="1"/>
-      <c r="Q65" s="4"/>
+      <c r="Q65" s="6"/>
       <c r="R65" s="1"/>
     </row>
     <row r="66" ht="12.75">
@@ -2234,7 +2236,7 @@
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
-      <c r="H66" s="3"/>
+      <c r="H66" s="5"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
@@ -2243,7 +2245,7 @@
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
       <c r="P66" s="1"/>
-      <c r="Q66" s="4"/>
+      <c r="Q66" s="6"/>
       <c r="R66" s="1"/>
     </row>
     <row r="67" ht="12.75">
@@ -2256,7 +2258,7 @@
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
-      <c r="H67" s="3"/>
+      <c r="H67" s="5"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
@@ -2265,7 +2267,7 @@
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
       <c r="P67" s="1"/>
-      <c r="Q67" s="4"/>
+      <c r="Q67" s="6"/>
       <c r="R67" s="1"/>
     </row>
     <row r="68" ht="12.75">
@@ -2278,7 +2280,7 @@
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
-      <c r="H68" s="3"/>
+      <c r="H68" s="5"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
@@ -2287,7 +2289,7 @@
       <c r="N68" s="1"/>
       <c r="O68" s="1"/>
       <c r="P68" s="1"/>
-      <c r="Q68" s="4"/>
+      <c r="Q68" s="6"/>
       <c r="R68" s="1"/>
     </row>
     <row r="69" ht="12.75">
@@ -2300,7 +2302,7 @@
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
-      <c r="H69" s="3"/>
+      <c r="H69" s="5"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
@@ -2309,7 +2311,7 @@
       <c r="N69" s="1"/>
       <c r="O69" s="1"/>
       <c r="P69" s="1"/>
-      <c r="Q69" s="4"/>
+      <c r="Q69" s="6"/>
       <c r="R69" s="1"/>
     </row>
     <row r="70" ht="12.75">
@@ -2322,7 +2324,7 @@
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
-      <c r="H70" s="3"/>
+      <c r="H70" s="5"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
@@ -2331,7 +2333,7 @@
       <c r="N70" s="1"/>
       <c r="O70" s="1"/>
       <c r="P70" s="1"/>
-      <c r="Q70" s="4"/>
+      <c r="Q70" s="6"/>
       <c r="R70" s="1"/>
     </row>
     <row r="71" ht="12.75">
@@ -2344,7 +2346,7 @@
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
-      <c r="H71" s="3"/>
+      <c r="H71" s="5"/>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
@@ -2353,7 +2355,7 @@
       <c r="N71" s="1"/>
       <c r="O71" s="1"/>
       <c r="P71" s="1"/>
-      <c r="Q71" s="4"/>
+      <c r="Q71" s="6"/>
       <c r="R71" s="1"/>
     </row>
     <row r="72" ht="12.75">
@@ -2366,7 +2368,7 @@
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
-      <c r="H72" s="3"/>
+      <c r="H72" s="5"/>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
@@ -2375,7 +2377,7 @@
       <c r="N72" s="1"/>
       <c r="O72" s="1"/>
       <c r="P72" s="1"/>
-      <c r="Q72" s="4"/>
+      <c r="Q72" s="6"/>
       <c r="R72" s="1"/>
     </row>
     <row r="73" ht="12.75">
@@ -2388,16 +2390,16 @@
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
-      <c r="H73" s="3"/>
+      <c r="H73" s="5"/>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
-      <c r="K73" s="5"/>
+      <c r="K73" s="7"/>
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
       <c r="N73" s="1"/>
       <c r="O73" s="1"/>
       <c r="P73" s="1"/>
-      <c r="Q73" s="4"/>
+      <c r="Q73" s="6"/>
       <c r="R73" s="1"/>
     </row>
     <row r="74" ht="12.75">
@@ -2410,7 +2412,7 @@
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
-      <c r="H74" s="3"/>
+      <c r="H74" s="5"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
@@ -2419,7 +2421,7 @@
       <c r="N74" s="1"/>
       <c r="O74" s="1"/>
       <c r="P74" s="1"/>
-      <c r="Q74" s="4"/>
+      <c r="Q74" s="6"/>
       <c r="R74" s="1"/>
     </row>
     <row r="75" ht="12.75">
@@ -2432,7 +2434,7 @@
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
-      <c r="H75" s="3"/>
+      <c r="H75" s="5"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
@@ -2441,7 +2443,7 @@
       <c r="N75" s="1"/>
       <c r="O75" s="1"/>
       <c r="P75" s="1"/>
-      <c r="Q75" s="4"/>
+      <c r="Q75" s="6"/>
       <c r="R75" s="1"/>
     </row>
     <row r="76" ht="12.75">
@@ -2454,7 +2456,7 @@
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
-      <c r="H76" s="3"/>
+      <c r="H76" s="5"/>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
@@ -2463,7 +2465,7 @@
       <c r="N76" s="1"/>
       <c r="O76" s="1"/>
       <c r="P76" s="1"/>
-      <c r="Q76" s="4"/>
+      <c r="Q76" s="6"/>
       <c r="R76" s="1"/>
     </row>
     <row r="77" ht="12.75">
@@ -2476,7 +2478,7 @@
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
-      <c r="H77" s="3"/>
+      <c r="H77" s="5"/>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
@@ -2485,7 +2487,7 @@
       <c r="N77" s="1"/>
       <c r="O77" s="1"/>
       <c r="P77" s="1"/>
-      <c r="Q77" s="4"/>
+      <c r="Q77" s="6"/>
       <c r="R77" s="1"/>
     </row>
     <row r="78" ht="12.75">
@@ -2498,7 +2500,7 @@
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
-      <c r="H78" s="3"/>
+      <c r="H78" s="5"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
@@ -2507,7 +2509,7 @@
       <c r="N78" s="1"/>
       <c r="O78" s="1"/>
       <c r="P78" s="1"/>
-      <c r="Q78" s="4"/>
+      <c r="Q78" s="6"/>
       <c r="R78" s="1"/>
     </row>
     <row r="79" ht="12.75">
@@ -2520,7 +2522,7 @@
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
-      <c r="H79" s="3"/>
+      <c r="H79" s="5"/>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
@@ -2529,7 +2531,7 @@
       <c r="N79" s="1"/>
       <c r="O79" s="1"/>
       <c r="P79" s="1"/>
-      <c r="Q79" s="4"/>
+      <c r="Q79" s="6"/>
       <c r="R79" s="1"/>
     </row>
     <row r="80" ht="12.75">
@@ -2542,16 +2544,16 @@
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
-      <c r="H80" s="3"/>
+      <c r="H80" s="5"/>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
-      <c r="K80" s="5"/>
+      <c r="K80" s="7"/>
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
       <c r="N80" s="1"/>
       <c r="O80" s="1"/>
       <c r="P80" s="1"/>
-      <c r="Q80" s="4"/>
+      <c r="Q80" s="6"/>
       <c r="R80" s="1"/>
     </row>
     <row r="81" ht="12.75">
@@ -2564,7 +2566,7 @@
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
-      <c r="H81" s="3"/>
+      <c r="H81" s="5"/>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
@@ -2573,7 +2575,7 @@
       <c r="N81" s="1"/>
       <c r="O81" s="1"/>
       <c r="P81" s="1"/>
-      <c r="Q81" s="4"/>
+      <c r="Q81" s="6"/>
       <c r="R81" s="1"/>
     </row>
     <row r="82" ht="12.75">
@@ -2586,7 +2588,7 @@
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
-      <c r="H82" s="3"/>
+      <c r="H82" s="5"/>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
@@ -2595,7 +2597,7 @@
       <c r="N82" s="1"/>
       <c r="O82" s="1"/>
       <c r="P82" s="1"/>
-      <c r="Q82" s="4"/>
+      <c r="Q82" s="6"/>
       <c r="R82" s="1"/>
     </row>
     <row r="83" ht="12.75">
@@ -2608,7 +2610,7 @@
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
-      <c r="H83" s="3"/>
+      <c r="H83" s="5"/>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
@@ -2617,7 +2619,7 @@
       <c r="N83" s="1"/>
       <c r="O83" s="1"/>
       <c r="P83" s="1"/>
-      <c r="Q83" s="4"/>
+      <c r="Q83" s="6"/>
       <c r="R83" s="1"/>
     </row>
     <row r="84" ht="12.75">
@@ -2630,7 +2632,7 @@
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
-      <c r="H84" s="3"/>
+      <c r="H84" s="5"/>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
@@ -2639,7 +2641,7 @@
       <c r="N84" s="1"/>
       <c r="O84" s="1"/>
       <c r="P84" s="1"/>
-      <c r="Q84" s="4"/>
+      <c r="Q84" s="6"/>
       <c r="R84" s="1"/>
     </row>
     <row r="85" ht="12.75">
@@ -2652,7 +2654,7 @@
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
-      <c r="H85" s="3"/>
+      <c r="H85" s="5"/>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
@@ -2661,7 +2663,7 @@
       <c r="N85" s="1"/>
       <c r="O85" s="1"/>
       <c r="P85" s="1"/>
-      <c r="Q85" s="4"/>
+      <c r="Q85" s="6"/>
       <c r="R85" s="1"/>
     </row>
     <row r="86" ht="12.75">
@@ -2674,16 +2676,16 @@
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
-      <c r="H86" s="3"/>
+      <c r="H86" s="5"/>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
-      <c r="K86" s="5"/>
+      <c r="K86" s="7"/>
       <c r="L86" s="1"/>
       <c r="M86" s="1"/>
       <c r="N86" s="1"/>
       <c r="O86" s="1"/>
       <c r="P86" s="1"/>
-      <c r="Q86" s="4"/>
+      <c r="Q86" s="6"/>
       <c r="R86" s="1"/>
     </row>
     <row r="87" ht="12.75">
@@ -2696,7 +2698,7 @@
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
-      <c r="H87" s="3"/>
+      <c r="H87" s="5"/>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
       <c r="K87" s="1"/>
@@ -2705,7 +2707,7 @@
       <c r="N87" s="1"/>
       <c r="O87" s="1"/>
       <c r="P87" s="1"/>
-      <c r="Q87" s="4"/>
+      <c r="Q87" s="6"/>
       <c r="R87" s="1"/>
     </row>
     <row r="88" ht="12.75">
@@ -2718,7 +2720,7 @@
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
-      <c r="H88" s="3"/>
+      <c r="H88" s="5"/>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
@@ -2727,7 +2729,7 @@
       <c r="N88" s="1"/>
       <c r="O88" s="1"/>
       <c r="P88" s="1"/>
-      <c r="Q88" s="4"/>
+      <c r="Q88" s="6"/>
       <c r="R88" s="1"/>
     </row>
     <row r="89" ht="12.75">
@@ -2740,16 +2742,16 @@
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
-      <c r="H89" s="3"/>
+      <c r="H89" s="5"/>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
-      <c r="K89" s="5"/>
-      <c r="L89" s="5"/>
+      <c r="K89" s="7"/>
+      <c r="L89" s="7"/>
       <c r="M89" s="1"/>
       <c r="N89" s="1"/>
       <c r="O89" s="1"/>
       <c r="P89" s="1"/>
-      <c r="Q89" s="4"/>
+      <c r="Q89" s="6"/>
       <c r="R89" s="1"/>
     </row>
     <row r="90" ht="12.75">
@@ -2762,7 +2764,7 @@
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
-      <c r="H90" s="3"/>
+      <c r="H90" s="5"/>
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
@@ -2771,7 +2773,7 @@
       <c r="N90" s="1"/>
       <c r="O90" s="1"/>
       <c r="P90" s="1"/>
-      <c r="Q90" s="4"/>
+      <c r="Q90" s="6"/>
       <c r="R90" s="1"/>
     </row>
     <row r="91" ht="12.75">
@@ -2784,7 +2786,7 @@
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
-      <c r="H91" s="3"/>
+      <c r="H91" s="5"/>
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
@@ -2793,7 +2795,7 @@
       <c r="N91" s="1"/>
       <c r="O91" s="1"/>
       <c r="P91" s="1"/>
-      <c r="Q91" s="4"/>
+      <c r="Q91" s="6"/>
       <c r="R91" s="1"/>
     </row>
     <row r="92" ht="12.75">
@@ -2806,7 +2808,7 @@
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
-      <c r="H92" s="3"/>
+      <c r="H92" s="5"/>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
@@ -2815,7 +2817,7 @@
       <c r="N92" s="1"/>
       <c r="O92" s="1"/>
       <c r="P92" s="1"/>
-      <c r="Q92" s="4"/>
+      <c r="Q92" s="6"/>
       <c r="R92" s="1"/>
     </row>
     <row r="93" ht="12.75">
@@ -2828,7 +2830,7 @@
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
-      <c r="H93" s="3"/>
+      <c r="H93" s="5"/>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
@@ -2837,7 +2839,7 @@
       <c r="N93" s="1"/>
       <c r="O93" s="1"/>
       <c r="P93" s="1"/>
-      <c r="Q93" s="4"/>
+      <c r="Q93" s="6"/>
       <c r="R93" s="1"/>
     </row>
     <row r="94" ht="12.75">
@@ -2850,7 +2852,7 @@
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
-      <c r="H94" s="3"/>
+      <c r="H94" s="5"/>
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
       <c r="K94" s="1"/>
@@ -2859,7 +2861,7 @@
       <c r="N94" s="1"/>
       <c r="O94" s="1"/>
       <c r="P94" s="1"/>
-      <c r="Q94" s="4"/>
+      <c r="Q94" s="6"/>
       <c r="R94" s="1"/>
     </row>
     <row r="95" ht="12.75">
@@ -2872,7 +2874,7 @@
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
-      <c r="H95" s="3"/>
+      <c r="H95" s="5"/>
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
@@ -2881,7 +2883,7 @@
       <c r="N95" s="1"/>
       <c r="O95" s="1"/>
       <c r="P95" s="1"/>
-      <c r="Q95" s="4"/>
+      <c r="Q95" s="6"/>
       <c r="R95" s="1"/>
     </row>
     <row r="96" ht="12.75">
@@ -2894,7 +2896,7 @@
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
-      <c r="H96" s="3"/>
+      <c r="H96" s="5"/>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
@@ -2903,7 +2905,7 @@
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
       <c r="P96" s="1"/>
-      <c r="Q96" s="4"/>
+      <c r="Q96" s="6"/>
       <c r="R96" s="1"/>
     </row>
     <row r="97" ht="12.75">
@@ -2916,7 +2918,7 @@
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
-      <c r="H97" s="3"/>
+      <c r="H97" s="5"/>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
@@ -2924,8 +2926,8 @@
       <c r="M97" s="1"/>
       <c r="N97" s="1"/>
       <c r="O97" s="1"/>
-      <c r="P97" s="4"/>
-      <c r="Q97" s="4"/>
+      <c r="P97" s="6"/>
+      <c r="Q97" s="6"/>
       <c r="R97" s="1"/>
     </row>
     <row r="98" ht="12.75">
@@ -2938,7 +2940,7 @@
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
-      <c r="H98" s="3"/>
+      <c r="H98" s="5"/>
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
@@ -2947,7 +2949,7 @@
       <c r="N98" s="1"/>
       <c r="O98" s="1"/>
       <c r="P98" s="1"/>
-      <c r="Q98" s="4"/>
+      <c r="Q98" s="6"/>
       <c r="R98" s="1"/>
     </row>
     <row r="99" ht="12.75">
@@ -2960,7 +2962,7 @@
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
-      <c r="H99" s="3"/>
+      <c r="H99" s="5"/>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
@@ -2969,7 +2971,7 @@
       <c r="N99" s="1"/>
       <c r="O99" s="1"/>
       <c r="P99" s="1"/>
-      <c r="Q99" s="4"/>
+      <c r="Q99" s="6"/>
       <c r="R99" s="1"/>
     </row>
     <row r="100" ht="12.75">
@@ -2982,7 +2984,7 @@
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
-      <c r="H100" s="3"/>
+      <c r="H100" s="5"/>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
@@ -2991,7 +2993,7 @@
       <c r="N100" s="1"/>
       <c r="O100" s="1"/>
       <c r="P100" s="1"/>
-      <c r="Q100" s="4"/>
+      <c r="Q100" s="6"/>
       <c r="R100" s="1"/>
     </row>
     <row r="101" ht="12.75">
@@ -3004,7 +3006,7 @@
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
-      <c r="H101" s="3"/>
+      <c r="H101" s="5"/>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
@@ -3013,7 +3015,7 @@
       <c r="N101" s="1"/>
       <c r="O101" s="1"/>
       <c r="P101" s="1"/>
-      <c r="Q101" s="4"/>
+      <c r="Q101" s="6"/>
       <c r="R101" s="1"/>
     </row>
     <row r="102" ht="12.75">
@@ -3026,7 +3028,7 @@
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
-      <c r="H102" s="3"/>
+      <c r="H102" s="5"/>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
@@ -3035,7 +3037,7 @@
       <c r="N102" s="1"/>
       <c r="O102" s="1"/>
       <c r="P102" s="1"/>
-      <c r="Q102" s="4"/>
+      <c r="Q102" s="6"/>
       <c r="R102" s="1"/>
     </row>
     <row r="103" ht="12.75">
@@ -3048,7 +3050,7 @@
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
-      <c r="H103" s="3"/>
+      <c r="H103" s="5"/>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
       <c r="K103" s="1"/>
@@ -3057,7 +3059,7 @@
       <c r="N103" s="1"/>
       <c r="O103" s="1"/>
       <c r="P103" s="1"/>
-      <c r="Q103" s="4"/>
+      <c r="Q103" s="6"/>
       <c r="R103" s="1"/>
     </row>
     <row r="104" ht="12.75">
@@ -3070,7 +3072,7 @@
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
-      <c r="H104" s="3"/>
+      <c r="H104" s="5"/>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
       <c r="K104" s="1"/>
@@ -3079,7 +3081,7 @@
       <c r="N104" s="1"/>
       <c r="O104" s="1"/>
       <c r="P104" s="1"/>
-      <c r="Q104" s="4"/>
+      <c r="Q104" s="6"/>
       <c r="R104" s="1"/>
     </row>
     <row r="105" ht="12.75">
@@ -3092,7 +3094,7 @@
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
-      <c r="H105" s="3"/>
+      <c r="H105" s="5"/>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
@@ -3101,7 +3103,7 @@
       <c r="N105" s="1"/>
       <c r="O105" s="1"/>
       <c r="P105" s="1"/>
-      <c r="Q105" s="4"/>
+      <c r="Q105" s="6"/>
       <c r="R105" s="1"/>
     </row>
     <row r="106" ht="12.75">
@@ -3114,7 +3116,7 @@
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
-      <c r="H106" s="3"/>
+      <c r="H106" s="5"/>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
@@ -3123,7 +3125,7 @@
       <c r="N106" s="1"/>
       <c r="O106" s="1"/>
       <c r="P106" s="1"/>
-      <c r="Q106" s="4"/>
+      <c r="Q106" s="6"/>
       <c r="R106" s="1"/>
     </row>
     <row r="107" ht="12.75">
@@ -3136,7 +3138,7 @@
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
-      <c r="H107" s="3"/>
+      <c r="H107" s="5"/>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
@@ -3145,7 +3147,7 @@
       <c r="N107" s="1"/>
       <c r="O107" s="1"/>
       <c r="P107" s="1"/>
-      <c r="Q107" s="4"/>
+      <c r="Q107" s="6"/>
       <c r="R107" s="1"/>
     </row>
     <row r="108" ht="12.75">
@@ -3158,16 +3160,16 @@
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
-      <c r="H108" s="3"/>
+      <c r="H108" s="5"/>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
-      <c r="K108" s="5"/>
+      <c r="K108" s="7"/>
       <c r="L108" s="1"/>
       <c r="M108" s="1"/>
       <c r="N108" s="1"/>
       <c r="O108" s="1"/>
       <c r="P108" s="1"/>
-      <c r="Q108" s="4"/>
+      <c r="Q108" s="6"/>
       <c r="R108" s="1"/>
     </row>
     <row r="109" ht="12.75">
@@ -3180,16 +3182,16 @@
       <c r="E109" s="1"/>
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
-      <c r="H109" s="3"/>
+      <c r="H109" s="5"/>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
-      <c r="K109" s="5"/>
+      <c r="K109" s="7"/>
       <c r="L109" s="1"/>
       <c r="M109" s="1"/>
       <c r="N109" s="1"/>
       <c r="O109" s="1"/>
       <c r="P109" s="1"/>
-      <c r="Q109" s="4"/>
+      <c r="Q109" s="6"/>
       <c r="R109" s="1"/>
     </row>
     <row r="110" ht="12.75">
@@ -3202,7 +3204,7 @@
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
-      <c r="H110" s="3"/>
+      <c r="H110" s="5"/>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
       <c r="K110" s="1"/>
@@ -3211,7 +3213,7 @@
       <c r="N110" s="1"/>
       <c r="O110" s="1"/>
       <c r="P110" s="1"/>
-      <c r="Q110" s="4"/>
+      <c r="Q110" s="6"/>
       <c r="R110" s="1"/>
     </row>
     <row r="111" ht="12.75">
@@ -3224,7 +3226,7 @@
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
-      <c r="H111" s="3"/>
+      <c r="H111" s="5"/>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
       <c r="K111" s="1"/>
@@ -3233,7 +3235,7 @@
       <c r="N111" s="1"/>
       <c r="O111" s="1"/>
       <c r="P111" s="1"/>
-      <c r="Q111" s="4"/>
+      <c r="Q111" s="6"/>
       <c r="R111" s="1"/>
     </row>
     <row r="112" ht="12.75">
@@ -3246,16 +3248,16 @@
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
-      <c r="H112" s="3"/>
+      <c r="H112" s="5"/>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
-      <c r="K112" s="5"/>
+      <c r="K112" s="7"/>
       <c r="L112" s="1"/>
       <c r="M112" s="1"/>
       <c r="N112" s="1"/>
       <c r="O112" s="1"/>
       <c r="P112" s="1"/>
-      <c r="Q112" s="4"/>
+      <c r="Q112" s="6"/>
       <c r="R112" s="1"/>
     </row>
     <row r="113" ht="12.75">
@@ -3268,7 +3270,7 @@
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
-      <c r="H113" s="3"/>
+      <c r="H113" s="5"/>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
       <c r="K113" s="1"/>
@@ -3277,7 +3279,7 @@
       <c r="N113" s="1"/>
       <c r="O113" s="1"/>
       <c r="P113" s="1"/>
-      <c r="Q113" s="4"/>
+      <c r="Q113" s="6"/>
       <c r="R113" s="1"/>
     </row>
     <row r="114" ht="12.75">
@@ -3290,7 +3292,7 @@
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
-      <c r="H114" s="3"/>
+      <c r="H114" s="5"/>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
       <c r="K114" s="1"/>
@@ -3299,7 +3301,7 @@
       <c r="N114" s="1"/>
       <c r="O114" s="1"/>
       <c r="P114" s="1"/>
-      <c r="Q114" s="4"/>
+      <c r="Q114" s="6"/>
       <c r="R114" s="1"/>
     </row>
     <row r="115" ht="12.75">
@@ -3312,7 +3314,7 @@
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
-      <c r="H115" s="3"/>
+      <c r="H115" s="5"/>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
       <c r="K115" s="1"/>
@@ -3321,7 +3323,7 @@
       <c r="N115" s="1"/>
       <c r="O115" s="1"/>
       <c r="P115" s="1"/>
-      <c r="Q115" s="4"/>
+      <c r="Q115" s="6"/>
       <c r="R115" s="1"/>
     </row>
     <row r="116" ht="12.75">
@@ -3334,7 +3336,7 @@
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
-      <c r="H116" s="3"/>
+      <c r="H116" s="5"/>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
       <c r="K116" s="1"/>
@@ -3343,7 +3345,7 @@
       <c r="N116" s="1"/>
       <c r="O116" s="1"/>
       <c r="P116" s="1"/>
-      <c r="Q116" s="4"/>
+      <c r="Q116" s="6"/>
       <c r="R116" s="1"/>
     </row>
     <row r="117" ht="12.75">
@@ -3356,7 +3358,7 @@
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
-      <c r="H117" s="3"/>
+      <c r="H117" s="5"/>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
       <c r="K117" s="1"/>
@@ -3365,7 +3367,7 @@
       <c r="N117" s="1"/>
       <c r="O117" s="1"/>
       <c r="P117" s="1"/>
-      <c r="Q117" s="4"/>
+      <c r="Q117" s="6"/>
       <c r="R117" s="1"/>
     </row>
     <row r="118" ht="12.75">
@@ -3378,7 +3380,7 @@
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
-      <c r="H118" s="3"/>
+      <c r="H118" s="5"/>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
       <c r="K118" s="1"/>
@@ -3387,7 +3389,7 @@
       <c r="N118" s="1"/>
       <c r="O118" s="1"/>
       <c r="P118" s="1"/>
-      <c r="Q118" s="4"/>
+      <c r="Q118" s="6"/>
       <c r="R118" s="1"/>
     </row>
     <row r="119" ht="12.75">
@@ -3400,7 +3402,7 @@
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
-      <c r="H119" s="3"/>
+      <c r="H119" s="5"/>
       <c r="I119" s="1"/>
       <c r="J119" s="1"/>
       <c r="K119" s="1"/>
@@ -3409,7 +3411,7 @@
       <c r="N119" s="1"/>
       <c r="O119" s="1"/>
       <c r="P119" s="1"/>
-      <c r="Q119" s="4"/>
+      <c r="Q119" s="6"/>
       <c r="R119" s="1"/>
     </row>
     <row r="120" ht="12.75">
@@ -3422,7 +3424,7 @@
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
-      <c r="H120" s="3"/>
+      <c r="H120" s="5"/>
       <c r="I120" s="1"/>
       <c r="J120" s="1"/>
       <c r="K120" s="1"/>
@@ -3431,7 +3433,7 @@
       <c r="N120" s="1"/>
       <c r="O120" s="1"/>
       <c r="P120" s="1"/>
-      <c r="Q120" s="4"/>
+      <c r="Q120" s="6"/>
       <c r="R120" s="1"/>
     </row>
     <row r="121" ht="12.75">
@@ -3444,7 +3446,7 @@
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
-      <c r="H121" s="3"/>
+      <c r="H121" s="5"/>
       <c r="I121" s="1"/>
       <c r="J121" s="1"/>
       <c r="K121" s="1"/>
@@ -3453,7 +3455,7 @@
       <c r="N121" s="1"/>
       <c r="O121" s="1"/>
       <c r="P121" s="1"/>
-      <c r="Q121" s="4"/>
+      <c r="Q121" s="6"/>
       <c r="R121" s="1"/>
     </row>
     <row r="122" ht="12.75">
@@ -3466,16 +3468,16 @@
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
-      <c r="H122" s="3"/>
+      <c r="H122" s="5"/>
       <c r="I122" s="1"/>
       <c r="J122" s="1"/>
-      <c r="K122" s="5"/>
+      <c r="K122" s="7"/>
       <c r="L122" s="1"/>
       <c r="M122" s="1"/>
       <c r="N122" s="1"/>
       <c r="O122" s="1"/>
       <c r="P122" s="1"/>
-      <c r="Q122" s="4"/>
+      <c r="Q122" s="6"/>
       <c r="R122" s="1"/>
     </row>
     <row r="123" ht="12.75">
@@ -3488,7 +3490,7 @@
       <c r="E123" s="1"/>
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
-      <c r="H123" s="3"/>
+      <c r="H123" s="5"/>
       <c r="I123" s="1"/>
       <c r="J123" s="1"/>
       <c r="K123" s="1"/>
@@ -3497,7 +3499,7 @@
       <c r="N123" s="1"/>
       <c r="O123" s="1"/>
       <c r="P123" s="1"/>
-      <c r="Q123" s="4"/>
+      <c r="Q123" s="6"/>
       <c r="R123" s="1"/>
     </row>
     <row r="124" ht="12.75">
@@ -3510,7 +3512,7 @@
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
-      <c r="H124" s="3"/>
+      <c r="H124" s="5"/>
       <c r="I124" s="1"/>
       <c r="J124" s="1"/>
       <c r="K124" s="1"/>
@@ -3519,7 +3521,7 @@
       <c r="N124" s="1"/>
       <c r="O124" s="1"/>
       <c r="P124" s="1"/>
-      <c r="Q124" s="4"/>
+      <c r="Q124" s="6"/>
       <c r="R124" s="1"/>
     </row>
     <row r="125" ht="12.75">
@@ -3532,7 +3534,7 @@
       <c r="E125" s="1"/>
       <c r="F125" s="1"/>
       <c r="G125" s="1"/>
-      <c r="H125" s="3"/>
+      <c r="H125" s="5"/>
       <c r="I125" s="1"/>
       <c r="J125" s="1"/>
       <c r="K125" s="1"/>
@@ -3541,7 +3543,7 @@
       <c r="N125" s="1"/>
       <c r="O125" s="1"/>
       <c r="P125" s="1"/>
-      <c r="Q125" s="4"/>
+      <c r="Q125" s="6"/>
       <c r="R125" s="1"/>
     </row>
     <row r="126" ht="12.75">
@@ -3554,7 +3556,7 @@
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
       <c r="G126" s="1"/>
-      <c r="H126" s="3"/>
+      <c r="H126" s="5"/>
       <c r="I126" s="1"/>
       <c r="J126" s="1"/>
       <c r="K126" s="1"/>
@@ -3563,7 +3565,7 @@
       <c r="N126" s="1"/>
       <c r="O126" s="1"/>
       <c r="P126" s="1"/>
-      <c r="Q126" s="4"/>
+      <c r="Q126" s="6"/>
       <c r="R126" s="1"/>
     </row>
     <row r="127" ht="12.75">
@@ -3576,7 +3578,7 @@
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
       <c r="G127" s="1"/>
-      <c r="H127" s="3"/>
+      <c r="H127" s="5"/>
       <c r="I127" s="1"/>
       <c r="J127" s="1"/>
       <c r="K127" s="1"/>
@@ -3585,7 +3587,7 @@
       <c r="N127" s="1"/>
       <c r="O127" s="1"/>
       <c r="P127" s="1"/>
-      <c r="Q127" s="4"/>
+      <c r="Q127" s="6"/>
       <c r="R127" s="1"/>
     </row>
     <row r="128" ht="12.75">
@@ -3598,7 +3600,7 @@
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
       <c r="G128" s="1"/>
-      <c r="H128" s="3"/>
+      <c r="H128" s="5"/>
       <c r="I128" s="1"/>
       <c r="J128" s="1"/>
       <c r="K128" s="1"/>
@@ -3607,7 +3609,7 @@
       <c r="N128" s="1"/>
       <c r="O128" s="1"/>
       <c r="P128" s="1"/>
-      <c r="Q128" s="4"/>
+      <c r="Q128" s="6"/>
       <c r="R128" s="1"/>
     </row>
     <row r="129" ht="12.75">
@@ -3620,7 +3622,7 @@
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
       <c r="G129" s="1"/>
-      <c r="H129" s="3"/>
+      <c r="H129" s="5"/>
       <c r="I129" s="1"/>
       <c r="J129" s="1"/>
       <c r="K129" s="1"/>
@@ -3629,7 +3631,7 @@
       <c r="N129" s="1"/>
       <c r="O129" s="1"/>
       <c r="P129" s="1"/>
-      <c r="Q129" s="4"/>
+      <c r="Q129" s="6"/>
       <c r="R129" s="1"/>
     </row>
     <row r="130" ht="12.75">
@@ -3642,7 +3644,7 @@
       <c r="E130" s="1"/>
       <c r="F130" s="1"/>
       <c r="G130" s="1"/>
-      <c r="H130" s="3"/>
+      <c r="H130" s="5"/>
       <c r="I130" s="1"/>
       <c r="J130" s="1"/>
       <c r="K130" s="1"/>
@@ -3651,7 +3653,7 @@
       <c r="N130" s="1"/>
       <c r="O130" s="1"/>
       <c r="P130" s="1"/>
-      <c r="Q130" s="4"/>
+      <c r="Q130" s="6"/>
       <c r="R130" s="1"/>
     </row>
     <row r="131" ht="12.75">
@@ -3664,7 +3666,7 @@
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
       <c r="G131" s="1"/>
-      <c r="H131" s="3"/>
+      <c r="H131" s="5"/>
       <c r="I131" s="1"/>
       <c r="J131" s="1"/>
       <c r="K131" s="1"/>
@@ -3673,7 +3675,7 @@
       <c r="N131" s="1"/>
       <c r="O131" s="1"/>
       <c r="P131" s="1"/>
-      <c r="Q131" s="4"/>
+      <c r="Q131" s="6"/>
       <c r="R131" s="1"/>
     </row>
     <row r="132" ht="12.75">
@@ -3686,7 +3688,7 @@
       <c r="E132" s="1"/>
       <c r="F132" s="1"/>
       <c r="G132" s="1"/>
-      <c r="H132" s="3"/>
+      <c r="H132" s="5"/>
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
       <c r="K132" s="1"/>
@@ -3695,7 +3697,7 @@
       <c r="N132" s="1"/>
       <c r="O132" s="1"/>
       <c r="P132" s="1"/>
-      <c r="Q132" s="4"/>
+      <c r="Q132" s="6"/>
       <c r="R132" s="1"/>
     </row>
     <row r="133" ht="12.75">
@@ -3708,7 +3710,7 @@
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
       <c r="G133" s="1"/>
-      <c r="H133" s="3"/>
+      <c r="H133" s="5"/>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
       <c r="K133" s="1"/>
@@ -3717,7 +3719,7 @@
       <c r="N133" s="1"/>
       <c r="O133" s="1"/>
       <c r="P133" s="1"/>
-      <c r="Q133" s="4"/>
+      <c r="Q133" s="6"/>
       <c r="R133" s="1"/>
     </row>
     <row r="134" ht="12.75">
@@ -3730,7 +3732,7 @@
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
-      <c r="H134" s="3"/>
+      <c r="H134" s="5"/>
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
       <c r="K134" s="1"/>
@@ -3739,7 +3741,7 @@
       <c r="N134" s="1"/>
       <c r="O134" s="1"/>
       <c r="P134" s="1"/>
-      <c r="Q134" s="4"/>
+      <c r="Q134" s="6"/>
       <c r="R134" s="1"/>
     </row>
     <row r="135" ht="12.75">
@@ -3752,7 +3754,7 @@
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
-      <c r="H135" s="3"/>
+      <c r="H135" s="5"/>
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
       <c r="K135" s="1"/>
@@ -3761,7 +3763,7 @@
       <c r="N135" s="1"/>
       <c r="O135" s="1"/>
       <c r="P135" s="1"/>
-      <c r="Q135" s="4"/>
+      <c r="Q135" s="6"/>
       <c r="R135" s="1"/>
     </row>
     <row r="136" ht="12.75">
@@ -3774,7 +3776,7 @@
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
       <c r="G136" s="1"/>
-      <c r="H136" s="3"/>
+      <c r="H136" s="5"/>
       <c r="I136" s="1"/>
       <c r="J136" s="1"/>
       <c r="K136" s="1"/>
@@ -3783,7 +3785,7 @@
       <c r="N136" s="1"/>
       <c r="O136" s="1"/>
       <c r="P136" s="1"/>
-      <c r="Q136" s="4"/>
+      <c r="Q136" s="6"/>
       <c r="R136" s="1"/>
     </row>
     <row r="137" ht="12.75">
@@ -3796,7 +3798,7 @@
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
-      <c r="H137" s="3"/>
+      <c r="H137" s="5"/>
       <c r="I137" s="1"/>
       <c r="J137" s="1"/>
       <c r="K137" s="1"/>
@@ -3805,7 +3807,7 @@
       <c r="N137" s="1"/>
       <c r="O137" s="1"/>
       <c r="P137" s="1"/>
-      <c r="Q137" s="4"/>
+      <c r="Q137" s="6"/>
       <c r="R137" s="1"/>
     </row>
     <row r="138" ht="12.75">
@@ -3818,7 +3820,7 @@
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
       <c r="G138" s="1"/>
-      <c r="H138" s="3"/>
+      <c r="H138" s="5"/>
       <c r="I138" s="1"/>
       <c r="J138" s="1"/>
       <c r="K138" s="1"/>
@@ -3827,7 +3829,7 @@
       <c r="N138" s="1"/>
       <c r="O138" s="1"/>
       <c r="P138" s="1"/>
-      <c r="Q138" s="4"/>
+      <c r="Q138" s="6"/>
       <c r="R138" s="1"/>
     </row>
     <row r="139" ht="12.75">
@@ -3840,16 +3842,16 @@
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
-      <c r="H139" s="3"/>
+      <c r="H139" s="5"/>
       <c r="I139" s="1"/>
       <c r="J139" s="1"/>
-      <c r="K139" s="5"/>
+      <c r="K139" s="7"/>
       <c r="L139" s="1"/>
       <c r="M139" s="1"/>
       <c r="N139" s="1"/>
       <c r="O139" s="1"/>
       <c r="P139" s="1"/>
-      <c r="Q139" s="4"/>
+      <c r="Q139" s="6"/>
       <c r="R139" s="1"/>
     </row>
     <row r="140" ht="12.75">
@@ -3862,7 +3864,7 @@
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
       <c r="G140" s="1"/>
-      <c r="H140" s="3"/>
+      <c r="H140" s="5"/>
       <c r="I140" s="1"/>
       <c r="J140" s="1"/>
       <c r="K140" s="1"/>
@@ -3871,7 +3873,7 @@
       <c r="N140" s="1"/>
       <c r="O140" s="1"/>
       <c r="P140" s="1"/>
-      <c r="Q140" s="4"/>
+      <c r="Q140" s="6"/>
       <c r="R140" s="1"/>
     </row>
     <row r="141" ht="12.75">
@@ -3884,7 +3886,7 @@
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
       <c r="G141" s="1"/>
-      <c r="H141" s="3"/>
+      <c r="H141" s="5"/>
       <c r="I141" s="1"/>
       <c r="J141" s="1"/>
       <c r="K141" s="1"/>
@@ -3893,7 +3895,7 @@
       <c r="N141" s="1"/>
       <c r="O141" s="1"/>
       <c r="P141" s="1"/>
-      <c r="Q141" s="4"/>
+      <c r="Q141" s="6"/>
       <c r="R141" s="1"/>
     </row>
     <row r="142" ht="12.75">
@@ -3906,7 +3908,7 @@
       <c r="E142" s="1"/>
       <c r="F142" s="1"/>
       <c r="G142" s="1"/>
-      <c r="H142" s="3"/>
+      <c r="H142" s="5"/>
       <c r="I142" s="1"/>
       <c r="J142" s="1"/>
       <c r="K142" s="1"/>
@@ -3915,7 +3917,7 @@
       <c r="N142" s="1"/>
       <c r="O142" s="1"/>
       <c r="P142" s="1"/>
-      <c r="Q142" s="4"/>
+      <c r="Q142" s="6"/>
       <c r="R142" s="1"/>
     </row>
     <row r="143" ht="12.75">
@@ -3928,7 +3930,7 @@
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
       <c r="G143" s="1"/>
-      <c r="H143" s="3"/>
+      <c r="H143" s="5"/>
       <c r="I143" s="1"/>
       <c r="J143" s="1"/>
       <c r="K143" s="1"/>
@@ -3937,7 +3939,7 @@
       <c r="N143" s="1"/>
       <c r="O143" s="1"/>
       <c r="P143" s="1"/>
-      <c r="Q143" s="4"/>
+      <c r="Q143" s="6"/>
       <c r="R143" s="1"/>
     </row>
     <row r="144" ht="12.75">
@@ -3950,7 +3952,7 @@
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
       <c r="G144" s="1"/>
-      <c r="H144" s="3"/>
+      <c r="H144" s="5"/>
       <c r="I144" s="1"/>
       <c r="J144" s="1"/>
       <c r="K144" s="1"/>
@@ -3959,7 +3961,7 @@
       <c r="N144" s="1"/>
       <c r="O144" s="1"/>
       <c r="P144" s="1"/>
-      <c r="Q144" s="4"/>
+      <c r="Q144" s="6"/>
       <c r="R144" s="1"/>
     </row>
     <row r="145" ht="12.75">
@@ -3972,7 +3974,7 @@
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
       <c r="G145" s="1"/>
-      <c r="H145" s="3"/>
+      <c r="H145" s="5"/>
       <c r="I145" s="1"/>
       <c r="J145" s="1"/>
       <c r="K145" s="1"/>
@@ -3981,7 +3983,7 @@
       <c r="N145" s="1"/>
       <c r="O145" s="1"/>
       <c r="P145" s="1"/>
-      <c r="Q145" s="4"/>
+      <c r="Q145" s="6"/>
       <c r="R145" s="1"/>
     </row>
     <row r="146" ht="12.75">
@@ -3994,7 +3996,7 @@
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
       <c r="G146" s="1"/>
-      <c r="H146" s="3"/>
+      <c r="H146" s="5"/>
       <c r="I146" s="1"/>
       <c r="J146" s="1"/>
       <c r="K146" s="1"/>
@@ -4003,7 +4005,7 @@
       <c r="N146" s="1"/>
       <c r="O146" s="1"/>
       <c r="P146" s="1"/>
-      <c r="Q146" s="4"/>
+      <c r="Q146" s="6"/>
       <c r="R146" s="1"/>
     </row>
     <row r="147" ht="12.75">
@@ -4016,7 +4018,7 @@
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
       <c r="G147" s="1"/>
-      <c r="H147" s="3"/>
+      <c r="H147" s="5"/>
       <c r="I147" s="1"/>
       <c r="J147" s="1"/>
       <c r="K147" s="1"/>
@@ -4025,7 +4027,7 @@
       <c r="N147" s="1"/>
       <c r="O147" s="1"/>
       <c r="P147" s="1"/>
-      <c r="Q147" s="4"/>
+      <c r="Q147" s="6"/>
       <c r="R147" s="1"/>
     </row>
     <row r="148" ht="12.75">
@@ -4038,7 +4040,7 @@
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
       <c r="G148" s="1"/>
-      <c r="H148" s="3"/>
+      <c r="H148" s="5"/>
       <c r="I148" s="1"/>
       <c r="J148" s="1"/>
       <c r="K148" s="1"/>
@@ -4047,7 +4049,7 @@
       <c r="N148" s="1"/>
       <c r="O148" s="1"/>
       <c r="P148" s="1"/>
-      <c r="Q148" s="4"/>
+      <c r="Q148" s="6"/>
       <c r="R148" s="1"/>
     </row>
     <row r="149" ht="12.75">
@@ -4060,7 +4062,7 @@
       <c r="E149" s="1"/>
       <c r="F149" s="1"/>
       <c r="G149" s="1"/>
-      <c r="H149" s="3"/>
+      <c r="H149" s="5"/>
       <c r="I149" s="1"/>
       <c r="J149" s="1"/>
       <c r="K149" s="1"/>
@@ -4069,7 +4071,7 @@
       <c r="N149" s="1"/>
       <c r="O149" s="1"/>
       <c r="P149" s="1"/>
-      <c r="Q149" s="4"/>
+      <c r="Q149" s="6"/>
       <c r="R149" s="1"/>
     </row>
     <row r="150" ht="12.75">
@@ -4082,7 +4084,7 @@
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
       <c r="G150" s="1"/>
-      <c r="H150" s="3"/>
+      <c r="H150" s="5"/>
       <c r="I150" s="1"/>
       <c r="J150" s="1"/>
       <c r="K150" s="1"/>
@@ -4091,7 +4093,7 @@
       <c r="N150" s="1"/>
       <c r="O150" s="1"/>
       <c r="P150" s="1"/>
-      <c r="Q150" s="4"/>
+      <c r="Q150" s="6"/>
       <c r="R150" s="1"/>
     </row>
     <row r="151" ht="12.75">
@@ -4104,7 +4106,7 @@
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
       <c r="G151" s="1"/>
-      <c r="H151" s="3"/>
+      <c r="H151" s="5"/>
       <c r="I151" s="1"/>
       <c r="J151" s="1"/>
       <c r="K151" s="1"/>
@@ -4113,7 +4115,7 @@
       <c r="N151" s="1"/>
       <c r="O151" s="1"/>
       <c r="P151" s="1"/>
-      <c r="Q151" s="4"/>
+      <c r="Q151" s="6"/>
       <c r="R151" s="1"/>
     </row>
     <row r="152" ht="12.75">
@@ -4126,7 +4128,7 @@
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
       <c r="G152" s="1"/>
-      <c r="H152" s="3"/>
+      <c r="H152" s="5"/>
       <c r="I152" s="1"/>
       <c r="J152" s="1"/>
       <c r="K152" s="1"/>
@@ -4135,7 +4137,7 @@
       <c r="N152" s="1"/>
       <c r="O152" s="1"/>
       <c r="P152" s="1"/>
-      <c r="Q152" s="4"/>
+      <c r="Q152" s="6"/>
       <c r="R152" s="1"/>
     </row>
     <row r="153" ht="12.75">
@@ -4148,7 +4150,7 @@
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
       <c r="G153" s="1"/>
-      <c r="H153" s="3"/>
+      <c r="H153" s="5"/>
       <c r="I153" s="1"/>
       <c r="J153" s="1"/>
       <c r="K153" s="1"/>
@@ -4157,7 +4159,7 @@
       <c r="N153" s="1"/>
       <c r="O153" s="1"/>
       <c r="P153" s="1"/>
-      <c r="Q153" s="4"/>
+      <c r="Q153" s="6"/>
       <c r="R153" s="1"/>
     </row>
     <row r="154" ht="12.75">
@@ -4170,16 +4172,16 @@
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
       <c r="G154" s="1"/>
-      <c r="H154" s="3"/>
+      <c r="H154" s="5"/>
       <c r="I154" s="1"/>
       <c r="J154" s="1"/>
-      <c r="K154" s="5"/>
+      <c r="K154" s="7"/>
       <c r="L154" s="1"/>
       <c r="M154" s="1"/>
       <c r="N154" s="1"/>
       <c r="O154" s="1"/>
       <c r="P154" s="1"/>
-      <c r="Q154" s="4"/>
+      <c r="Q154" s="6"/>
       <c r="R154" s="1"/>
     </row>
     <row r="155" ht="12.75">
@@ -4192,7 +4194,7 @@
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
       <c r="G155" s="1"/>
-      <c r="H155" s="3"/>
+      <c r="H155" s="5"/>
       <c r="I155" s="1"/>
       <c r="J155" s="1"/>
       <c r="K155" s="1"/>
@@ -4201,7 +4203,7 @@
       <c r="N155" s="1"/>
       <c r="O155" s="1"/>
       <c r="P155" s="1"/>
-      <c r="Q155" s="4"/>
+      <c r="Q155" s="6"/>
       <c r="R155" s="1"/>
     </row>
     <row r="156" ht="12.75">
@@ -4214,7 +4216,7 @@
       <c r="E156" s="1"/>
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
-      <c r="H156" s="3"/>
+      <c r="H156" s="5"/>
       <c r="I156" s="1"/>
       <c r="J156" s="1"/>
       <c r="K156" s="1"/>
@@ -4223,7 +4225,7 @@
       <c r="N156" s="1"/>
       <c r="O156" s="1"/>
       <c r="P156" s="1"/>
-      <c r="Q156" s="4"/>
+      <c r="Q156" s="6"/>
       <c r="R156" s="1"/>
     </row>
     <row r="157" ht="12.75">
@@ -4236,7 +4238,7 @@
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
       <c r="G157" s="1"/>
-      <c r="H157" s="3"/>
+      <c r="H157" s="5"/>
       <c r="I157" s="1"/>
       <c r="J157" s="1"/>
       <c r="K157" s="1"/>
@@ -4245,7 +4247,7 @@
       <c r="N157" s="1"/>
       <c r="O157" s="1"/>
       <c r="P157" s="1"/>
-      <c r="Q157" s="4"/>
+      <c r="Q157" s="6"/>
       <c r="R157" s="1"/>
     </row>
     <row r="158" ht="12.75">
@@ -4258,7 +4260,7 @@
       <c r="E158" s="1"/>
       <c r="F158" s="1"/>
       <c r="G158" s="1"/>
-      <c r="H158" s="3"/>
+      <c r="H158" s="5"/>
       <c r="I158" s="1"/>
       <c r="J158" s="1"/>
       <c r="K158" s="1"/>
@@ -4267,7 +4269,7 @@
       <c r="N158" s="1"/>
       <c r="O158" s="1"/>
       <c r="P158" s="1"/>
-      <c r="Q158" s="4"/>
+      <c r="Q158" s="6"/>
       <c r="R158" s="1"/>
     </row>
     <row r="159" ht="12.75">
@@ -4280,7 +4282,7 @@
       <c r="E159" s="1"/>
       <c r="F159" s="1"/>
       <c r="G159" s="1"/>
-      <c r="H159" s="3"/>
+      <c r="H159" s="5"/>
       <c r="I159" s="1"/>
       <c r="J159" s="1"/>
       <c r="K159" s="1"/>
@@ -4289,7 +4291,7 @@
       <c r="N159" s="1"/>
       <c r="O159" s="1"/>
       <c r="P159" s="1"/>
-      <c r="Q159" s="4"/>
+      <c r="Q159" s="6"/>
       <c r="R159" s="1"/>
     </row>
     <row r="160" ht="12.75">
@@ -4302,7 +4304,7 @@
       <c r="E160" s="1"/>
       <c r="F160" s="1"/>
       <c r="G160" s="1"/>
-      <c r="H160" s="3"/>
+      <c r="H160" s="5"/>
       <c r="I160" s="1"/>
       <c r="J160" s="1"/>
       <c r="K160" s="1"/>
@@ -4311,7 +4313,7 @@
       <c r="N160" s="1"/>
       <c r="O160" s="1"/>
       <c r="P160" s="1"/>
-      <c r="Q160" s="4"/>
+      <c r="Q160" s="6"/>
       <c r="R160" s="1"/>
     </row>
     <row r="161" ht="12.75">
@@ -4324,7 +4326,7 @@
       <c r="E161" s="1"/>
       <c r="F161" s="1"/>
       <c r="G161" s="1"/>
-      <c r="H161" s="3"/>
+      <c r="H161" s="5"/>
       <c r="I161" s="1"/>
       <c r="J161" s="1"/>
       <c r="K161" s="1"/>
@@ -4333,7 +4335,7 @@
       <c r="N161" s="1"/>
       <c r="O161" s="1"/>
       <c r="P161" s="1"/>
-      <c r="Q161" s="4"/>
+      <c r="Q161" s="6"/>
       <c r="R161" s="1"/>
     </row>
     <row r="162" ht="12.75">
@@ -4346,7 +4348,7 @@
       <c r="E162" s="1"/>
       <c r="F162" s="1"/>
       <c r="G162" s="1"/>
-      <c r="H162" s="3"/>
+      <c r="H162" s="5"/>
       <c r="I162" s="1"/>
       <c r="J162" s="1"/>
       <c r="K162" s="1"/>
@@ -4355,7 +4357,7 @@
       <c r="N162" s="1"/>
       <c r="O162" s="1"/>
       <c r="P162" s="1"/>
-      <c r="Q162" s="4"/>
+      <c r="Q162" s="6"/>
       <c r="R162" s="1"/>
     </row>
     <row r="163" ht="12.75">
@@ -4368,7 +4370,7 @@
       <c r="E163" s="1"/>
       <c r="F163" s="1"/>
       <c r="G163" s="1"/>
-      <c r="H163" s="3"/>
+      <c r="H163" s="5"/>
       <c r="I163" s="1"/>
       <c r="J163" s="1"/>
       <c r="K163" s="1"/>
@@ -4377,7 +4379,7 @@
       <c r="N163" s="1"/>
       <c r="O163" s="1"/>
       <c r="P163" s="1"/>
-      <c r="Q163" s="4"/>
+      <c r="Q163" s="6"/>
       <c r="R163" s="1"/>
     </row>
     <row r="164" ht="12.75">
@@ -4390,7 +4392,7 @@
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
       <c r="G164" s="1"/>
-      <c r="H164" s="3"/>
+      <c r="H164" s="5"/>
       <c r="I164" s="1"/>
       <c r="J164" s="1"/>
       <c r="K164" s="1"/>
@@ -4399,7 +4401,7 @@
       <c r="N164" s="1"/>
       <c r="O164" s="1"/>
       <c r="P164" s="1"/>
-      <c r="Q164" s="4"/>
+      <c r="Q164" s="6"/>
       <c r="R164" s="1"/>
     </row>
     <row r="165" ht="12.75">
@@ -4412,16 +4414,16 @@
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
       <c r="G165" s="1"/>
-      <c r="H165" s="3"/>
+      <c r="H165" s="5"/>
       <c r="I165" s="1"/>
       <c r="J165" s="1"/>
-      <c r="K165" s="5"/>
+      <c r="K165" s="7"/>
       <c r="L165" s="1"/>
       <c r="M165" s="1"/>
       <c r="N165" s="1"/>
       <c r="O165" s="1"/>
       <c r="P165" s="1"/>
-      <c r="Q165" s="4"/>
+      <c r="Q165" s="6"/>
       <c r="R165" s="1"/>
     </row>
     <row r="166" ht="12.75">
@@ -4434,7 +4436,7 @@
       <c r="E166" s="1"/>
       <c r="F166" s="1"/>
       <c r="G166" s="1"/>
-      <c r="H166" s="3"/>
+      <c r="H166" s="5"/>
       <c r="I166" s="1"/>
       <c r="J166" s="1"/>
       <c r="K166" s="1"/>
@@ -4443,7 +4445,7 @@
       <c r="N166" s="1"/>
       <c r="O166" s="1"/>
       <c r="P166" s="1"/>
-      <c r="Q166" s="4"/>
+      <c r="Q166" s="6"/>
       <c r="R166" s="1"/>
     </row>
     <row r="167" ht="12.75">
@@ -4456,7 +4458,7 @@
       <c r="E167" s="1"/>
       <c r="F167" s="1"/>
       <c r="G167" s="1"/>
-      <c r="H167" s="3"/>
+      <c r="H167" s="5"/>
       <c r="I167" s="1"/>
       <c r="J167" s="1"/>
       <c r="K167" s="1"/>
@@ -4465,7 +4467,7 @@
       <c r="N167" s="1"/>
       <c r="O167" s="1"/>
       <c r="P167" s="1"/>
-      <c r="Q167" s="4"/>
+      <c r="Q167" s="6"/>
       <c r="R167" s="1"/>
     </row>
     <row r="168" ht="12.75">
@@ -4478,16 +4480,16 @@
       <c r="E168" s="1"/>
       <c r="F168" s="1"/>
       <c r="G168" s="1"/>
-      <c r="H168" s="3"/>
+      <c r="H168" s="5"/>
       <c r="I168" s="1"/>
       <c r="J168" s="1"/>
-      <c r="K168" s="5"/>
+      <c r="K168" s="7"/>
       <c r="L168" s="1"/>
       <c r="M168" s="1"/>
       <c r="N168" s="1"/>
       <c r="O168" s="1"/>
       <c r="P168" s="1"/>
-      <c r="Q168" s="4"/>
+      <c r="Q168" s="6"/>
       <c r="R168" s="1"/>
     </row>
     <row r="169" ht="12.75">
@@ -4500,16 +4502,16 @@
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
       <c r="G169" s="1"/>
-      <c r="H169" s="3"/>
+      <c r="H169" s="5"/>
       <c r="I169" s="1"/>
       <c r="J169" s="1"/>
-      <c r="K169" s="5"/>
+      <c r="K169" s="7"/>
       <c r="L169" s="1"/>
       <c r="M169" s="1"/>
       <c r="N169" s="1"/>
       <c r="O169" s="1"/>
       <c r="P169" s="1"/>
-      <c r="Q169" s="4"/>
+      <c r="Q169" s="6"/>
       <c r="R169" s="1"/>
     </row>
     <row r="170" ht="12.75">
@@ -4522,7 +4524,7 @@
       <c r="E170" s="1"/>
       <c r="F170" s="1"/>
       <c r="G170" s="1"/>
-      <c r="H170" s="3"/>
+      <c r="H170" s="5"/>
       <c r="I170" s="1"/>
       <c r="J170" s="1"/>
       <c r="K170" s="1"/>
@@ -4531,7 +4533,7 @@
       <c r="N170" s="1"/>
       <c r="O170" s="1"/>
       <c r="P170" s="1"/>
-      <c r="Q170" s="4"/>
+      <c r="Q170" s="6"/>
       <c r="R170" s="1"/>
     </row>
     <row r="171" ht="12.75">
@@ -4544,7 +4546,7 @@
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
       <c r="G171" s="1"/>
-      <c r="H171" s="3"/>
+      <c r="H171" s="5"/>
       <c r="I171" s="1"/>
       <c r="J171" s="1"/>
       <c r="K171" s="1"/>
@@ -4553,7 +4555,7 @@
       <c r="N171" s="1"/>
       <c r="O171" s="1"/>
       <c r="P171" s="1"/>
-      <c r="Q171" s="4"/>
+      <c r="Q171" s="6"/>
       <c r="R171" s="1"/>
     </row>
     <row r="172" ht="12.75">
@@ -4566,16 +4568,16 @@
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
       <c r="G172" s="1"/>
-      <c r="H172" s="3"/>
+      <c r="H172" s="5"/>
       <c r="I172" s="1"/>
       <c r="J172" s="1"/>
-      <c r="K172" s="5"/>
+      <c r="K172" s="7"/>
       <c r="L172" s="1"/>
       <c r="M172" s="1"/>
       <c r="N172" s="1"/>
       <c r="O172" s="1"/>
       <c r="P172" s="1"/>
-      <c r="Q172" s="4"/>
+      <c r="Q172" s="6"/>
       <c r="R172" s="1"/>
     </row>
     <row r="173" ht="12.75">
@@ -4588,7 +4590,7 @@
       <c r="E173" s="1"/>
       <c r="F173" s="1"/>
       <c r="G173" s="1"/>
-      <c r="H173" s="3"/>
+      <c r="H173" s="5"/>
       <c r="I173" s="1"/>
       <c r="J173" s="1"/>
       <c r="K173" s="1"/>
@@ -4597,7 +4599,7 @@
       <c r="N173" s="1"/>
       <c r="O173" s="1"/>
       <c r="P173" s="1"/>
-      <c r="Q173" s="4"/>
+      <c r="Q173" s="6"/>
       <c r="R173" s="1"/>
     </row>
     <row r="174" ht="12.75">
@@ -4610,7 +4612,7 @@
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
       <c r="G174" s="1"/>
-      <c r="H174" s="3"/>
+      <c r="H174" s="5"/>
       <c r="I174" s="1"/>
       <c r="J174" s="1"/>
       <c r="K174" s="1"/>
@@ -4619,7 +4621,7 @@
       <c r="N174" s="1"/>
       <c r="O174" s="1"/>
       <c r="P174" s="1"/>
-      <c r="Q174" s="4"/>
+      <c r="Q174" s="6"/>
       <c r="R174" s="1"/>
     </row>
     <row r="175" ht="12.75">
@@ -4632,7 +4634,7 @@
       <c r="E175" s="1"/>
       <c r="F175" s="1"/>
       <c r="G175" s="1"/>
-      <c r="H175" s="3"/>
+      <c r="H175" s="5"/>
       <c r="I175" s="1"/>
       <c r="J175" s="1"/>
       <c r="K175" s="1"/>
@@ -4641,7 +4643,7 @@
       <c r="N175" s="1"/>
       <c r="O175" s="1"/>
       <c r="P175" s="1"/>
-      <c r="Q175" s="4"/>
+      <c r="Q175" s="6"/>
       <c r="R175" s="1"/>
     </row>
     <row r="176" ht="12.75">
@@ -4654,16 +4656,16 @@
       <c r="E176" s="1"/>
       <c r="F176" s="1"/>
       <c r="G176" s="1"/>
-      <c r="H176" s="3"/>
+      <c r="H176" s="5"/>
       <c r="I176" s="1"/>
       <c r="J176" s="1"/>
-      <c r="K176" s="5"/>
+      <c r="K176" s="7"/>
       <c r="L176" s="1"/>
       <c r="M176" s="1"/>
       <c r="N176" s="1"/>
       <c r="O176" s="1"/>
       <c r="P176" s="1"/>
-      <c r="Q176" s="4"/>
+      <c r="Q176" s="6"/>
       <c r="R176" s="1"/>
     </row>
     <row r="177" ht="12.75">
@@ -4676,7 +4678,7 @@
       <c r="E177" s="1"/>
       <c r="F177" s="1"/>
       <c r="G177" s="1"/>
-      <c r="H177" s="3"/>
+      <c r="H177" s="5"/>
       <c r="I177" s="1"/>
       <c r="J177" s="1"/>
       <c r="K177" s="1"/>
@@ -4685,7 +4687,7 @@
       <c r="N177" s="1"/>
       <c r="O177" s="1"/>
       <c r="P177" s="1"/>
-      <c r="Q177" s="4"/>
+      <c r="Q177" s="6"/>
       <c r="R177" s="1"/>
     </row>
     <row r="178" ht="12.75">
@@ -4698,7 +4700,7 @@
       <c r="E178" s="1"/>
       <c r="F178" s="1"/>
       <c r="G178" s="1"/>
-      <c r="H178" s="3"/>
+      <c r="H178" s="5"/>
       <c r="I178" s="1"/>
       <c r="J178" s="1"/>
       <c r="K178" s="1"/>
@@ -4707,7 +4709,7 @@
       <c r="N178" s="1"/>
       <c r="O178" s="1"/>
       <c r="P178" s="1"/>
-      <c r="Q178" s="4"/>
+      <c r="Q178" s="6"/>
       <c r="R178" s="1"/>
     </row>
     <row r="179" ht="12.75">
@@ -4720,7 +4722,7 @@
       <c r="E179" s="1"/>
       <c r="F179" s="1"/>
       <c r="G179" s="1"/>
-      <c r="H179" s="3"/>
+      <c r="H179" s="5"/>
       <c r="I179" s="1"/>
       <c r="J179" s="1"/>
       <c r="K179" s="1"/>
@@ -4729,7 +4731,7 @@
       <c r="N179" s="1"/>
       <c r="O179" s="1"/>
       <c r="P179" s="1"/>
-      <c r="Q179" s="4"/>
+      <c r="Q179" s="6"/>
       <c r="R179" s="1"/>
     </row>
     <row r="180" ht="12.75">
@@ -4742,7 +4744,7 @@
       <c r="E180" s="1"/>
       <c r="F180" s="1"/>
       <c r="G180" s="1"/>
-      <c r="H180" s="3"/>
+      <c r="H180" s="5"/>
       <c r="I180" s="1"/>
       <c r="J180" s="1"/>
       <c r="K180" s="1"/>
@@ -4751,7 +4753,7 @@
       <c r="N180" s="1"/>
       <c r="O180" s="1"/>
       <c r="P180" s="1"/>
-      <c r="Q180" s="4"/>
+      <c r="Q180" s="6"/>
       <c r="R180" s="1"/>
     </row>
     <row r="181" ht="12.75">
@@ -4764,7 +4766,7 @@
       <c r="E181" s="1"/>
       <c r="F181" s="1"/>
       <c r="G181" s="1"/>
-      <c r="H181" s="3"/>
+      <c r="H181" s="5"/>
       <c r="I181" s="1"/>
       <c r="J181" s="1"/>
       <c r="K181" s="1"/>
@@ -4773,7 +4775,7 @@
       <c r="N181" s="1"/>
       <c r="O181" s="1"/>
       <c r="P181" s="1"/>
-      <c r="Q181" s="4"/>
+      <c r="Q181" s="6"/>
       <c r="R181" s="1"/>
     </row>
     <row r="182" ht="12.75">
@@ -4786,7 +4788,7 @@
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
       <c r="G182" s="1"/>
-      <c r="H182" s="3"/>
+      <c r="H182" s="5"/>
       <c r="I182" s="1"/>
       <c r="J182" s="1"/>
       <c r="K182" s="1"/>
@@ -4795,7 +4797,7 @@
       <c r="N182" s="1"/>
       <c r="O182" s="1"/>
       <c r="P182" s="1"/>
-      <c r="Q182" s="4"/>
+      <c r="Q182" s="6"/>
       <c r="R182" s="1"/>
     </row>
     <row r="183" ht="12.75">
@@ -4808,7 +4810,7 @@
       <c r="E183" s="1"/>
       <c r="F183" s="1"/>
       <c r="G183" s="1"/>
-      <c r="H183" s="3"/>
+      <c r="H183" s="5"/>
       <c r="I183" s="1"/>
       <c r="J183" s="1"/>
       <c r="K183" s="1"/>
@@ -4817,7 +4819,7 @@
       <c r="N183" s="1"/>
       <c r="O183" s="1"/>
       <c r="P183" s="1"/>
-      <c r="Q183" s="4"/>
+      <c r="Q183" s="6"/>
       <c r="R183" s="1"/>
     </row>
     <row r="184" ht="12.75">
@@ -4830,7 +4832,7 @@
       <c r="E184" s="1"/>
       <c r="F184" s="1"/>
       <c r="G184" s="1"/>
-      <c r="H184" s="3"/>
+      <c r="H184" s="5"/>
       <c r="I184" s="1"/>
       <c r="J184" s="1"/>
       <c r="K184" s="1"/>
@@ -4839,7 +4841,7 @@
       <c r="N184" s="1"/>
       <c r="O184" s="1"/>
       <c r="P184" s="1"/>
-      <c r="Q184" s="4"/>
+      <c r="Q184" s="6"/>
       <c r="R184" s="1"/>
     </row>
     <row r="185" ht="12.75">
@@ -4852,7 +4854,7 @@
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
       <c r="G185" s="1"/>
-      <c r="H185" s="3"/>
+      <c r="H185" s="5"/>
       <c r="I185" s="1"/>
       <c r="J185" s="1"/>
       <c r="K185" s="1"/>
@@ -4861,7 +4863,7 @@
       <c r="N185" s="1"/>
       <c r="O185" s="1"/>
       <c r="P185" s="1"/>
-      <c r="Q185" s="4"/>
+      <c r="Q185" s="6"/>
       <c r="R185" s="1"/>
     </row>
     <row r="186" ht="12.75">
@@ -4874,7 +4876,7 @@
       <c r="E186" s="1"/>
       <c r="F186" s="1"/>
       <c r="G186" s="1"/>
-      <c r="H186" s="3"/>
+      <c r="H186" s="5"/>
       <c r="I186" s="1"/>
       <c r="J186" s="1"/>
       <c r="K186" s="1"/>
@@ -4883,7 +4885,7 @@
       <c r="N186" s="1"/>
       <c r="O186" s="1"/>
       <c r="P186" s="1"/>
-      <c r="Q186" s="4"/>
+      <c r="Q186" s="6"/>
       <c r="R186" s="1"/>
     </row>
     <row r="187" ht="12.75">
@@ -4896,7 +4898,7 @@
       <c r="E187" s="1"/>
       <c r="F187" s="1"/>
       <c r="G187" s="1"/>
-      <c r="H187" s="3"/>
+      <c r="H187" s="5"/>
       <c r="I187" s="1"/>
       <c r="J187" s="1"/>
       <c r="K187" s="1"/>
@@ -4905,7 +4907,7 @@
       <c r="N187" s="1"/>
       <c r="O187" s="1"/>
       <c r="P187" s="1"/>
-      <c r="Q187" s="4"/>
+      <c r="Q187" s="6"/>
       <c r="R187" s="1"/>
     </row>
     <row r="188" ht="12.75">
@@ -4918,7 +4920,7 @@
       <c r="E188" s="1"/>
       <c r="F188" s="1"/>
       <c r="G188" s="1"/>
-      <c r="H188" s="3"/>
+      <c r="H188" s="5"/>
       <c r="I188" s="1"/>
       <c r="J188" s="1"/>
       <c r="K188" s="1"/>
@@ -4927,7 +4929,7 @@
       <c r="N188" s="1"/>
       <c r="O188" s="1"/>
       <c r="P188" s="1"/>
-      <c r="Q188" s="4"/>
+      <c r="Q188" s="6"/>
       <c r="R188" s="1"/>
     </row>
     <row r="189" ht="12.75">
@@ -4940,7 +4942,7 @@
       <c r="E189" s="1"/>
       <c r="F189" s="1"/>
       <c r="G189" s="1"/>
-      <c r="H189" s="3"/>
+      <c r="H189" s="5"/>
       <c r="I189" s="1"/>
       <c r="J189" s="1"/>
       <c r="K189" s="1"/>
@@ -4949,7 +4951,7 @@
       <c r="N189" s="1"/>
       <c r="O189" s="1"/>
       <c r="P189" s="1"/>
-      <c r="Q189" s="4"/>
+      <c r="Q189" s="6"/>
       <c r="R189" s="1"/>
     </row>
     <row r="190" ht="12.75">
@@ -4962,7 +4964,7 @@
       <c r="E190" s="1"/>
       <c r="F190" s="1"/>
       <c r="G190" s="1"/>
-      <c r="H190" s="3"/>
+      <c r="H190" s="5"/>
       <c r="I190" s="1"/>
       <c r="J190" s="1"/>
       <c r="K190" s="1"/>
@@ -4971,7 +4973,7 @@
       <c r="N190" s="1"/>
       <c r="O190" s="1"/>
       <c r="P190" s="1"/>
-      <c r="Q190" s="4"/>
+      <c r="Q190" s="6"/>
       <c r="R190" s="1"/>
     </row>
     <row r="191" ht="12.75">
@@ -4984,7 +4986,7 @@
       <c r="E191" s="1"/>
       <c r="F191" s="1"/>
       <c r="G191" s="1"/>
-      <c r="H191" s="3"/>
+      <c r="H191" s="5"/>
       <c r="I191" s="1"/>
       <c r="J191" s="1"/>
       <c r="K191" s="1"/>
@@ -4993,7 +4995,7 @@
       <c r="N191" s="1"/>
       <c r="O191" s="1"/>
       <c r="P191" s="1"/>
-      <c r="Q191" s="4"/>
+      <c r="Q191" s="6"/>
       <c r="R191" s="1"/>
     </row>
     <row r="192" ht="12.75">
@@ -5006,7 +5008,7 @@
       <c r="E192" s="1"/>
       <c r="F192" s="1"/>
       <c r="G192" s="1"/>
-      <c r="H192" s="3"/>
+      <c r="H192" s="5"/>
       <c r="I192" s="1"/>
       <c r="J192" s="1"/>
       <c r="K192" s="1"/>
@@ -5015,7 +5017,7 @@
       <c r="N192" s="1"/>
       <c r="O192" s="1"/>
       <c r="P192" s="1"/>
-      <c r="Q192" s="4"/>
+      <c r="Q192" s="6"/>
       <c r="R192" s="1"/>
     </row>
     <row r="193" ht="12.75">
@@ -5028,7 +5030,7 @@
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
       <c r="G193" s="1"/>
-      <c r="H193" s="3"/>
+      <c r="H193" s="5"/>
       <c r="I193" s="1"/>
       <c r="J193" s="1"/>
       <c r="K193" s="1"/>
@@ -5037,7 +5039,7 @@
       <c r="N193" s="1"/>
       <c r="O193" s="1"/>
       <c r="P193" s="1"/>
-      <c r="Q193" s="4"/>
+      <c r="Q193" s="6"/>
       <c r="R193" s="1"/>
     </row>
     <row r="194" ht="12.75">
@@ -5050,7 +5052,7 @@
       <c r="E194" s="1"/>
       <c r="F194" s="1"/>
       <c r="G194" s="1"/>
-      <c r="H194" s="3"/>
+      <c r="H194" s="5"/>
       <c r="I194" s="1"/>
       <c r="J194" s="1"/>
       <c r="K194" s="1"/>
@@ -5059,7 +5061,7 @@
       <c r="N194" s="1"/>
       <c r="O194" s="1"/>
       <c r="P194" s="1"/>
-      <c r="Q194" s="4"/>
+      <c r="Q194" s="6"/>
       <c r="R194" s="1"/>
     </row>
     <row r="195" ht="12.75">
@@ -5072,16 +5074,16 @@
       <c r="E195" s="1"/>
       <c r="F195" s="1"/>
       <c r="G195" s="1"/>
-      <c r="H195" s="3"/>
+      <c r="H195" s="5"/>
       <c r="I195" s="1"/>
       <c r="J195" s="1"/>
-      <c r="K195" s="5"/>
+      <c r="K195" s="7"/>
       <c r="L195" s="1"/>
       <c r="M195" s="1"/>
       <c r="N195" s="1"/>
       <c r="O195" s="1"/>
       <c r="P195" s="1"/>
-      <c r="Q195" s="4"/>
+      <c r="Q195" s="6"/>
       <c r="R195" s="1"/>
     </row>
     <row r="196" ht="12.75">
@@ -5094,7 +5096,7 @@
       <c r="E196" s="1"/>
       <c r="F196" s="1"/>
       <c r="G196" s="1"/>
-      <c r="H196" s="3"/>
+      <c r="H196" s="5"/>
       <c r="I196" s="1"/>
       <c r="J196" s="1"/>
       <c r="K196" s="1"/>
@@ -5103,7 +5105,7 @@
       <c r="N196" s="1"/>
       <c r="O196" s="1"/>
       <c r="P196" s="1"/>
-      <c r="Q196" s="4"/>
+      <c r="Q196" s="6"/>
       <c r="R196" s="1"/>
     </row>
     <row r="197" ht="12.75">
@@ -5116,7 +5118,7 @@
       <c r="E197" s="1"/>
       <c r="F197" s="1"/>
       <c r="G197" s="1"/>
-      <c r="H197" s="3"/>
+      <c r="H197" s="5"/>
       <c r="I197" s="1"/>
       <c r="J197" s="1"/>
       <c r="K197" s="1"/>
@@ -5125,7 +5127,7 @@
       <c r="N197" s="1"/>
       <c r="O197" s="1"/>
       <c r="P197" s="1"/>
-      <c r="Q197" s="4"/>
+      <c r="Q197" s="6"/>
       <c r="R197" s="1"/>
     </row>
     <row r="198" ht="12.75">
@@ -5138,16 +5140,16 @@
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
       <c r="G198" s="1"/>
-      <c r="H198" s="3"/>
+      <c r="H198" s="5"/>
       <c r="I198" s="1"/>
       <c r="J198" s="1"/>
-      <c r="K198" s="5"/>
+      <c r="K198" s="7"/>
       <c r="L198" s="1"/>
       <c r="M198" s="1"/>
       <c r="N198" s="1"/>
       <c r="O198" s="1"/>
       <c r="P198" s="1"/>
-      <c r="Q198" s="4"/>
+      <c r="Q198" s="6"/>
       <c r="R198" s="1"/>
     </row>
     <row r="199" ht="12.75">
@@ -5160,7 +5162,7 @@
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
       <c r="G199" s="1"/>
-      <c r="H199" s="3"/>
+      <c r="H199" s="5"/>
       <c r="I199" s="1"/>
       <c r="J199" s="1"/>
       <c r="K199" s="1"/>
@@ -5169,7 +5171,7 @@
       <c r="N199" s="1"/>
       <c r="O199" s="1"/>
       <c r="P199" s="1"/>
-      <c r="Q199" s="4"/>
+      <c r="Q199" s="6"/>
       <c r="R199" s="1"/>
     </row>
     <row r="200" ht="12.75">
@@ -5182,7 +5184,7 @@
       <c r="E200" s="1"/>
       <c r="F200" s="1"/>
       <c r="G200" s="1"/>
-      <c r="H200" s="3"/>
+      <c r="H200" s="5"/>
       <c r="I200" s="1"/>
       <c r="J200" s="1"/>
       <c r="K200" s="1"/>
@@ -5191,7 +5193,7 @@
       <c r="N200" s="1"/>
       <c r="O200" s="1"/>
       <c r="P200" s="1"/>
-      <c r="Q200" s="4"/>
+      <c r="Q200" s="6"/>
       <c r="R200" s="1"/>
     </row>
     <row r="201" ht="12.75">
@@ -5204,7 +5206,7 @@
       <c r="E201" s="1"/>
       <c r="F201" s="1"/>
       <c r="G201" s="1"/>
-      <c r="H201" s="3"/>
+      <c r="H201" s="5"/>
       <c r="I201" s="1"/>
       <c r="J201" s="1"/>
       <c r="K201" s="1"/>
@@ -5213,7 +5215,7 @@
       <c r="N201" s="1"/>
       <c r="O201" s="1"/>
       <c r="P201" s="1"/>
-      <c r="Q201" s="4"/>
+      <c r="Q201" s="6"/>
       <c r="R201" s="1"/>
     </row>
     <row r="202" ht="12.75">
@@ -5226,7 +5228,7 @@
       <c r="E202" s="1"/>
       <c r="F202" s="1"/>
       <c r="G202" s="1"/>
-      <c r="H202" s="3"/>
+      <c r="H202" s="5"/>
       <c r="I202" s="1"/>
       <c r="J202" s="1"/>
       <c r="K202" s="1"/>
@@ -5235,7 +5237,7 @@
       <c r="N202" s="1"/>
       <c r="O202" s="1"/>
       <c r="P202" s="1"/>
-      <c r="Q202" s="4"/>
+      <c r="Q202" s="6"/>
       <c r="R202" s="1"/>
     </row>
     <row r="203" ht="12.75">
@@ -5248,7 +5250,7 @@
       <c r="E203" s="1"/>
       <c r="F203" s="1"/>
       <c r="G203" s="1"/>
-      <c r="H203" s="3"/>
+      <c r="H203" s="5"/>
       <c r="I203" s="1"/>
       <c r="J203" s="1"/>
       <c r="K203" s="1"/>
@@ -5257,7 +5259,7 @@
       <c r="N203" s="1"/>
       <c r="O203" s="1"/>
       <c r="P203" s="1"/>
-      <c r="Q203" s="4"/>
+      <c r="Q203" s="6"/>
       <c r="R203" s="1"/>
     </row>
     <row r="204" ht="12.75">
@@ -5270,7 +5272,7 @@
       <c r="E204" s="1"/>
       <c r="F204" s="1"/>
       <c r="G204" s="1"/>
-      <c r="H204" s="3"/>
+      <c r="H204" s="5"/>
       <c r="I204" s="1"/>
       <c r="J204" s="1"/>
       <c r="K204" s="1"/>
@@ -5279,7 +5281,7 @@
       <c r="N204" s="1"/>
       <c r="O204" s="1"/>
       <c r="P204" s="1"/>
-      <c r="Q204" s="4"/>
+      <c r="Q204" s="6"/>
       <c r="R204" s="1"/>
     </row>
     <row r="205" ht="12.75">
@@ -5292,7 +5294,7 @@
       <c r="E205" s="1"/>
       <c r="F205" s="1"/>
       <c r="G205" s="1"/>
-      <c r="H205" s="3"/>
+      <c r="H205" s="5"/>
       <c r="I205" s="1"/>
       <c r="J205" s="1"/>
       <c r="K205" s="1"/>
@@ -5301,7 +5303,7 @@
       <c r="N205" s="1"/>
       <c r="O205" s="1"/>
       <c r="P205" s="1"/>
-      <c r="Q205" s="4"/>
+      <c r="Q205" s="6"/>
       <c r="R205" s="1"/>
     </row>
     <row r="206" ht="12.75">
@@ -5314,16 +5316,16 @@
       <c r="E206" s="1"/>
       <c r="F206" s="1"/>
       <c r="G206" s="1"/>
-      <c r="H206" s="3"/>
+      <c r="H206" s="5"/>
       <c r="I206" s="1"/>
       <c r="J206" s="1"/>
-      <c r="K206" s="5"/>
-      <c r="L206" s="5"/>
+      <c r="K206" s="7"/>
+      <c r="L206" s="7"/>
       <c r="M206" s="1"/>
       <c r="N206" s="1"/>
       <c r="O206" s="1"/>
       <c r="P206" s="1"/>
-      <c r="Q206" s="4"/>
+      <c r="Q206" s="6"/>
       <c r="R206" s="1"/>
     </row>
     <row r="207" ht="12.75">
@@ -5336,16 +5338,16 @@
       <c r="E207" s="1"/>
       <c r="F207" s="1"/>
       <c r="G207" s="1"/>
-      <c r="H207" s="3"/>
+      <c r="H207" s="5"/>
       <c r="I207" s="1"/>
       <c r="J207" s="1"/>
-      <c r="K207" s="5"/>
-      <c r="L207" s="5"/>
+      <c r="K207" s="7"/>
+      <c r="L207" s="7"/>
       <c r="M207" s="1"/>
       <c r="N207" s="1"/>
       <c r="O207" s="1"/>
       <c r="P207" s="1"/>
-      <c r="Q207" s="4"/>
+      <c r="Q207" s="6"/>
       <c r="R207" s="1"/>
     </row>
     <row r="208" ht="12.75">
@@ -5358,7 +5360,7 @@
       <c r="E208" s="1"/>
       <c r="F208" s="1"/>
       <c r="G208" s="1"/>
-      <c r="H208" s="3"/>
+      <c r="H208" s="5"/>
       <c r="I208" s="1"/>
       <c r="J208" s="1"/>
       <c r="K208" s="1"/>
@@ -5367,7 +5369,7 @@
       <c r="N208" s="1"/>
       <c r="O208" s="1"/>
       <c r="P208" s="1"/>
-      <c r="Q208" s="4"/>
+      <c r="Q208" s="6"/>
       <c r="R208" s="1"/>
     </row>
     <row r="209" ht="12.75">
@@ -5380,7 +5382,7 @@
       <c r="E209" s="1"/>
       <c r="F209" s="1"/>
       <c r="G209" s="1"/>
-      <c r="H209" s="3"/>
+      <c r="H209" s="5"/>
       <c r="I209" s="1"/>
       <c r="J209" s="1"/>
       <c r="K209" s="1"/>
@@ -5389,7 +5391,7 @@
       <c r="N209" s="1"/>
       <c r="O209" s="1"/>
       <c r="P209" s="1"/>
-      <c r="Q209" s="4"/>
+      <c r="Q209" s="6"/>
       <c r="R209" s="1"/>
     </row>
     <row r="210" ht="12.75">
@@ -5402,7 +5404,7 @@
       <c r="E210" s="1"/>
       <c r="F210" s="1"/>
       <c r="G210" s="1"/>
-      <c r="H210" s="3"/>
+      <c r="H210" s="5"/>
       <c r="I210" s="1"/>
       <c r="J210" s="1"/>
       <c r="K210" s="1"/>
@@ -5411,7 +5413,7 @@
       <c r="N210" s="1"/>
       <c r="O210" s="1"/>
       <c r="P210" s="1"/>
-      <c r="Q210" s="4"/>
+      <c r="Q210" s="6"/>
       <c r="R210" s="1"/>
     </row>
     <row r="211" ht="12.75">
@@ -5424,7 +5426,7 @@
       <c r="E211" s="1"/>
       <c r="F211" s="1"/>
       <c r="G211" s="1"/>
-      <c r="H211" s="3"/>
+      <c r="H211" s="5"/>
       <c r="I211" s="1"/>
       <c r="J211" s="1"/>
       <c r="K211" s="1"/>
@@ -5433,7 +5435,7 @@
       <c r="N211" s="1"/>
       <c r="O211" s="1"/>
       <c r="P211" s="1"/>
-      <c r="Q211" s="4"/>
+      <c r="Q211" s="6"/>
       <c r="R211" s="1"/>
     </row>
     <row r="212" ht="12.75">
@@ -5446,7 +5448,7 @@
       <c r="E212" s="1"/>
       <c r="F212" s="1"/>
       <c r="G212" s="1"/>
-      <c r="H212" s="3"/>
+      <c r="H212" s="5"/>
       <c r="I212" s="1"/>
       <c r="J212" s="1"/>
       <c r="K212" s="1"/>
@@ -5455,7 +5457,7 @@
       <c r="N212" s="1"/>
       <c r="O212" s="1"/>
       <c r="P212" s="1"/>
-      <c r="Q212" s="4"/>
+      <c r="Q212" s="6"/>
       <c r="R212" s="1"/>
     </row>
     <row r="213" ht="12.75">
@@ -5468,7 +5470,7 @@
       <c r="E213" s="1"/>
       <c r="F213" s="1"/>
       <c r="G213" s="1"/>
-      <c r="H213" s="3"/>
+      <c r="H213" s="5"/>
       <c r="I213" s="1"/>
       <c r="J213" s="1"/>
       <c r="K213" s="1"/>
@@ -5477,7 +5479,7 @@
       <c r="N213" s="1"/>
       <c r="O213" s="1"/>
       <c r="P213" s="1"/>
-      <c r="Q213" s="4"/>
+      <c r="Q213" s="6"/>
       <c r="R213" s="1"/>
     </row>
     <row r="214" ht="12.75">
@@ -5490,7 +5492,7 @@
       <c r="E214" s="1"/>
       <c r="F214" s="1"/>
       <c r="G214" s="1"/>
-      <c r="H214" s="3"/>
+      <c r="H214" s="5"/>
       <c r="I214" s="1"/>
       <c r="J214" s="1"/>
       <c r="K214" s="1"/>
@@ -5499,7 +5501,7 @@
       <c r="N214" s="1"/>
       <c r="O214" s="1"/>
       <c r="P214" s="1"/>
-      <c r="Q214" s="4"/>
+      <c r="Q214" s="6"/>
       <c r="R214" s="1"/>
     </row>
     <row r="215" ht="12.75">
@@ -5512,7 +5514,7 @@
       <c r="E215" s="1"/>
       <c r="F215" s="1"/>
       <c r="G215" s="1"/>
-      <c r="H215" s="3"/>
+      <c r="H215" s="5"/>
       <c r="I215" s="1"/>
       <c r="J215" s="1"/>
       <c r="K215" s="1"/>
@@ -5521,7 +5523,7 @@
       <c r="N215" s="1"/>
       <c r="O215" s="1"/>
       <c r="P215" s="1"/>
-      <c r="Q215" s="4"/>
+      <c r="Q215" s="6"/>
       <c r="R215" s="1"/>
     </row>
     <row r="216" ht="12.75">
@@ -5534,7 +5536,7 @@
       <c r="E216" s="1"/>
       <c r="F216" s="1"/>
       <c r="G216" s="1"/>
-      <c r="H216" s="3"/>
+      <c r="H216" s="5"/>
       <c r="I216" s="1"/>
       <c r="J216" s="1"/>
       <c r="K216" s="1"/>
@@ -5543,7 +5545,7 @@
       <c r="N216" s="1"/>
       <c r="O216" s="1"/>
       <c r="P216" s="1"/>
-      <c r="Q216" s="4"/>
+      <c r="Q216" s="6"/>
       <c r="R216" s="1"/>
     </row>
     <row r="217" ht="12.75">
@@ -5556,7 +5558,7 @@
       <c r="E217" s="1"/>
       <c r="F217" s="1"/>
       <c r="G217" s="1"/>
-      <c r="H217" s="3"/>
+      <c r="H217" s="5"/>
       <c r="I217" s="1"/>
       <c r="J217" s="1"/>
       <c r="K217" s="1"/>
@@ -5565,7 +5567,7 @@
       <c r="N217" s="1"/>
       <c r="O217" s="1"/>
       <c r="P217" s="1"/>
-      <c r="Q217" s="4"/>
+      <c r="Q217" s="6"/>
       <c r="R217" s="1"/>
     </row>
     <row r="218" ht="12.75">
@@ -5578,16 +5580,16 @@
       <c r="E218" s="1"/>
       <c r="F218" s="1"/>
       <c r="G218" s="1"/>
-      <c r="H218" s="3"/>
+      <c r="H218" s="5"/>
       <c r="I218" s="1"/>
       <c r="J218" s="1"/>
-      <c r="K218" s="5"/>
+      <c r="K218" s="7"/>
       <c r="L218" s="1"/>
       <c r="M218" s="1"/>
       <c r="N218" s="1"/>
       <c r="O218" s="1"/>
       <c r="P218" s="1"/>
-      <c r="Q218" s="4"/>
+      <c r="Q218" s="6"/>
       <c r="R218" s="1"/>
     </row>
     <row r="219" ht="12.75">
@@ -5600,7 +5602,7 @@
       <c r="E219" s="1"/>
       <c r="F219" s="1"/>
       <c r="G219" s="1"/>
-      <c r="H219" s="3"/>
+      <c r="H219" s="5"/>
       <c r="I219" s="1"/>
       <c r="J219" s="1"/>
       <c r="K219" s="1"/>
@@ -5609,7 +5611,7 @@
       <c r="N219" s="1"/>
       <c r="O219" s="1"/>
       <c r="P219" s="1"/>
-      <c r="Q219" s="4"/>
+      <c r="Q219" s="6"/>
       <c r="R219" s="1"/>
     </row>
     <row r="220" ht="12.75">
@@ -5622,7 +5624,7 @@
       <c r="E220" s="1"/>
       <c r="F220" s="1"/>
       <c r="G220" s="1"/>
-      <c r="H220" s="3"/>
+      <c r="H220" s="5"/>
       <c r="I220" s="1"/>
       <c r="J220" s="1"/>
       <c r="K220" s="1"/>
@@ -5631,7 +5633,7 @@
       <c r="N220" s="1"/>
       <c r="O220" s="1"/>
       <c r="P220" s="1"/>
-      <c r="Q220" s="4"/>
+      <c r="Q220" s="6"/>
       <c r="R220" s="1"/>
     </row>
     <row r="221" ht="12.75">
@@ -5644,7 +5646,7 @@
       <c r="E221" s="1"/>
       <c r="F221" s="1"/>
       <c r="G221" s="1"/>
-      <c r="H221" s="3"/>
+      <c r="H221" s="5"/>
       <c r="I221" s="1"/>
       <c r="J221" s="1"/>
       <c r="K221" s="1"/>
@@ -5653,7 +5655,7 @@
       <c r="N221" s="1"/>
       <c r="O221" s="1"/>
       <c r="P221" s="1"/>
-      <c r="Q221" s="4"/>
+      <c r="Q221" s="6"/>
       <c r="R221" s="1"/>
     </row>
     <row r="222" ht="12.75">
@@ -5666,7 +5668,7 @@
       <c r="E222" s="1"/>
       <c r="F222" s="1"/>
       <c r="G222" s="1"/>
-      <c r="H222" s="3"/>
+      <c r="H222" s="5"/>
       <c r="I222" s="1"/>
       <c r="J222" s="1"/>
       <c r="K222" s="1"/>
@@ -5675,7 +5677,7 @@
       <c r="N222" s="1"/>
       <c r="O222" s="1"/>
       <c r="P222" s="1"/>
-      <c r="Q222" s="4"/>
+      <c r="Q222" s="6"/>
       <c r="R222" s="1"/>
     </row>
     <row r="223" ht="12.75">
@@ -5688,16 +5690,16 @@
       <c r="E223" s="1"/>
       <c r="F223" s="1"/>
       <c r="G223" s="1"/>
-      <c r="H223" s="3"/>
+      <c r="H223" s="5"/>
       <c r="I223" s="1"/>
       <c r="J223" s="1"/>
-      <c r="K223" s="5"/>
+      <c r="K223" s="7"/>
       <c r="L223" s="1"/>
       <c r="M223" s="1"/>
       <c r="N223" s="1"/>
       <c r="O223" s="1"/>
       <c r="P223" s="1"/>
-      <c r="Q223" s="4"/>
+      <c r="Q223" s="6"/>
       <c r="R223" s="1"/>
     </row>
     <row r="224" ht="12.75">
@@ -5710,7 +5712,7 @@
       <c r="E224" s="1"/>
       <c r="F224" s="1"/>
       <c r="G224" s="1"/>
-      <c r="H224" s="3"/>
+      <c r="H224" s="5"/>
       <c r="I224" s="1"/>
       <c r="J224" s="1"/>
       <c r="K224" s="1"/>
@@ -5719,7 +5721,7 @@
       <c r="N224" s="1"/>
       <c r="O224" s="1"/>
       <c r="P224" s="1"/>
-      <c r="Q224" s="4"/>
+      <c r="Q224" s="6"/>
       <c r="R224" s="1"/>
     </row>
     <row r="225" ht="12.75">
@@ -5732,7 +5734,7 @@
       <c r="E225" s="1"/>
       <c r="F225" s="1"/>
       <c r="G225" s="1"/>
-      <c r="H225" s="3"/>
+      <c r="H225" s="5"/>
       <c r="I225" s="1"/>
       <c r="J225" s="1"/>
       <c r="K225" s="1"/>
@@ -5741,7 +5743,7 @@
       <c r="N225" s="1"/>
       <c r="O225" s="1"/>
       <c r="P225" s="1"/>
-      <c r="Q225" s="4"/>
+      <c r="Q225" s="6"/>
       <c r="R225" s="1"/>
     </row>
     <row r="226" ht="12.75">
@@ -5754,7 +5756,7 @@
       <c r="E226" s="1"/>
       <c r="F226" s="1"/>
       <c r="G226" s="1"/>
-      <c r="H226" s="3"/>
+      <c r="H226" s="5"/>
       <c r="I226" s="1"/>
       <c r="J226" s="1"/>
       <c r="K226" s="1"/>
@@ -5763,7 +5765,7 @@
       <c r="N226" s="1"/>
       <c r="O226" s="1"/>
       <c r="P226" s="1"/>
-      <c r="Q226" s="4"/>
+      <c r="Q226" s="6"/>
       <c r="R226" s="1"/>
     </row>
     <row r="227" ht="12.75">
@@ -5776,7 +5778,7 @@
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
       <c r="G227" s="1"/>
-      <c r="H227" s="3"/>
+      <c r="H227" s="5"/>
       <c r="I227" s="1"/>
       <c r="J227" s="1"/>
       <c r="K227" s="1"/>
@@ -5785,7 +5787,7 @@
       <c r="N227" s="1"/>
       <c r="O227" s="1"/>
       <c r="P227" s="1"/>
-      <c r="Q227" s="4"/>
+      <c r="Q227" s="6"/>
       <c r="R227" s="1"/>
     </row>
     <row r="228" ht="12.75">
@@ -5798,7 +5800,7 @@
       <c r="E228" s="1"/>
       <c r="F228" s="1"/>
       <c r="G228" s="1"/>
-      <c r="H228" s="3"/>
+      <c r="H228" s="5"/>
       <c r="I228" s="1"/>
       <c r="J228" s="1"/>
       <c r="K228" s="1"/>
@@ -5807,7 +5809,7 @@
       <c r="N228" s="1"/>
       <c r="O228" s="1"/>
       <c r="P228" s="1"/>
-      <c r="Q228" s="4"/>
+      <c r="Q228" s="6"/>
       <c r="R228" s="1"/>
     </row>
     <row r="229" ht="12.75">
@@ -5820,7 +5822,7 @@
       <c r="E229" s="1"/>
       <c r="F229" s="1"/>
       <c r="G229" s="1"/>
-      <c r="H229" s="3"/>
+      <c r="H229" s="5"/>
       <c r="I229" s="1"/>
       <c r="J229" s="1"/>
       <c r="K229" s="1"/>
@@ -5829,7 +5831,7 @@
       <c r="N229" s="1"/>
       <c r="O229" s="1"/>
       <c r="P229" s="1"/>
-      <c r="Q229" s="4"/>
+      <c r="Q229" s="6"/>
       <c r="R229" s="1"/>
     </row>
     <row r="230" ht="12.75">
@@ -5842,7 +5844,7 @@
       <c r="E230" s="1"/>
       <c r="F230" s="1"/>
       <c r="G230" s="1"/>
-      <c r="H230" s="3"/>
+      <c r="H230" s="5"/>
       <c r="I230" s="1"/>
       <c r="J230" s="1"/>
       <c r="K230" s="1"/>
@@ -5851,7 +5853,7 @@
       <c r="N230" s="1"/>
       <c r="O230" s="1"/>
       <c r="P230" s="1"/>
-      <c r="Q230" s="4"/>
+      <c r="Q230" s="6"/>
       <c r="R230" s="1"/>
     </row>
     <row r="231" ht="12.75">
@@ -5864,16 +5866,16 @@
       <c r="E231" s="1"/>
       <c r="F231" s="1"/>
       <c r="G231" s="1"/>
-      <c r="H231" s="3"/>
+      <c r="H231" s="5"/>
       <c r="I231" s="1"/>
       <c r="J231" s="1"/>
-      <c r="K231" s="5"/>
+      <c r="K231" s="7"/>
       <c r="L231" s="1"/>
       <c r="M231" s="1"/>
       <c r="N231" s="1"/>
       <c r="O231" s="1"/>
       <c r="P231" s="1"/>
-      <c r="Q231" s="4"/>
+      <c r="Q231" s="6"/>
       <c r="R231" s="1"/>
     </row>
     <row r="232" ht="12.75">
@@ -5886,7 +5888,7 @@
       <c r="E232" s="1"/>
       <c r="F232" s="1"/>
       <c r="G232" s="1"/>
-      <c r="H232" s="3"/>
+      <c r="H232" s="5"/>
       <c r="I232" s="1"/>
       <c r="J232" s="1"/>
       <c r="K232" s="1"/>
@@ -5895,7 +5897,7 @@
       <c r="N232" s="1"/>
       <c r="O232" s="1"/>
       <c r="P232" s="1"/>
-      <c r="Q232" s="4"/>
+      <c r="Q232" s="6"/>
       <c r="R232" s="1"/>
     </row>
     <row r="233" ht="12.75">
@@ -5908,7 +5910,7 @@
       <c r="E233" s="1"/>
       <c r="F233" s="1"/>
       <c r="G233" s="1"/>
-      <c r="H233" s="3"/>
+      <c r="H233" s="5"/>
       <c r="I233" s="1"/>
       <c r="J233" s="1"/>
       <c r="K233" s="1"/>
@@ -5917,7 +5919,7 @@
       <c r="N233" s="1"/>
       <c r="O233" s="1"/>
       <c r="P233" s="1"/>
-      <c r="Q233" s="4"/>
+      <c r="Q233" s="6"/>
       <c r="R233" s="1"/>
     </row>
     <row r="234" ht="12.75">
@@ -5930,7 +5932,7 @@
       <c r="E234" s="1"/>
       <c r="F234" s="1"/>
       <c r="G234" s="1"/>
-      <c r="H234" s="3"/>
+      <c r="H234" s="5"/>
       <c r="I234" s="1"/>
       <c r="J234" s="1"/>
       <c r="K234" s="1"/>
@@ -5939,7 +5941,7 @@
       <c r="N234" s="1"/>
       <c r="O234" s="1"/>
       <c r="P234" s="1"/>
-      <c r="Q234" s="4"/>
+      <c r="Q234" s="6"/>
       <c r="R234" s="1"/>
     </row>
     <row r="235" ht="12.75">
@@ -5952,7 +5954,7 @@
       <c r="E235" s="1"/>
       <c r="F235" s="1"/>
       <c r="G235" s="1"/>
-      <c r="H235" s="3"/>
+      <c r="H235" s="5"/>
       <c r="I235" s="1"/>
       <c r="J235" s="1"/>
       <c r="K235" s="1"/>
@@ -5961,7 +5963,7 @@
       <c r="N235" s="1"/>
       <c r="O235" s="1"/>
       <c r="P235" s="1"/>
-      <c r="Q235" s="4"/>
+      <c r="Q235" s="6"/>
       <c r="R235" s="1"/>
     </row>
     <row r="236" ht="12.75">
@@ -5974,7 +5976,7 @@
       <c r="E236" s="1"/>
       <c r="F236" s="1"/>
       <c r="G236" s="1"/>
-      <c r="H236" s="3"/>
+      <c r="H236" s="5"/>
       <c r="I236" s="1"/>
       <c r="J236" s="1"/>
       <c r="K236" s="1"/>
@@ -5983,7 +5985,7 @@
       <c r="N236" s="1"/>
       <c r="O236" s="1"/>
       <c r="P236" s="1"/>
-      <c r="Q236" s="4"/>
+      <c r="Q236" s="6"/>
       <c r="R236" s="1"/>
     </row>
     <row r="237" ht="12.75">
@@ -5996,7 +5998,7 @@
       <c r="E237" s="1"/>
       <c r="F237" s="1"/>
       <c r="G237" s="1"/>
-      <c r="H237" s="3"/>
+      <c r="H237" s="5"/>
       <c r="I237" s="1"/>
       <c r="J237" s="1"/>
       <c r="K237" s="1"/>
@@ -6005,7 +6007,7 @@
       <c r="N237" s="1"/>
       <c r="O237" s="1"/>
       <c r="P237" s="1"/>
-      <c r="Q237" s="4"/>
+      <c r="Q237" s="6"/>
       <c r="R237" s="1"/>
     </row>
     <row r="238" ht="12.75">
@@ -6018,7 +6020,7 @@
       <c r="E238" s="1"/>
       <c r="F238" s="1"/>
       <c r="G238" s="1"/>
-      <c r="H238" s="3"/>
+      <c r="H238" s="5"/>
       <c r="I238" s="1"/>
       <c r="J238" s="1"/>
       <c r="K238" s="1"/>
@@ -6027,7 +6029,7 @@
       <c r="N238" s="1"/>
       <c r="O238" s="1"/>
       <c r="P238" s="1"/>
-      <c r="Q238" s="4"/>
+      <c r="Q238" s="6"/>
       <c r="R238" s="1"/>
     </row>
     <row r="239" ht="12.75">
@@ -6040,7 +6042,7 @@
       <c r="E239" s="1"/>
       <c r="F239" s="1"/>
       <c r="G239" s="1"/>
-      <c r="H239" s="3"/>
+      <c r="H239" s="5"/>
       <c r="I239" s="1"/>
       <c r="J239" s="1"/>
       <c r="K239" s="1"/>
@@ -6049,7 +6051,7 @@
       <c r="N239" s="1"/>
       <c r="O239" s="1"/>
       <c r="P239" s="1"/>
-      <c r="Q239" s="4"/>
+      <c r="Q239" s="6"/>
       <c r="R239" s="1"/>
     </row>
     <row r="240" ht="12.75">
@@ -6062,7 +6064,7 @@
       <c r="E240" s="1"/>
       <c r="F240" s="1"/>
       <c r="G240" s="1"/>
-      <c r="H240" s="3"/>
+      <c r="H240" s="5"/>
       <c r="I240" s="1"/>
       <c r="J240" s="1"/>
       <c r="K240" s="1"/>
@@ -6071,7 +6073,7 @@
       <c r="N240" s="1"/>
       <c r="O240" s="1"/>
       <c r="P240" s="1"/>
-      <c r="Q240" s="4"/>
+      <c r="Q240" s="6"/>
       <c r="R240" s="1"/>
     </row>
     <row r="241" ht="12.75">
@@ -6084,7 +6086,7 @@
       <c r="E241" s="1"/>
       <c r="F241" s="1"/>
       <c r="G241" s="1"/>
-      <c r="H241" s="3"/>
+      <c r="H241" s="5"/>
       <c r="I241" s="1"/>
       <c r="J241" s="1"/>
       <c r="K241" s="1"/>
@@ -6093,7 +6095,7 @@
       <c r="N241" s="1"/>
       <c r="O241" s="1"/>
       <c r="P241" s="1"/>
-      <c r="Q241" s="4"/>
+      <c r="Q241" s="6"/>
       <c r="R241" s="1"/>
     </row>
     <row r="242" ht="12.75">
@@ -6106,16 +6108,16 @@
       <c r="E242" s="1"/>
       <c r="F242" s="1"/>
       <c r="G242" s="1"/>
-      <c r="H242" s="3"/>
+      <c r="H242" s="5"/>
       <c r="I242" s="1"/>
       <c r="J242" s="1"/>
-      <c r="K242" s="5"/>
+      <c r="K242" s="7"/>
       <c r="L242" s="1"/>
       <c r="M242" s="1"/>
       <c r="N242" s="1"/>
       <c r="O242" s="1"/>
       <c r="P242" s="1"/>
-      <c r="Q242" s="4"/>
+      <c r="Q242" s="6"/>
       <c r="R242" s="1"/>
     </row>
     <row r="243" ht="12.75">
@@ -6128,7 +6130,7 @@
       <c r="E243" s="1"/>
       <c r="F243" s="1"/>
       <c r="G243" s="1"/>
-      <c r="H243" s="3"/>
+      <c r="H243" s="5"/>
       <c r="I243" s="1"/>
       <c r="J243" s="1"/>
       <c r="K243" s="1"/>
@@ -6137,7 +6139,7 @@
       <c r="N243" s="1"/>
       <c r="O243" s="1"/>
       <c r="P243" s="1"/>
-      <c r="Q243" s="4"/>
+      <c r="Q243" s="6"/>
       <c r="R243" s="1"/>
     </row>
     <row r="244" ht="12.75">
@@ -6150,7 +6152,7 @@
       <c r="E244" s="1"/>
       <c r="F244" s="1"/>
       <c r="G244" s="1"/>
-      <c r="H244" s="3"/>
+      <c r="H244" s="5"/>
       <c r="I244" s="1"/>
       <c r="J244" s="1"/>
       <c r="K244" s="1"/>
@@ -6159,7 +6161,7 @@
       <c r="N244" s="1"/>
       <c r="O244" s="1"/>
       <c r="P244" s="1"/>
-      <c r="Q244" s="4"/>
+      <c r="Q244" s="6"/>
       <c r="R244" s="1"/>
     </row>
     <row r="245" ht="12.75">
@@ -6172,7 +6174,7 @@
       <c r="E245" s="1"/>
       <c r="F245" s="1"/>
       <c r="G245" s="1"/>
-      <c r="H245" s="3"/>
+      <c r="H245" s="5"/>
       <c r="I245" s="1"/>
       <c r="J245" s="1"/>
       <c r="K245" s="1"/>
@@ -6181,7 +6183,7 @@
       <c r="N245" s="1"/>
       <c r="O245" s="1"/>
       <c r="P245" s="1"/>
-      <c r="Q245" s="4"/>
+      <c r="Q245" s="6"/>
       <c r="R245" s="1"/>
     </row>
     <row r="246" ht="12.75">
@@ -6194,7 +6196,7 @@
       <c r="E246" s="1"/>
       <c r="F246" s="1"/>
       <c r="G246" s="1"/>
-      <c r="H246" s="3"/>
+      <c r="H246" s="5"/>
       <c r="I246" s="1"/>
       <c r="J246" s="1"/>
       <c r="K246" s="1"/>
@@ -6203,7 +6205,7 @@
       <c r="N246" s="1"/>
       <c r="O246" s="1"/>
       <c r="P246" s="1"/>
-      <c r="Q246" s="4"/>
+      <c r="Q246" s="6"/>
       <c r="R246" s="1"/>
     </row>
     <row r="247" ht="12.75">
@@ -6216,16 +6218,16 @@
       <c r="E247" s="1"/>
       <c r="F247" s="1"/>
       <c r="G247" s="1"/>
-      <c r="H247" s="3"/>
+      <c r="H247" s="5"/>
       <c r="I247" s="1"/>
       <c r="J247" s="1"/>
-      <c r="K247" s="5"/>
+      <c r="K247" s="7"/>
       <c r="L247" s="1"/>
       <c r="M247" s="1"/>
       <c r="N247" s="1"/>
       <c r="O247" s="1"/>
       <c r="P247" s="1"/>
-      <c r="Q247" s="4"/>
+      <c r="Q247" s="6"/>
       <c r="R247" s="1"/>
     </row>
     <row r="248" ht="12.75">
@@ -6238,7 +6240,7 @@
       <c r="E248" s="1"/>
       <c r="F248" s="1"/>
       <c r="G248" s="1"/>
-      <c r="H248" s="3"/>
+      <c r="H248" s="5"/>
       <c r="I248" s="1"/>
       <c r="J248" s="1"/>
       <c r="K248" s="1"/>
@@ -6247,7 +6249,7 @@
       <c r="N248" s="1"/>
       <c r="O248" s="1"/>
       <c r="P248" s="1"/>
-      <c r="Q248" s="4"/>
+      <c r="Q248" s="6"/>
       <c r="R248" s="1"/>
     </row>
     <row r="249" ht="12.75">
@@ -6260,7 +6262,7 @@
       <c r="E249" s="1"/>
       <c r="F249" s="1"/>
       <c r="G249" s="1"/>
-      <c r="H249" s="3"/>
+      <c r="H249" s="5"/>
       <c r="I249" s="1"/>
       <c r="J249" s="1"/>
       <c r="K249" s="1"/>
@@ -6269,7 +6271,7 @@
       <c r="N249" s="1"/>
       <c r="O249" s="1"/>
       <c r="P249" s="1"/>
-      <c r="Q249" s="4"/>
+      <c r="Q249" s="6"/>
       <c r="R249" s="1"/>
     </row>
     <row r="250" ht="12.75">
@@ -6282,7 +6284,7 @@
       <c r="E250" s="1"/>
       <c r="F250" s="1"/>
       <c r="G250" s="1"/>
-      <c r="H250" s="3"/>
+      <c r="H250" s="5"/>
       <c r="I250" s="1"/>
       <c r="J250" s="1"/>
       <c r="K250" s="1"/>
@@ -6291,7 +6293,7 @@
       <c r="N250" s="1"/>
       <c r="O250" s="1"/>
       <c r="P250" s="1"/>
-      <c r="Q250" s="4"/>
+      <c r="Q250" s="6"/>
       <c r="R250" s="1"/>
     </row>
     <row r="251" ht="12.75">
@@ -6304,7 +6306,7 @@
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
       <c r="G251" s="1"/>
-      <c r="H251" s="3"/>
+      <c r="H251" s="5"/>
       <c r="I251" s="1"/>
       <c r="J251" s="1"/>
       <c r="K251" s="1"/>
@@ -6313,7 +6315,7 @@
       <c r="N251" s="1"/>
       <c r="O251" s="1"/>
       <c r="P251" s="1"/>
-      <c r="Q251" s="4"/>
+      <c r="Q251" s="6"/>
       <c r="R251" s="1"/>
     </row>
     <row r="252" ht="12.75">
@@ -6326,16 +6328,16 @@
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
       <c r="G252" s="1"/>
-      <c r="H252" s="3"/>
+      <c r="H252" s="5"/>
       <c r="I252" s="1"/>
       <c r="J252" s="1"/>
-      <c r="K252" s="5"/>
+      <c r="K252" s="7"/>
       <c r="L252" s="1"/>
       <c r="M252" s="1"/>
       <c r="N252" s="1"/>
       <c r="O252" s="1"/>
       <c r="P252" s="1"/>
-      <c r="Q252" s="4"/>
+      <c r="Q252" s="6"/>
       <c r="R252" s="1"/>
     </row>
     <row r="253" ht="12.75">
@@ -6348,7 +6350,7 @@
       <c r="E253" s="1"/>
       <c r="F253" s="1"/>
       <c r="G253" s="1"/>
-      <c r="H253" s="3"/>
+      <c r="H253" s="5"/>
       <c r="I253" s="1"/>
       <c r="J253" s="1"/>
       <c r="K253" s="1"/>
@@ -6357,7 +6359,7 @@
       <c r="N253" s="1"/>
       <c r="O253" s="1"/>
       <c r="P253" s="1"/>
-      <c r="Q253" s="4"/>
+      <c r="Q253" s="6"/>
       <c r="R253" s="1"/>
     </row>
     <row r="254" ht="12.75">
@@ -6370,7 +6372,7 @@
       <c r="E254" s="1"/>
       <c r="F254" s="1"/>
       <c r="G254" s="1"/>
-      <c r="H254" s="3"/>
+      <c r="H254" s="5"/>
       <c r="I254" s="1"/>
       <c r="J254" s="1"/>
       <c r="K254" s="1"/>
@@ -6379,7 +6381,7 @@
       <c r="N254" s="1"/>
       <c r="O254" s="1"/>
       <c r="P254" s="1"/>
-      <c r="Q254" s="4"/>
+      <c r="Q254" s="6"/>
       <c r="R254" s="1"/>
     </row>
     <row r="255" ht="12.75">
@@ -6392,7 +6394,7 @@
       <c r="E255" s="1"/>
       <c r="F255" s="1"/>
       <c r="G255" s="1"/>
-      <c r="H255" s="3"/>
+      <c r="H255" s="5"/>
       <c r="I255" s="1"/>
       <c r="J255" s="1"/>
       <c r="K255" s="1"/>
@@ -6401,7 +6403,7 @@
       <c r="N255" s="1"/>
       <c r="O255" s="1"/>
       <c r="P255" s="1"/>
-      <c r="Q255" s="4"/>
+      <c r="Q255" s="6"/>
       <c r="R255" s="1"/>
     </row>
     <row r="256" ht="12.75">
@@ -6414,7 +6416,7 @@
       <c r="E256" s="1"/>
       <c r="F256" s="1"/>
       <c r="G256" s="1"/>
-      <c r="H256" s="3"/>
+      <c r="H256" s="5"/>
       <c r="I256" s="1"/>
       <c r="J256" s="1"/>
       <c r="K256" s="1"/>
@@ -6423,7 +6425,7 @@
       <c r="N256" s="1"/>
       <c r="O256" s="1"/>
       <c r="P256" s="1"/>
-      <c r="Q256" s="4"/>
+      <c r="Q256" s="6"/>
       <c r="R256" s="1"/>
     </row>
     <row r="257" ht="12.75">
@@ -6436,7 +6438,7 @@
       <c r="E257" s="1"/>
       <c r="F257" s="1"/>
       <c r="G257" s="1"/>
-      <c r="H257" s="3"/>
+      <c r="H257" s="5"/>
       <c r="I257" s="1"/>
       <c r="J257" s="1"/>
       <c r="K257" s="1"/>
@@ -6445,7 +6447,7 @@
       <c r="N257" s="1"/>
       <c r="O257" s="1"/>
       <c r="P257" s="1"/>
-      <c r="Q257" s="4"/>
+      <c r="Q257" s="6"/>
       <c r="R257" s="1"/>
     </row>
     <row r="258" ht="12.75">
@@ -6458,7 +6460,7 @@
       <c r="E258" s="1"/>
       <c r="F258" s="1"/>
       <c r="G258" s="1"/>
-      <c r="H258" s="3"/>
+      <c r="H258" s="5"/>
       <c r="I258" s="1"/>
       <c r="J258" s="1"/>
       <c r="K258" s="1"/>
@@ -6467,7 +6469,7 @@
       <c r="N258" s="1"/>
       <c r="O258" s="1"/>
       <c r="P258" s="1"/>
-      <c r="Q258" s="4"/>
+      <c r="Q258" s="6"/>
       <c r="R258" s="1"/>
     </row>
     <row r="259" ht="12.75">
@@ -6480,7 +6482,7 @@
       <c r="E259" s="1"/>
       <c r="F259" s="1"/>
       <c r="G259" s="1"/>
-      <c r="H259" s="3"/>
+      <c r="H259" s="5"/>
       <c r="I259" s="1"/>
       <c r="J259" s="1"/>
       <c r="K259" s="1"/>
@@ -6489,7 +6491,7 @@
       <c r="N259" s="1"/>
       <c r="O259" s="1"/>
       <c r="P259" s="1"/>
-      <c r="Q259" s="4"/>
+      <c r="Q259" s="6"/>
       <c r="R259" s="1"/>
     </row>
     <row r="260" ht="12.75">
@@ -6502,7 +6504,7 @@
       <c r="E260" s="1"/>
       <c r="F260" s="1"/>
       <c r="G260" s="1"/>
-      <c r="H260" s="3"/>
+      <c r="H260" s="5"/>
       <c r="I260" s="1"/>
       <c r="J260" s="1"/>
       <c r="K260" s="1"/>
@@ -6511,7 +6513,7 @@
       <c r="N260" s="1"/>
       <c r="O260" s="1"/>
       <c r="P260" s="1"/>
-      <c r="Q260" s="4"/>
+      <c r="Q260" s="6"/>
       <c r="R260" s="1"/>
     </row>
     <row r="261" ht="12.75">
@@ -6524,7 +6526,7 @@
       <c r="E261" s="1"/>
       <c r="F261" s="1"/>
       <c r="G261" s="1"/>
-      <c r="H261" s="3"/>
+      <c r="H261" s="5"/>
       <c r="I261" s="1"/>
       <c r="J261" s="1"/>
       <c r="K261" s="1"/>
@@ -6533,7 +6535,7 @@
       <c r="N261" s="1"/>
       <c r="O261" s="1"/>
       <c r="P261" s="1"/>
-      <c r="Q261" s="4"/>
+      <c r="Q261" s="6"/>
       <c r="R261" s="1"/>
     </row>
     <row r="262" ht="12.75">
@@ -6546,7 +6548,7 @@
       <c r="E262" s="1"/>
       <c r="F262" s="1"/>
       <c r="G262" s="1"/>
-      <c r="H262" s="3"/>
+      <c r="H262" s="5"/>
       <c r="I262" s="1"/>
       <c r="J262" s="1"/>
       <c r="K262" s="1"/>
@@ -6555,7 +6557,7 @@
       <c r="N262" s="1"/>
       <c r="O262" s="1"/>
       <c r="P262" s="1"/>
-      <c r="Q262" s="4"/>
+      <c r="Q262" s="6"/>
       <c r="R262" s="1"/>
     </row>
     <row r="263" ht="12.75">
@@ -6568,16 +6570,16 @@
       <c r="E263" s="1"/>
       <c r="F263" s="1"/>
       <c r="G263" s="1"/>
-      <c r="H263" s="3"/>
+      <c r="H263" s="5"/>
       <c r="I263" s="1"/>
       <c r="J263" s="1"/>
-      <c r="K263" s="5"/>
+      <c r="K263" s="7"/>
       <c r="L263" s="1"/>
       <c r="M263" s="1"/>
       <c r="N263" s="1"/>
       <c r="O263" s="1"/>
       <c r="P263" s="1"/>
-      <c r="Q263" s="4"/>
+      <c r="Q263" s="6"/>
       <c r="R263" s="1"/>
     </row>
     <row r="264" ht="12.75">
@@ -6590,16 +6592,16 @@
       <c r="E264" s="1"/>
       <c r="F264" s="1"/>
       <c r="G264" s="1"/>
-      <c r="H264" s="3"/>
+      <c r="H264" s="5"/>
       <c r="I264" s="1"/>
       <c r="J264" s="1"/>
-      <c r="K264" s="5"/>
+      <c r="K264" s="7"/>
       <c r="L264" s="1"/>
       <c r="M264" s="1"/>
       <c r="N264" s="1"/>
       <c r="O264" s="1"/>
       <c r="P264" s="1"/>
-      <c r="Q264" s="4"/>
+      <c r="Q264" s="6"/>
       <c r="R264" s="1"/>
     </row>
     <row r="265" ht="12.75">
@@ -6612,16 +6614,16 @@
       <c r="E265" s="1"/>
       <c r="F265" s="1"/>
       <c r="G265" s="1"/>
-      <c r="H265" s="3"/>
+      <c r="H265" s="5"/>
       <c r="I265" s="1"/>
       <c r="J265" s="1"/>
-      <c r="K265" s="5"/>
+      <c r="K265" s="7"/>
       <c r="L265" s="1"/>
       <c r="M265" s="1"/>
       <c r="N265" s="1"/>
       <c r="O265" s="1"/>
       <c r="P265" s="1"/>
-      <c r="Q265" s="4"/>
+      <c r="Q265" s="6"/>
       <c r="R265" s="1"/>
     </row>
     <row r="266" ht="12.75">
@@ -6634,7 +6636,7 @@
       <c r="E266" s="1"/>
       <c r="F266" s="1"/>
       <c r="G266" s="1"/>
-      <c r="H266" s="3"/>
+      <c r="H266" s="5"/>
       <c r="I266" s="1"/>
       <c r="J266" s="1"/>
       <c r="K266" s="1"/>
@@ -6643,7 +6645,7 @@
       <c r="N266" s="1"/>
       <c r="O266" s="1"/>
       <c r="P266" s="1"/>
-      <c r="Q266" s="4"/>
+      <c r="Q266" s="6"/>
       <c r="R266" s="1"/>
     </row>
     <row r="267" ht="12.75">
@@ -6656,7 +6658,7 @@
       <c r="E267" s="1"/>
       <c r="F267" s="1"/>
       <c r="G267" s="1"/>
-      <c r="H267" s="3"/>
+      <c r="H267" s="5"/>
       <c r="I267" s="1"/>
       <c r="J267" s="1"/>
       <c r="K267" s="1"/>
@@ -6665,7 +6667,7 @@
       <c r="N267" s="1"/>
       <c r="O267" s="1"/>
       <c r="P267" s="1"/>
-      <c r="Q267" s="4"/>
+      <c r="Q267" s="6"/>
       <c r="R267" s="1"/>
     </row>
     <row r="268" ht="12.75">
@@ -6678,16 +6680,16 @@
       <c r="E268" s="1"/>
       <c r="F268" s="1"/>
       <c r="G268" s="1"/>
-      <c r="H268" s="3"/>
+      <c r="H268" s="5"/>
       <c r="I268" s="1"/>
       <c r="J268" s="1"/>
       <c r="K268" s="1"/>
-      <c r="L268" s="5"/>
+      <c r="L268" s="7"/>
       <c r="M268" s="1"/>
       <c r="N268" s="1"/>
       <c r="O268" s="1"/>
       <c r="P268" s="1"/>
-      <c r="Q268" s="4"/>
+      <c r="Q268" s="6"/>
       <c r="R268" s="1"/>
     </row>
     <row r="269" ht="12.75">
@@ -6700,7 +6702,7 @@
       <c r="E269" s="1"/>
       <c r="F269" s="1"/>
       <c r="G269" s="1"/>
-      <c r="H269" s="3"/>
+      <c r="H269" s="5"/>
       <c r="I269" s="1"/>
       <c r="J269" s="1"/>
       <c r="K269" s="1"/>
@@ -6709,7 +6711,7 @@
       <c r="N269" s="1"/>
       <c r="O269" s="1"/>
       <c r="P269" s="1"/>
-      <c r="Q269" s="4"/>
+      <c r="Q269" s="6"/>
       <c r="R269" s="1"/>
     </row>
     <row r="270" ht="12.75">
@@ -6722,7 +6724,7 @@
       <c r="E270" s="1"/>
       <c r="F270" s="1"/>
       <c r="G270" s="1"/>
-      <c r="H270" s="3"/>
+      <c r="H270" s="5"/>
       <c r="I270" s="1"/>
       <c r="J270" s="1"/>
       <c r="K270" s="1"/>
@@ -6731,7 +6733,7 @@
       <c r="N270" s="1"/>
       <c r="O270" s="1"/>
       <c r="P270" s="1"/>
-      <c r="Q270" s="4"/>
+      <c r="Q270" s="6"/>
       <c r="R270" s="1"/>
     </row>
     <row r="271" ht="12.75">
@@ -6744,7 +6746,7 @@
       <c r="E271" s="1"/>
       <c r="F271" s="1"/>
       <c r="G271" s="1"/>
-      <c r="H271" s="3"/>
+      <c r="H271" s="5"/>
       <c r="I271" s="1"/>
       <c r="J271" s="1"/>
       <c r="K271" s="1"/>
@@ -6753,7 +6755,7 @@
       <c r="N271" s="1"/>
       <c r="O271" s="1"/>
       <c r="P271" s="1"/>
-      <c r="Q271" s="4"/>
+      <c r="Q271" s="6"/>
       <c r="R271" s="1"/>
     </row>
     <row r="272" ht="12.75">
@@ -6766,7 +6768,7 @@
       <c r="E272" s="1"/>
       <c r="F272" s="1"/>
       <c r="G272" s="1"/>
-      <c r="H272" s="3"/>
+      <c r="H272" s="5"/>
       <c r="I272" s="1"/>
       <c r="J272" s="1"/>
       <c r="K272" s="1"/>
@@ -6775,7 +6777,7 @@
       <c r="N272" s="1"/>
       <c r="O272" s="1"/>
       <c r="P272" s="1"/>
-      <c r="Q272" s="4"/>
+      <c r="Q272" s="6"/>
       <c r="R272" s="1"/>
     </row>
     <row r="273" ht="12.75">
@@ -6788,7 +6790,7 @@
       <c r="E273" s="1"/>
       <c r="F273" s="1"/>
       <c r="G273" s="1"/>
-      <c r="H273" s="3"/>
+      <c r="H273" s="5"/>
       <c r="I273" s="1"/>
       <c r="J273" s="1"/>
       <c r="K273" s="1"/>
@@ -6797,7 +6799,7 @@
       <c r="N273" s="1"/>
       <c r="O273" s="1"/>
       <c r="P273" s="1"/>
-      <c r="Q273" s="4"/>
+      <c r="Q273" s="6"/>
       <c r="R273" s="1"/>
     </row>
     <row r="274" ht="12.75">
@@ -6810,7 +6812,7 @@
       <c r="E274" s="1"/>
       <c r="F274" s="1"/>
       <c r="G274" s="1"/>
-      <c r="H274" s="3"/>
+      <c r="H274" s="5"/>
       <c r="I274" s="1"/>
       <c r="J274" s="1"/>
       <c r="K274" s="1"/>
@@ -6819,7 +6821,7 @@
       <c r="N274" s="1"/>
       <c r="O274" s="1"/>
       <c r="P274" s="1"/>
-      <c r="Q274" s="4"/>
+      <c r="Q274" s="6"/>
       <c r="R274" s="1"/>
     </row>
     <row r="275" ht="12.75">
@@ -6832,7 +6834,7 @@
       <c r="E275" s="1"/>
       <c r="F275" s="1"/>
       <c r="G275" s="1"/>
-      <c r="H275" s="3"/>
+      <c r="H275" s="5"/>
       <c r="I275" s="1"/>
       <c r="J275" s="1"/>
       <c r="K275" s="1"/>
@@ -6841,7 +6843,7 @@
       <c r="N275" s="1"/>
       <c r="O275" s="1"/>
       <c r="P275" s="1"/>
-      <c r="Q275" s="4"/>
+      <c r="Q275" s="6"/>
       <c r="R275" s="1"/>
     </row>
     <row r="276" ht="12.75">
@@ -6854,16 +6856,16 @@
       <c r="E276" s="1"/>
       <c r="F276" s="1"/>
       <c r="G276" s="1"/>
-      <c r="H276" s="3"/>
+      <c r="H276" s="5"/>
       <c r="I276" s="1"/>
       <c r="J276" s="1"/>
       <c r="K276" s="1"/>
-      <c r="L276" s="5"/>
+      <c r="L276" s="7"/>
       <c r="M276" s="1"/>
       <c r="N276" s="1"/>
       <c r="O276" s="1"/>
       <c r="P276" s="1"/>
-      <c r="Q276" s="4"/>
+      <c r="Q276" s="6"/>
       <c r="R276" s="1"/>
     </row>
     <row r="277" ht="12.75">
@@ -6876,16 +6878,16 @@
       <c r="E277" s="1"/>
       <c r="F277" s="1"/>
       <c r="G277" s="1"/>
-      <c r="H277" s="3"/>
+      <c r="H277" s="5"/>
       <c r="I277" s="1"/>
       <c r="J277" s="1"/>
-      <c r="K277" s="5"/>
+      <c r="K277" s="7"/>
       <c r="L277" s="1"/>
       <c r="M277" s="1"/>
       <c r="N277" s="1"/>
       <c r="O277" s="1"/>
       <c r="P277" s="1"/>
-      <c r="Q277" s="4"/>
+      <c r="Q277" s="6"/>
       <c r="R277" s="1"/>
     </row>
     <row r="278" ht="12.75">
@@ -6898,7 +6900,7 @@
       <c r="E278" s="1"/>
       <c r="F278" s="1"/>
       <c r="G278" s="1"/>
-      <c r="H278" s="3"/>
+      <c r="H278" s="5"/>
       <c r="I278" s="1"/>
       <c r="J278" s="1"/>
       <c r="K278" s="1"/>
@@ -6907,7 +6909,7 @@
       <c r="N278" s="1"/>
       <c r="O278" s="1"/>
       <c r="P278" s="1"/>
-      <c r="Q278" s="4"/>
+      <c r="Q278" s="6"/>
       <c r="R278" s="1"/>
     </row>
     <row r="279" ht="12.75">
@@ -6920,7 +6922,7 @@
       <c r="E279" s="1"/>
       <c r="F279" s="1"/>
       <c r="G279" s="1"/>
-      <c r="H279" s="3"/>
+      <c r="H279" s="5"/>
       <c r="I279" s="1"/>
       <c r="J279" s="1"/>
       <c r="K279" s="1"/>
@@ -6929,7 +6931,7 @@
       <c r="N279" s="1"/>
       <c r="O279" s="1"/>
       <c r="P279" s="1"/>
-      <c r="Q279" s="4"/>
+      <c r="Q279" s="6"/>
       <c r="R279" s="1"/>
     </row>
     <row r="280" ht="12.75">
@@ -6942,7 +6944,7 @@
       <c r="E280" s="1"/>
       <c r="F280" s="1"/>
       <c r="G280" s="1"/>
-      <c r="H280" s="3"/>
+      <c r="H280" s="5"/>
       <c r="I280" s="1"/>
       <c r="J280" s="1"/>
       <c r="K280" s="1"/>
@@ -6951,7 +6953,7 @@
       <c r="N280" s="1"/>
       <c r="O280" s="1"/>
       <c r="P280" s="1"/>
-      <c r="Q280" s="4"/>
+      <c r="Q280" s="6"/>
       <c r="R280" s="1"/>
     </row>
     <row r="281" ht="12.75">
@@ -6964,7 +6966,7 @@
       <c r="E281" s="1"/>
       <c r="F281" s="1"/>
       <c r="G281" s="1"/>
-      <c r="H281" s="3"/>
+      <c r="H281" s="5"/>
       <c r="I281" s="1"/>
       <c r="J281" s="1"/>
       <c r="K281" s="1"/>
@@ -6973,7 +6975,7 @@
       <c r="N281" s="1"/>
       <c r="O281" s="1"/>
       <c r="P281" s="1"/>
-      <c r="Q281" s="4"/>
+      <c r="Q281" s="6"/>
       <c r="R281" s="1"/>
     </row>
     <row r="282" ht="12.75">
@@ -6986,7 +6988,7 @@
       <c r="E282" s="1"/>
       <c r="F282" s="1"/>
       <c r="G282" s="1"/>
-      <c r="H282" s="3"/>
+      <c r="H282" s="5"/>
       <c r="I282" s="1"/>
       <c r="J282" s="1"/>
       <c r="K282" s="1"/>
@@ -6995,7 +6997,7 @@
       <c r="N282" s="1"/>
       <c r="O282" s="1"/>
       <c r="P282" s="1"/>
-      <c r="Q282" s="4"/>
+      <c r="Q282" s="6"/>
       <c r="R282" s="1"/>
     </row>
     <row r="283" ht="12.75">
@@ -7008,7 +7010,7 @@
       <c r="E283" s="1"/>
       <c r="F283" s="1"/>
       <c r="G283" s="1"/>
-      <c r="H283" s="3"/>
+      <c r="H283" s="5"/>
       <c r="I283" s="1"/>
       <c r="J283" s="1"/>
       <c r="K283" s="1"/>
@@ -7017,7 +7019,7 @@
       <c r="N283" s="1"/>
       <c r="O283" s="1"/>
       <c r="P283" s="1"/>
-      <c r="Q283" s="4"/>
+      <c r="Q283" s="6"/>
       <c r="R283" s="1"/>
     </row>
     <row r="284" ht="12.75">
@@ -7030,7 +7032,7 @@
       <c r="E284" s="1"/>
       <c r="F284" s="1"/>
       <c r="G284" s="1"/>
-      <c r="H284" s="3"/>
+      <c r="H284" s="5"/>
       <c r="I284" s="1"/>
       <c r="J284" s="1"/>
       <c r="K284" s="1"/>
@@ -7039,7 +7041,7 @@
       <c r="N284" s="1"/>
       <c r="O284" s="1"/>
       <c r="P284" s="1"/>
-      <c r="Q284" s="4"/>
+      <c r="Q284" s="6"/>
       <c r="R284" s="1"/>
     </row>
     <row r="285" ht="12.75">
@@ -7052,7 +7054,7 @@
       <c r="E285" s="1"/>
       <c r="F285" s="1"/>
       <c r="G285" s="1"/>
-      <c r="H285" s="3"/>
+      <c r="H285" s="5"/>
       <c r="I285" s="1"/>
       <c r="J285" s="1"/>
       <c r="K285" s="1"/>
@@ -7061,7 +7063,7 @@
       <c r="N285" s="1"/>
       <c r="O285" s="1"/>
       <c r="P285" s="1"/>
-      <c r="Q285" s="4"/>
+      <c r="Q285" s="6"/>
       <c r="R285" s="1"/>
     </row>
     <row r="286" ht="12.75">
@@ -7074,16 +7076,16 @@
       <c r="E286" s="1"/>
       <c r="F286" s="1"/>
       <c r="G286" s="1"/>
-      <c r="H286" s="3"/>
+      <c r="H286" s="5"/>
       <c r="I286" s="1"/>
       <c r="J286" s="1"/>
-      <c r="K286" s="5"/>
+      <c r="K286" s="7"/>
       <c r="L286" s="1"/>
       <c r="M286" s="1"/>
       <c r="N286" s="1"/>
       <c r="O286" s="1"/>
       <c r="P286" s="1"/>
-      <c r="Q286" s="4"/>
+      <c r="Q286" s="6"/>
       <c r="R286" s="1"/>
     </row>
     <row r="287" ht="12.75">
@@ -7096,16 +7098,16 @@
       <c r="E287" s="1"/>
       <c r="F287" s="1"/>
       <c r="G287" s="1"/>
-      <c r="H287" s="3"/>
+      <c r="H287" s="5"/>
       <c r="I287" s="1"/>
       <c r="J287" s="1"/>
-      <c r="K287" s="5"/>
+      <c r="K287" s="7"/>
       <c r="L287" s="1"/>
       <c r="M287" s="1"/>
       <c r="N287" s="1"/>
       <c r="O287" s="1"/>
       <c r="P287" s="1"/>
-      <c r="Q287" s="4"/>
+      <c r="Q287" s="6"/>
       <c r="R287" s="1"/>
     </row>
     <row r="288" ht="12.75">
@@ -7118,7 +7120,7 @@
       <c r="E288" s="1"/>
       <c r="F288" s="1"/>
       <c r="G288" s="1"/>
-      <c r="H288" s="3"/>
+      <c r="H288" s="5"/>
       <c r="I288" s="1"/>
       <c r="J288" s="1"/>
       <c r="K288" s="1"/>
@@ -7127,7 +7129,7 @@
       <c r="N288" s="1"/>
       <c r="O288" s="1"/>
       <c r="P288" s="1"/>
-      <c r="Q288" s="4"/>
+      <c r="Q288" s="6"/>
       <c r="R288" s="1"/>
     </row>
     <row r="289" ht="12.75">
@@ -7140,16 +7142,16 @@
       <c r="E289" s="1"/>
       <c r="F289" s="1"/>
       <c r="G289" s="1"/>
-      <c r="H289" s="3"/>
+      <c r="H289" s="5"/>
       <c r="I289" s="1"/>
       <c r="J289" s="1"/>
-      <c r="K289" s="5"/>
+      <c r="K289" s="7"/>
       <c r="L289" s="1"/>
       <c r="M289" s="1"/>
       <c r="N289" s="1"/>
       <c r="O289" s="1"/>
       <c r="P289" s="1"/>
-      <c r="Q289" s="4"/>
+      <c r="Q289" s="6"/>
       <c r="R289" s="1"/>
     </row>
     <row r="290" ht="12.75">
@@ -7162,7 +7164,7 @@
       <c r="E290" s="1"/>
       <c r="F290" s="1"/>
       <c r="G290" s="1"/>
-      <c r="H290" s="3"/>
+      <c r="H290" s="5"/>
       <c r="I290" s="1"/>
       <c r="J290" s="1"/>
       <c r="K290" s="1"/>
@@ -7171,7 +7173,7 @@
       <c r="N290" s="1"/>
       <c r="O290" s="1"/>
       <c r="P290" s="1"/>
-      <c r="Q290" s="4"/>
+      <c r="Q290" s="6"/>
       <c r="R290" s="1"/>
     </row>
     <row r="291" ht="12.75">
@@ -7184,7 +7186,7 @@
       <c r="E291" s="1"/>
       <c r="F291" s="1"/>
       <c r="G291" s="1"/>
-      <c r="H291" s="3"/>
+      <c r="H291" s="5"/>
       <c r="I291" s="1"/>
       <c r="J291" s="1"/>
       <c r="K291" s="1"/>
@@ -7193,7 +7195,7 @@
       <c r="N291" s="1"/>
       <c r="O291" s="1"/>
       <c r="P291" s="1"/>
-      <c r="Q291" s="4"/>
+      <c r="Q291" s="6"/>
       <c r="R291" s="1"/>
     </row>
     <row r="292" ht="12.75">
@@ -7206,7 +7208,7 @@
       <c r="E292" s="1"/>
       <c r="F292" s="1"/>
       <c r="G292" s="1"/>
-      <c r="H292" s="3"/>
+      <c r="H292" s="5"/>
       <c r="I292" s="1"/>
       <c r="J292" s="1"/>
       <c r="K292" s="1"/>
@@ -7215,7 +7217,7 @@
       <c r="N292" s="1"/>
       <c r="O292" s="1"/>
       <c r="P292" s="1"/>
-      <c r="Q292" s="4"/>
+      <c r="Q292" s="6"/>
       <c r="R292" s="1"/>
     </row>
     <row r="293" ht="12.75">
@@ -7228,7 +7230,7 @@
       <c r="E293" s="1"/>
       <c r="F293" s="1"/>
       <c r="G293" s="1"/>
-      <c r="H293" s="3"/>
+      <c r="H293" s="5"/>
       <c r="I293" s="1"/>
       <c r="J293" s="1"/>
       <c r="K293" s="1"/>
@@ -7237,7 +7239,7 @@
       <c r="N293" s="1"/>
       <c r="O293" s="1"/>
       <c r="P293" s="1"/>
-      <c r="Q293" s="4"/>
+      <c r="Q293" s="6"/>
       <c r="R293" s="1"/>
     </row>
     <row r="294" ht="12.75">
@@ -7250,7 +7252,7 @@
       <c r="E294" s="1"/>
       <c r="F294" s="1"/>
       <c r="G294" s="1"/>
-      <c r="H294" s="3"/>
+      <c r="H294" s="5"/>
       <c r="I294" s="1"/>
       <c r="J294" s="1"/>
       <c r="K294" s="1"/>
@@ -7259,7 +7261,7 @@
       <c r="N294" s="1"/>
       <c r="O294" s="1"/>
       <c r="P294" s="1"/>
-      <c r="Q294" s="4"/>
+      <c r="Q294" s="6"/>
       <c r="R294" s="1"/>
     </row>
     <row r="295" ht="12.75">
@@ -7272,7 +7274,7 @@
       <c r="E295" s="1"/>
       <c r="F295" s="1"/>
       <c r="G295" s="1"/>
-      <c r="H295" s="3"/>
+      <c r="H295" s="5"/>
       <c r="I295" s="1"/>
       <c r="J295" s="1"/>
       <c r="K295" s="1"/>
@@ -7281,7 +7283,7 @@
       <c r="N295" s="1"/>
       <c r="O295" s="1"/>
       <c r="P295" s="1"/>
-      <c r="Q295" s="4"/>
+      <c r="Q295" s="6"/>
       <c r="R295" s="1"/>
     </row>
     <row r="296" ht="12.75">
@@ -7294,7 +7296,7 @@
       <c r="E296" s="1"/>
       <c r="F296" s="1"/>
       <c r="G296" s="1"/>
-      <c r="H296" s="3"/>
+      <c r="H296" s="5"/>
       <c r="I296" s="1"/>
       <c r="J296" s="1"/>
       <c r="K296" s="1"/>
@@ -7303,7 +7305,7 @@
       <c r="N296" s="1"/>
       <c r="O296" s="1"/>
       <c r="P296" s="1"/>
-      <c r="Q296" s="4"/>
+      <c r="Q296" s="6"/>
       <c r="R296" s="1"/>
     </row>
     <row r="297" ht="12.75">
@@ -7316,7 +7318,7 @@
       <c r="E297" s="1"/>
       <c r="F297" s="1"/>
       <c r="G297" s="1"/>
-      <c r="H297" s="3"/>
+      <c r="H297" s="5"/>
       <c r="I297" s="1"/>
       <c r="J297" s="1"/>
       <c r="K297" s="1"/>
@@ -7325,7 +7327,7 @@
       <c r="N297" s="1"/>
       <c r="O297" s="1"/>
       <c r="P297" s="1"/>
-      <c r="Q297" s="4"/>
+      <c r="Q297" s="6"/>
       <c r="R297" s="1"/>
     </row>
     <row r="298" ht="12.75">
@@ -7338,7 +7340,7 @@
       <c r="E298" s="1"/>
       <c r="F298" s="1"/>
       <c r="G298" s="1"/>
-      <c r="H298" s="3"/>
+      <c r="H298" s="5"/>
       <c r="I298" s="1"/>
       <c r="J298" s="1"/>
       <c r="K298" s="1"/>
@@ -7347,7 +7349,7 @@
       <c r="N298" s="1"/>
       <c r="O298" s="1"/>
       <c r="P298" s="1"/>
-      <c r="Q298" s="4"/>
+      <c r="Q298" s="6"/>
       <c r="R298" s="1"/>
     </row>
     <row r="299" ht="12.75">
@@ -7360,7 +7362,7 @@
       <c r="E299" s="1"/>
       <c r="F299" s="1"/>
       <c r="G299" s="1"/>
-      <c r="H299" s="3"/>
+      <c r="H299" s="5"/>
       <c r="I299" s="1"/>
       <c r="J299" s="1"/>
       <c r="K299" s="1"/>
@@ -7369,7 +7371,7 @@
       <c r="N299" s="1"/>
       <c r="O299" s="1"/>
       <c r="P299" s="1"/>
-      <c r="Q299" s="4"/>
+      <c r="Q299" s="6"/>
       <c r="R299" s="1"/>
     </row>
     <row r="300" ht="12.75">
@@ -7382,16 +7384,16 @@
       <c r="E300" s="1"/>
       <c r="F300" s="1"/>
       <c r="G300" s="1"/>
-      <c r="H300" s="3"/>
+      <c r="H300" s="5"/>
       <c r="I300" s="1"/>
       <c r="J300" s="1"/>
-      <c r="K300" s="5"/>
+      <c r="K300" s="7"/>
       <c r="L300" s="1"/>
       <c r="M300" s="1"/>
       <c r="N300" s="1"/>
       <c r="O300" s="1"/>
       <c r="P300" s="1"/>
-      <c r="Q300" s="4"/>
+      <c r="Q300" s="6"/>
       <c r="R300" s="1"/>
     </row>
     <row r="301" ht="12.75">
@@ -7404,7 +7406,7 @@
       <c r="E301" s="1"/>
       <c r="F301" s="1"/>
       <c r="G301" s="1"/>
-      <c r="H301" s="3"/>
+      <c r="H301" s="5"/>
       <c r="I301" s="1"/>
       <c r="J301" s="1"/>
       <c r="K301" s="1"/>
@@ -7413,7 +7415,7 @@
       <c r="N301" s="1"/>
       <c r="O301" s="1"/>
       <c r="P301" s="1"/>
-      <c r="Q301" s="4"/>
+      <c r="Q301" s="6"/>
       <c r="R301" s="1"/>
     </row>
     <row r="302" ht="12.75">
@@ -7426,7 +7428,7 @@
       <c r="E302" s="1"/>
       <c r="F302" s="1"/>
       <c r="G302" s="1"/>
-      <c r="H302" s="3"/>
+      <c r="H302" s="5"/>
       <c r="I302" s="1"/>
       <c r="J302" s="1"/>
       <c r="K302" s="1"/>
@@ -7435,7 +7437,7 @@
       <c r="N302" s="1"/>
       <c r="O302" s="1"/>
       <c r="P302" s="1"/>
-      <c r="Q302" s="4"/>
+      <c r="Q302" s="6"/>
       <c r="R302" s="1"/>
     </row>
     <row r="303" ht="12.75">
@@ -7448,16 +7450,16 @@
       <c r="E303" s="1"/>
       <c r="F303" s="1"/>
       <c r="G303" s="1"/>
-      <c r="H303" s="3"/>
+      <c r="H303" s="5"/>
       <c r="I303" s="1"/>
       <c r="J303" s="1"/>
-      <c r="K303" s="5"/>
+      <c r="K303" s="7"/>
       <c r="L303" s="1"/>
       <c r="M303" s="1"/>
       <c r="N303" s="1"/>
       <c r="O303" s="1"/>
       <c r="P303" s="1"/>
-      <c r="Q303" s="4"/>
+      <c r="Q303" s="6"/>
       <c r="R303" s="1"/>
     </row>
     <row r="304" ht="12.75">
@@ -7470,7 +7472,7 @@
       <c r="E304" s="1"/>
       <c r="F304" s="1"/>
       <c r="G304" s="1"/>
-      <c r="H304" s="3"/>
+      <c r="H304" s="5"/>
       <c r="I304" s="1"/>
       <c r="J304" s="1"/>
       <c r="K304" s="1"/>
@@ -7479,7 +7481,7 @@
       <c r="N304" s="1"/>
       <c r="O304" s="1"/>
       <c r="P304" s="1"/>
-      <c r="Q304" s="4"/>
+      <c r="Q304" s="6"/>
       <c r="R304" s="1"/>
     </row>
     <row r="305" ht="12.75">
@@ -7492,7 +7494,7 @@
       <c r="E305" s="1"/>
       <c r="F305" s="1"/>
       <c r="G305" s="1"/>
-      <c r="H305" s="3"/>
+      <c r="H305" s="5"/>
       <c r="I305" s="1"/>
       <c r="J305" s="1"/>
       <c r="K305" s="1"/>
@@ -7501,7 +7503,7 @@
       <c r="N305" s="1"/>
       <c r="O305" s="1"/>
       <c r="P305" s="1"/>
-      <c r="Q305" s="4"/>
+      <c r="Q305" s="6"/>
       <c r="R305" s="1"/>
     </row>
     <row r="306" ht="12.75">
@@ -7514,16 +7516,16 @@
       <c r="E306" s="1"/>
       <c r="F306" s="1"/>
       <c r="G306" s="1"/>
-      <c r="H306" s="3"/>
+      <c r="H306" s="5"/>
       <c r="I306" s="1"/>
       <c r="J306" s="1"/>
-      <c r="K306" s="5"/>
+      <c r="K306" s="7"/>
       <c r="L306" s="1"/>
       <c r="M306" s="1"/>
       <c r="N306" s="1"/>
       <c r="O306" s="1"/>
       <c r="P306" s="1"/>
-      <c r="Q306" s="4"/>
+      <c r="Q306" s="6"/>
       <c r="R306" s="1"/>
     </row>
     <row r="307" ht="12.75">
@@ -7536,16 +7538,16 @@
       <c r="E307" s="1"/>
       <c r="F307" s="1"/>
       <c r="G307" s="1"/>
-      <c r="H307" s="3"/>
+      <c r="H307" s="5"/>
       <c r="I307" s="1"/>
       <c r="J307" s="1"/>
-      <c r="K307" s="5"/>
+      <c r="K307" s="7"/>
       <c r="L307" s="1"/>
       <c r="M307" s="1"/>
       <c r="N307" s="1"/>
       <c r="O307" s="1"/>
       <c r="P307" s="1"/>
-      <c r="Q307" s="4"/>
+      <c r="Q307" s="6"/>
       <c r="R307" s="1"/>
     </row>
     <row r="308" ht="12.75">
@@ -7558,7 +7560,7 @@
       <c r="E308" s="1"/>
       <c r="F308" s="1"/>
       <c r="G308" s="1"/>
-      <c r="H308" s="3"/>
+      <c r="H308" s="5"/>
       <c r="I308" s="1"/>
       <c r="J308" s="1"/>
       <c r="K308" s="1"/>
@@ -7567,7 +7569,7 @@
       <c r="N308" s="1"/>
       <c r="O308" s="1"/>
       <c r="P308" s="1"/>
-      <c r="Q308" s="4"/>
+      <c r="Q308" s="6"/>
       <c r="R308" s="1"/>
     </row>
     <row r="309" ht="12.75">
@@ -7580,16 +7582,16 @@
       <c r="E309" s="1"/>
       <c r="F309" s="1"/>
       <c r="G309" s="1"/>
-      <c r="H309" s="3"/>
+      <c r="H309" s="5"/>
       <c r="I309" s="1"/>
       <c r="J309" s="1"/>
-      <c r="K309" s="5"/>
+      <c r="K309" s="7"/>
       <c r="L309" s="1"/>
       <c r="M309" s="1"/>
       <c r="N309" s="1"/>
       <c r="O309" s="1"/>
       <c r="P309" s="1"/>
-      <c r="Q309" s="4"/>
+      <c r="Q309" s="6"/>
       <c r="R309" s="1"/>
     </row>
     <row r="310" ht="12.75">
@@ -7602,7 +7604,7 @@
       <c r="E310" s="1"/>
       <c r="F310" s="1"/>
       <c r="G310" s="1"/>
-      <c r="H310" s="3"/>
+      <c r="H310" s="5"/>
       <c r="I310" s="1"/>
       <c r="J310" s="1"/>
       <c r="K310" s="1"/>
@@ -7611,7 +7613,7 @@
       <c r="N310" s="1"/>
       <c r="O310" s="1"/>
       <c r="P310" s="1"/>
-      <c r="Q310" s="4"/>
+      <c r="Q310" s="6"/>
       <c r="R310" s="1"/>
     </row>
     <row r="311" ht="12.75">
@@ -7624,7 +7626,7 @@
       <c r="E311" s="1"/>
       <c r="F311" s="1"/>
       <c r="G311" s="1"/>
-      <c r="H311" s="3"/>
+      <c r="H311" s="5"/>
       <c r="I311" s="1"/>
       <c r="J311" s="1"/>
       <c r="K311" s="1"/>
@@ -7633,7 +7635,7 @@
       <c r="N311" s="1"/>
       <c r="O311" s="1"/>
       <c r="P311" s="1"/>
-      <c r="Q311" s="4"/>
+      <c r="Q311" s="6"/>
       <c r="R311" s="1"/>
     </row>
     <row r="312" ht="12.75">
@@ -7646,7 +7648,7 @@
       <c r="E312" s="1"/>
       <c r="F312" s="1"/>
       <c r="G312" s="1"/>
-      <c r="H312" s="3"/>
+      <c r="H312" s="5"/>
       <c r="I312" s="1"/>
       <c r="J312" s="1"/>
       <c r="K312" s="1"/>
@@ -7655,7 +7657,7 @@
       <c r="N312" s="1"/>
       <c r="O312" s="1"/>
       <c r="P312" s="1"/>
-      <c r="Q312" s="4"/>
+      <c r="Q312" s="6"/>
       <c r="R312" s="1"/>
     </row>
     <row r="313" ht="12.75">
@@ -7668,7 +7670,7 @@
       <c r="E313" s="1"/>
       <c r="F313" s="1"/>
       <c r="G313" s="1"/>
-      <c r="H313" s="3"/>
+      <c r="H313" s="5"/>
       <c r="I313" s="1"/>
       <c r="J313" s="1"/>
       <c r="K313" s="1"/>
@@ -7677,7 +7679,7 @@
       <c r="N313" s="1"/>
       <c r="O313" s="1"/>
       <c r="P313" s="1"/>
-      <c r="Q313" s="4"/>
+      <c r="Q313" s="6"/>
       <c r="R313" s="1"/>
     </row>
     <row r="314" ht="12.75">
@@ -7690,16 +7692,16 @@
       <c r="E314" s="1"/>
       <c r="F314" s="1"/>
       <c r="G314" s="1"/>
-      <c r="H314" s="3"/>
+      <c r="H314" s="5"/>
       <c r="I314" s="1"/>
       <c r="J314" s="1"/>
-      <c r="K314" s="5"/>
+      <c r="K314" s="7"/>
       <c r="L314" s="1"/>
       <c r="M314" s="1"/>
       <c r="N314" s="1"/>
       <c r="O314" s="1"/>
       <c r="P314" s="1"/>
-      <c r="Q314" s="4"/>
+      <c r="Q314" s="6"/>
       <c r="R314" s="1"/>
     </row>
     <row r="315" ht="12.75">
@@ -7712,7 +7714,7 @@
       <c r="E315" s="1"/>
       <c r="F315" s="1"/>
       <c r="G315" s="1"/>
-      <c r="H315" s="3"/>
+      <c r="H315" s="5"/>
       <c r="I315" s="1"/>
       <c r="J315" s="1"/>
       <c r="K315" s="1"/>
@@ -7721,7 +7723,7 @@
       <c r="N315" s="1"/>
       <c r="O315" s="1"/>
       <c r="P315" s="1"/>
-      <c r="Q315" s="4"/>
+      <c r="Q315" s="6"/>
       <c r="R315" s="1"/>
     </row>
     <row r="316" ht="12.75">
@@ -7734,7 +7736,7 @@
       <c r="E316" s="1"/>
       <c r="F316" s="1"/>
       <c r="G316" s="1"/>
-      <c r="H316" s="3"/>
+      <c r="H316" s="5"/>
       <c r="I316" s="1"/>
       <c r="J316" s="1"/>
       <c r="K316" s="1"/>
@@ -7743,7 +7745,7 @@
       <c r="N316" s="1"/>
       <c r="O316" s="1"/>
       <c r="P316" s="1"/>
-      <c r="Q316" s="4"/>
+      <c r="Q316" s="6"/>
       <c r="R316" s="1"/>
     </row>
     <row r="317" ht="12.75">
@@ -7756,7 +7758,7 @@
       <c r="E317" s="1"/>
       <c r="F317" s="1"/>
       <c r="G317" s="1"/>
-      <c r="H317" s="3"/>
+      <c r="H317" s="5"/>
       <c r="I317" s="1"/>
       <c r="J317" s="1"/>
       <c r="K317" s="1"/>
@@ -7765,7 +7767,7 @@
       <c r="N317" s="1"/>
       <c r="O317" s="1"/>
       <c r="P317" s="1"/>
-      <c r="Q317" s="4"/>
+      <c r="Q317" s="6"/>
       <c r="R317" s="1"/>
     </row>
     <row r="318" ht="12.75">
@@ -7778,7 +7780,7 @@
       <c r="E318" s="1"/>
       <c r="F318" s="1"/>
       <c r="G318" s="1"/>
-      <c r="H318" s="3"/>
+      <c r="H318" s="5"/>
       <c r="I318" s="1"/>
       <c r="J318" s="1"/>
       <c r="K318" s="1"/>
@@ -7787,7 +7789,7 @@
       <c r="N318" s="1"/>
       <c r="O318" s="1"/>
       <c r="P318" s="1"/>
-      <c r="Q318" s="4"/>
+      <c r="Q318" s="6"/>
       <c r="R318" s="1"/>
     </row>
     <row r="319" ht="12.75">
@@ -7800,7 +7802,7 @@
       <c r="E319" s="1"/>
       <c r="F319" s="1"/>
       <c r="G319" s="1"/>
-      <c r="H319" s="3"/>
+      <c r="H319" s="5"/>
       <c r="I319" s="1"/>
       <c r="J319" s="1"/>
       <c r="K319" s="1"/>
@@ -7809,7 +7811,7 @@
       <c r="N319" s="1"/>
       <c r="O319" s="1"/>
       <c r="P319" s="1"/>
-      <c r="Q319" s="4"/>
+      <c r="Q319" s="6"/>
       <c r="R319" s="1"/>
     </row>
     <row r="320" ht="12.75">
@@ -7822,7 +7824,7 @@
       <c r="E320" s="1"/>
       <c r="F320" s="1"/>
       <c r="G320" s="1"/>
-      <c r="H320" s="3"/>
+      <c r="H320" s="5"/>
       <c r="I320" s="1"/>
       <c r="J320" s="1"/>
       <c r="K320" s="1"/>
@@ -7831,7 +7833,7 @@
       <c r="N320" s="1"/>
       <c r="O320" s="1"/>
       <c r="P320" s="1"/>
-      <c r="Q320" s="4"/>
+      <c r="Q320" s="6"/>
       <c r="R320" s="1"/>
     </row>
     <row r="321" ht="12.75">
@@ -7844,16 +7846,16 @@
       <c r="E321" s="1"/>
       <c r="F321" s="1"/>
       <c r="G321" s="1"/>
-      <c r="H321" s="3"/>
+      <c r="H321" s="5"/>
       <c r="I321" s="1"/>
       <c r="J321" s="1"/>
-      <c r="K321" s="5"/>
+      <c r="K321" s="7"/>
       <c r="L321" s="1"/>
       <c r="M321" s="1"/>
       <c r="N321" s="1"/>
       <c r="O321" s="1"/>
       <c r="P321" s="1"/>
-      <c r="Q321" s="4"/>
+      <c r="Q321" s="6"/>
       <c r="R321" s="1"/>
     </row>
     <row r="322" ht="12.75">
@@ -7866,7 +7868,7 @@
       <c r="E322" s="1"/>
       <c r="F322" s="1"/>
       <c r="G322" s="1"/>
-      <c r="H322" s="3"/>
+      <c r="H322" s="5"/>
       <c r="I322" s="1"/>
       <c r="J322" s="1"/>
       <c r="K322" s="1"/>
@@ -7875,7 +7877,7 @@
       <c r="N322" s="1"/>
       <c r="O322" s="1"/>
       <c r="P322" s="1"/>
-      <c r="Q322" s="4"/>
+      <c r="Q322" s="6"/>
       <c r="R322" s="1"/>
     </row>
     <row r="323" ht="12.75">
@@ -7888,7 +7890,7 @@
       <c r="E323" s="1"/>
       <c r="F323" s="1"/>
       <c r="G323" s="1"/>
-      <c r="H323" s="3"/>
+      <c r="H323" s="5"/>
       <c r="I323" s="1"/>
       <c r="J323" s="1"/>
       <c r="K323" s="1"/>
@@ -7897,7 +7899,7 @@
       <c r="N323" s="1"/>
       <c r="O323" s="1"/>
       <c r="P323" s="1"/>
-      <c r="Q323" s="4"/>
+      <c r="Q323" s="6"/>
       <c r="R323" s="1"/>
     </row>
     <row r="324" ht="12.75">
@@ -7910,7 +7912,7 @@
       <c r="E324" s="1"/>
       <c r="F324" s="1"/>
       <c r="G324" s="1"/>
-      <c r="H324" s="3"/>
+      <c r="H324" s="5"/>
       <c r="I324" s="1"/>
       <c r="J324" s="1"/>
       <c r="K324" s="1"/>
@@ -7919,7 +7921,7 @@
       <c r="N324" s="1"/>
       <c r="O324" s="1"/>
       <c r="P324" s="1"/>
-      <c r="Q324" s="4"/>
+      <c r="Q324" s="6"/>
       <c r="R324" s="1"/>
     </row>
     <row r="325" ht="12.75">
@@ -7932,7 +7934,7 @@
       <c r="E325" s="1"/>
       <c r="F325" s="1"/>
       <c r="G325" s="1"/>
-      <c r="H325" s="3"/>
+      <c r="H325" s="5"/>
       <c r="I325" s="1"/>
       <c r="J325" s="1"/>
       <c r="K325" s="1"/>
@@ -7941,7 +7943,7 @@
       <c r="N325" s="1"/>
       <c r="O325" s="1"/>
       <c r="P325" s="1"/>
-      <c r="Q325" s="4"/>
+      <c r="Q325" s="6"/>
       <c r="R325" s="1"/>
     </row>
     <row r="326" ht="12.75">
@@ -7954,7 +7956,7 @@
       <c r="E326" s="1"/>
       <c r="F326" s="1"/>
       <c r="G326" s="1"/>
-      <c r="H326" s="3"/>
+      <c r="H326" s="5"/>
       <c r="I326" s="1"/>
       <c r="J326" s="1"/>
       <c r="K326" s="1"/>
@@ -7963,7 +7965,7 @@
       <c r="N326" s="1"/>
       <c r="O326" s="1"/>
       <c r="P326" s="1"/>
-      <c r="Q326" s="4"/>
+      <c r="Q326" s="6"/>
       <c r="R326" s="1"/>
     </row>
     <row r="327" ht="12.75">
@@ -7976,7 +7978,7 @@
       <c r="E327" s="1"/>
       <c r="F327" s="1"/>
       <c r="G327" s="1"/>
-      <c r="H327" s="3"/>
+      <c r="H327" s="5"/>
       <c r="I327" s="1"/>
       <c r="J327" s="1"/>
       <c r="K327" s="1"/>
@@ -7985,7 +7987,7 @@
       <c r="N327" s="1"/>
       <c r="O327" s="1"/>
       <c r="P327" s="1"/>
-      <c r="Q327" s="4"/>
+      <c r="Q327" s="6"/>
       <c r="R327" s="1"/>
     </row>
     <row r="328" ht="12.75">
@@ -7998,7 +8000,7 @@
       <c r="E328" s="1"/>
       <c r="F328" s="1"/>
       <c r="G328" s="1"/>
-      <c r="H328" s="3"/>
+      <c r="H328" s="5"/>
       <c r="I328" s="1"/>
       <c r="J328" s="1"/>
       <c r="K328" s="1"/>
@@ -8007,7 +8009,7 @@
       <c r="N328" s="1"/>
       <c r="O328" s="1"/>
       <c r="P328" s="1"/>
-      <c r="Q328" s="4"/>
+      <c r="Q328" s="6"/>
       <c r="R328" s="1"/>
     </row>
     <row r="329" ht="12.75">
@@ -8020,7 +8022,7 @@
       <c r="E329" s="1"/>
       <c r="F329" s="1"/>
       <c r="G329" s="1"/>
-      <c r="H329" s="3"/>
+      <c r="H329" s="5"/>
       <c r="I329" s="1"/>
       <c r="J329" s="1"/>
       <c r="K329" s="1"/>
@@ -8029,7 +8031,7 @@
       <c r="N329" s="1"/>
       <c r="O329" s="1"/>
       <c r="P329" s="1"/>
-      <c r="Q329" s="4"/>
+      <c r="Q329" s="6"/>
       <c r="R329" s="1"/>
     </row>
     <row r="330" ht="12.75">
@@ -8042,7 +8044,7 @@
       <c r="E330" s="1"/>
       <c r="F330" s="1"/>
       <c r="G330" s="1"/>
-      <c r="H330" s="3"/>
+      <c r="H330" s="5"/>
       <c r="I330" s="1"/>
       <c r="J330" s="1"/>
       <c r="K330" s="1"/>
@@ -8050,8 +8052,8 @@
       <c r="M330" s="1"/>
       <c r="N330" s="1"/>
       <c r="O330" s="1"/>
-      <c r="P330" s="4"/>
-      <c r="Q330" s="4"/>
+      <c r="P330" s="6"/>
+      <c r="Q330" s="6"/>
       <c r="R330" s="1"/>
     </row>
     <row r="331" ht="12.75">
@@ -8064,7 +8066,7 @@
       <c r="E331" s="1"/>
       <c r="F331" s="1"/>
       <c r="G331" s="1"/>
-      <c r="H331" s="3"/>
+      <c r="H331" s="5"/>
       <c r="I331" s="1"/>
       <c r="J331" s="1"/>
       <c r="K331" s="1"/>
@@ -8073,7 +8075,7 @@
       <c r="N331" s="1"/>
       <c r="O331" s="1"/>
       <c r="P331" s="1"/>
-      <c r="Q331" s="4"/>
+      <c r="Q331" s="6"/>
       <c r="R331" s="1"/>
     </row>
     <row r="332" ht="12.75">
@@ -8086,7 +8088,7 @@
       <c r="E332" s="1"/>
       <c r="F332" s="1"/>
       <c r="G332" s="1"/>
-      <c r="H332" s="3"/>
+      <c r="H332" s="5"/>
       <c r="I332" s="1"/>
       <c r="J332" s="1"/>
       <c r="K332" s="1"/>
@@ -8095,7 +8097,7 @@
       <c r="N332" s="1"/>
       <c r="O332" s="1"/>
       <c r="P332" s="1"/>
-      <c r="Q332" s="4"/>
+      <c r="Q332" s="6"/>
       <c r="R332" s="1"/>
     </row>
     <row r="333" ht="12.75">
@@ -8108,7 +8110,7 @@
       <c r="E333" s="1"/>
       <c r="F333" s="1"/>
       <c r="G333" s="1"/>
-      <c r="H333" s="3"/>
+      <c r="H333" s="5"/>
       <c r="I333" s="1"/>
       <c r="J333" s="1"/>
       <c r="K333" s="1"/>
@@ -8117,7 +8119,7 @@
       <c r="N333" s="1"/>
       <c r="O333" s="1"/>
       <c r="P333" s="1"/>
-      <c r="Q333" s="4"/>
+      <c r="Q333" s="6"/>
       <c r="R333" s="1"/>
     </row>
     <row r="334" ht="12.75">
@@ -8130,7 +8132,7 @@
       <c r="E334" s="1"/>
       <c r="F334" s="1"/>
       <c r="G334" s="1"/>
-      <c r="H334" s="3"/>
+      <c r="H334" s="5"/>
       <c r="I334" s="1"/>
       <c r="J334" s="1"/>
       <c r="K334" s="1"/>
@@ -8139,7 +8141,7 @@
       <c r="N334" s="1"/>
       <c r="O334" s="1"/>
       <c r="P334" s="1"/>
-      <c r="Q334" s="4"/>
+      <c r="Q334" s="6"/>
       <c r="R334" s="1"/>
     </row>
     <row r="335" ht="12.75">
@@ -8152,16 +8154,16 @@
       <c r="E335" s="1"/>
       <c r="F335" s="1"/>
       <c r="G335" s="1"/>
-      <c r="H335" s="3"/>
+      <c r="H335" s="5"/>
       <c r="I335" s="1"/>
       <c r="J335" s="1"/>
-      <c r="K335" s="5"/>
+      <c r="K335" s="7"/>
       <c r="L335" s="1"/>
       <c r="M335" s="1"/>
       <c r="N335" s="1"/>
       <c r="O335" s="1"/>
       <c r="P335" s="1"/>
-      <c r="Q335" s="4"/>
+      <c r="Q335" s="6"/>
       <c r="R335" s="1"/>
     </row>
     <row r="336" ht="12.75">
@@ -8174,7 +8176,7 @@
       <c r="E336" s="1"/>
       <c r="F336" s="1"/>
       <c r="G336" s="1"/>
-      <c r="H336" s="3"/>
+      <c r="H336" s="5"/>
       <c r="I336" s="1"/>
       <c r="J336" s="1"/>
       <c r="K336" s="1"/>
@@ -8183,7 +8185,7 @@
       <c r="N336" s="1"/>
       <c r="O336" s="1"/>
       <c r="P336" s="1"/>
-      <c r="Q336" s="4"/>
+      <c r="Q336" s="6"/>
       <c r="R336" s="1"/>
     </row>
     <row r="337" ht="12.75">
@@ -8196,7 +8198,7 @@
       <c r="E337" s="1"/>
       <c r="F337" s="1"/>
       <c r="G337" s="1"/>
-      <c r="H337" s="3"/>
+      <c r="H337" s="5"/>
       <c r="I337" s="1"/>
       <c r="J337" s="1"/>
       <c r="K337" s="1"/>
@@ -8205,7 +8207,7 @@
       <c r="N337" s="1"/>
       <c r="O337" s="1"/>
       <c r="P337" s="1"/>
-      <c r="Q337" s="4"/>
+      <c r="Q337" s="6"/>
       <c r="R337" s="1"/>
     </row>
     <row r="338" ht="12.75">
@@ -8218,7 +8220,7 @@
       <c r="E338" s="1"/>
       <c r="F338" s="1"/>
       <c r="G338" s="1"/>
-      <c r="H338" s="3"/>
+      <c r="H338" s="5"/>
       <c r="I338" s="1"/>
       <c r="J338" s="1"/>
       <c r="K338" s="1"/>
@@ -8227,7 +8229,7 @@
       <c r="N338" s="1"/>
       <c r="O338" s="1"/>
       <c r="P338" s="1"/>
-      <c r="Q338" s="4"/>
+      <c r="Q338" s="6"/>
       <c r="R338" s="1"/>
     </row>
     <row r="339" ht="12.75">
@@ -8240,7 +8242,7 @@
       <c r="E339" s="1"/>
       <c r="F339" s="1"/>
       <c r="G339" s="1"/>
-      <c r="H339" s="3"/>
+      <c r="H339" s="5"/>
       <c r="I339" s="1"/>
       <c r="J339" s="1"/>
       <c r="K339" s="1"/>
@@ -8249,7 +8251,7 @@
       <c r="N339" s="1"/>
       <c r="O339" s="1"/>
       <c r="P339" s="1"/>
-      <c r="Q339" s="4"/>
+      <c r="Q339" s="6"/>
       <c r="R339" s="1"/>
     </row>
     <row r="340" ht="12.75">
@@ -8262,7 +8264,7 @@
       <c r="E340" s="1"/>
       <c r="F340" s="1"/>
       <c r="G340" s="1"/>
-      <c r="H340" s="3"/>
+      <c r="H340" s="5"/>
       <c r="I340" s="1"/>
       <c r="J340" s="1"/>
       <c r="K340" s="1"/>
@@ -8271,7 +8273,7 @@
       <c r="N340" s="1"/>
       <c r="O340" s="1"/>
       <c r="P340" s="1"/>
-      <c r="Q340" s="4"/>
+      <c r="Q340" s="6"/>
       <c r="R340" s="1"/>
     </row>
     <row r="341" ht="12.75">
@@ -8284,7 +8286,7 @@
       <c r="E341" s="1"/>
       <c r="F341" s="1"/>
       <c r="G341" s="1"/>
-      <c r="H341" s="3"/>
+      <c r="H341" s="5"/>
       <c r="I341" s="1"/>
       <c r="J341" s="1"/>
       <c r="K341" s="1"/>
@@ -8293,7 +8295,7 @@
       <c r="N341" s="1"/>
       <c r="O341" s="1"/>
       <c r="P341" s="1"/>
-      <c r="Q341" s="4"/>
+      <c r="Q341" s="6"/>
       <c r="R341" s="1"/>
     </row>
     <row r="342" ht="12.75">
@@ -8306,7 +8308,7 @@
       <c r="E342" s="1"/>
       <c r="F342" s="1"/>
       <c r="G342" s="1"/>
-      <c r="H342" s="3"/>
+      <c r="H342" s="5"/>
       <c r="I342" s="1"/>
       <c r="J342" s="1"/>
       <c r="K342" s="1"/>
@@ -8315,7 +8317,7 @@
       <c r="N342" s="1"/>
       <c r="O342" s="1"/>
       <c r="P342" s="1"/>
-      <c r="Q342" s="4"/>
+      <c r="Q342" s="6"/>
       <c r="R342" s="1"/>
     </row>
     <row r="343" ht="12.75">
@@ -8328,7 +8330,7 @@
       <c r="E343" s="1"/>
       <c r="F343" s="1"/>
       <c r="G343" s="1"/>
-      <c r="H343" s="3"/>
+      <c r="H343" s="5"/>
       <c r="I343" s="1"/>
       <c r="J343" s="1"/>
       <c r="K343" s="1"/>
@@ -8337,7 +8339,7 @@
       <c r="N343" s="1"/>
       <c r="O343" s="1"/>
       <c r="P343" s="1"/>
-      <c r="Q343" s="4"/>
+      <c r="Q343" s="6"/>
       <c r="R343" s="1"/>
     </row>
     <row r="344" ht="12.75">
@@ -8350,7 +8352,7 @@
       <c r="E344" s="1"/>
       <c r="F344" s="1"/>
       <c r="G344" s="1"/>
-      <c r="H344" s="3"/>
+      <c r="H344" s="5"/>
       <c r="I344" s="1"/>
       <c r="J344" s="1"/>
       <c r="K344" s="1"/>
@@ -8359,7 +8361,7 @@
       <c r="N344" s="1"/>
       <c r="O344" s="1"/>
       <c r="P344" s="1"/>
-      <c r="Q344" s="4"/>
+      <c r="Q344" s="6"/>
       <c r="R344" s="1"/>
     </row>
     <row r="345" ht="12.75">
@@ -8372,7 +8374,7 @@
       <c r="E345" s="1"/>
       <c r="F345" s="1"/>
       <c r="G345" s="1"/>
-      <c r="H345" s="3"/>
+      <c r="H345" s="5"/>
       <c r="I345" s="1"/>
       <c r="J345" s="1"/>
       <c r="K345" s="1"/>
@@ -8381,7 +8383,7 @@
       <c r="N345" s="1"/>
       <c r="O345" s="1"/>
       <c r="P345" s="1"/>
-      <c r="Q345" s="4"/>
+      <c r="Q345" s="6"/>
       <c r="R345" s="1"/>
     </row>
     <row r="346" ht="12.75">
@@ -8394,7 +8396,7 @@
       <c r="E346" s="1"/>
       <c r="F346" s="1"/>
       <c r="G346" s="1"/>
-      <c r="H346" s="3"/>
+      <c r="H346" s="5"/>
       <c r="I346" s="1"/>
       <c r="J346" s="1"/>
       <c r="K346" s="1"/>
@@ -8403,7 +8405,7 @@
       <c r="N346" s="1"/>
       <c r="O346" s="1"/>
       <c r="P346" s="1"/>
-      <c r="Q346" s="4"/>
+      <c r="Q346" s="6"/>
       <c r="R346" s="1"/>
     </row>
     <row r="347" ht="12.75">
@@ -8416,7 +8418,7 @@
       <c r="E347" s="1"/>
       <c r="F347" s="1"/>
       <c r="G347" s="1"/>
-      <c r="H347" s="3"/>
+      <c r="H347" s="5"/>
       <c r="I347" s="1"/>
       <c r="J347" s="1"/>
       <c r="K347" s="1"/>
@@ -8425,7 +8427,7 @@
       <c r="N347" s="1"/>
       <c r="O347" s="1"/>
       <c r="P347" s="1"/>
-      <c r="Q347" s="4"/>
+      <c r="Q347" s="6"/>
       <c r="R347" s="1"/>
     </row>
     <row r="348" ht="12.75">
@@ -8438,7 +8440,7 @@
       <c r="E348" s="1"/>
       <c r="F348" s="1"/>
       <c r="G348" s="1"/>
-      <c r="H348" s="3"/>
+      <c r="H348" s="5"/>
       <c r="I348" s="1"/>
       <c r="J348" s="1"/>
       <c r="K348" s="1"/>
@@ -8447,7 +8449,7 @@
       <c r="N348" s="1"/>
       <c r="O348" s="1"/>
       <c r="P348" s="1"/>
-      <c r="Q348" s="4"/>
+      <c r="Q348" s="6"/>
       <c r="R348" s="1"/>
     </row>
     <row r="349" ht="12.75">
@@ -8460,16 +8462,16 @@
       <c r="E349" s="1"/>
       <c r="F349" s="1"/>
       <c r="G349" s="1"/>
-      <c r="H349" s="3"/>
+      <c r="H349" s="5"/>
       <c r="I349" s="1"/>
       <c r="J349" s="1"/>
-      <c r="K349" s="5"/>
+      <c r="K349" s="7"/>
       <c r="L349" s="1"/>
       <c r="M349" s="1"/>
       <c r="N349" s="1"/>
       <c r="O349" s="1"/>
       <c r="P349" s="1"/>
-      <c r="Q349" s="4"/>
+      <c r="Q349" s="6"/>
       <c r="R349" s="1"/>
     </row>
     <row r="350" ht="12.75">
@@ -8482,7 +8484,7 @@
       <c r="E350" s="1"/>
       <c r="F350" s="1"/>
       <c r="G350" s="1"/>
-      <c r="H350" s="3"/>
+      <c r="H350" s="5"/>
       <c r="I350" s="1"/>
       <c r="J350" s="1"/>
       <c r="K350" s="1"/>
@@ -8491,7 +8493,7 @@
       <c r="N350" s="1"/>
       <c r="O350" s="1"/>
       <c r="P350" s="1"/>
-      <c r="Q350" s="4"/>
+      <c r="Q350" s="6"/>
       <c r="R350" s="1"/>
     </row>
     <row r="351" ht="12.75">
@@ -8504,7 +8506,7 @@
       <c r="E351" s="1"/>
       <c r="F351" s="1"/>
       <c r="G351" s="1"/>
-      <c r="H351" s="3"/>
+      <c r="H351" s="5"/>
       <c r="I351" s="1"/>
       <c r="J351" s="1"/>
       <c r="K351" s="1"/>
@@ -8513,7 +8515,7 @@
       <c r="N351" s="1"/>
       <c r="O351" s="1"/>
       <c r="P351" s="1"/>
-      <c r="Q351" s="4"/>
+      <c r="Q351" s="6"/>
       <c r="R351" s="1"/>
     </row>
     <row r="352" ht="12.75">
@@ -8526,7 +8528,7 @@
       <c r="E352" s="1"/>
       <c r="F352" s="1"/>
       <c r="G352" s="1"/>
-      <c r="H352" s="3"/>
+      <c r="H352" s="5"/>
       <c r="I352" s="1"/>
       <c r="J352" s="1"/>
       <c r="K352" s="1"/>
@@ -8534,8 +8536,8 @@
       <c r="M352" s="1"/>
       <c r="N352" s="1"/>
       <c r="O352" s="1"/>
-      <c r="P352" s="4"/>
-      <c r="Q352" s="4"/>
+      <c r="P352" s="6"/>
+      <c r="Q352" s="6"/>
       <c r="R352" s="1"/>
     </row>
     <row r="353" ht="12.75">
@@ -8548,7 +8550,7 @@
       <c r="E353" s="1"/>
       <c r="F353" s="1"/>
       <c r="G353" s="1"/>
-      <c r="H353" s="3"/>
+      <c r="H353" s="5"/>
       <c r="I353" s="1"/>
       <c r="J353" s="1"/>
       <c r="K353" s="1"/>
@@ -8556,8 +8558,8 @@
       <c r="M353" s="1"/>
       <c r="N353" s="1"/>
       <c r="O353" s="1"/>
-      <c r="P353" s="4"/>
-      <c r="Q353" s="4"/>
+      <c r="P353" s="6"/>
+      <c r="Q353" s="6"/>
       <c r="R353" s="1"/>
     </row>
     <row r="354" ht="12.75">
@@ -8570,7 +8572,7 @@
       <c r="E354" s="1"/>
       <c r="F354" s="1"/>
       <c r="G354" s="1"/>
-      <c r="H354" s="3"/>
+      <c r="H354" s="5"/>
       <c r="I354" s="1"/>
       <c r="J354" s="1"/>
       <c r="K354" s="1"/>
@@ -8579,7 +8581,7 @@
       <c r="N354" s="1"/>
       <c r="O354" s="1"/>
       <c r="P354" s="1"/>
-      <c r="Q354" s="4"/>
+      <c r="Q354" s="6"/>
       <c r="R354" s="1"/>
     </row>
     <row r="355" ht="12.75">
@@ -8592,7 +8594,7 @@
       <c r="E355" s="1"/>
       <c r="F355" s="1"/>
       <c r="G355" s="1"/>
-      <c r="H355" s="3"/>
+      <c r="H355" s="5"/>
       <c r="I355" s="1"/>
       <c r="J355" s="1"/>
       <c r="K355" s="1"/>
@@ -8600,8 +8602,8 @@
       <c r="M355" s="1"/>
       <c r="N355" s="1"/>
       <c r="O355" s="1"/>
-      <c r="P355" s="4"/>
-      <c r="Q355" s="4"/>
+      <c r="P355" s="6"/>
+      <c r="Q355" s="6"/>
       <c r="R355" s="1"/>
     </row>
     <row r="356" ht="12.75">
@@ -8614,7 +8616,7 @@
       <c r="E356" s="1"/>
       <c r="F356" s="1"/>
       <c r="G356" s="1"/>
-      <c r="H356" s="3"/>
+      <c r="H356" s="5"/>
       <c r="I356" s="1"/>
       <c r="J356" s="1"/>
       <c r="K356" s="1"/>
@@ -8623,7 +8625,7 @@
       <c r="N356" s="1"/>
       <c r="O356" s="1"/>
       <c r="P356" s="1"/>
-      <c r="Q356" s="4"/>
+      <c r="Q356" s="6"/>
       <c r="R356" s="1"/>
     </row>
     <row r="357" ht="12.75">
@@ -8636,7 +8638,7 @@
       <c r="E357" s="1"/>
       <c r="F357" s="1"/>
       <c r="G357" s="1"/>
-      <c r="H357" s="3"/>
+      <c r="H357" s="5"/>
       <c r="I357" s="1"/>
       <c r="J357" s="1"/>
       <c r="K357" s="1"/>
@@ -8645,7 +8647,7 @@
       <c r="N357" s="1"/>
       <c r="O357" s="1"/>
       <c r="P357" s="1"/>
-      <c r="Q357" s="4"/>
+      <c r="Q357" s="6"/>
       <c r="R357" s="1"/>
     </row>
     <row r="358" ht="12.75">
@@ -8658,7 +8660,7 @@
       <c r="E358" s="1"/>
       <c r="F358" s="1"/>
       <c r="G358" s="1"/>
-      <c r="H358" s="3"/>
+      <c r="H358" s="5"/>
       <c r="I358" s="1"/>
       <c r="J358" s="1"/>
       <c r="K358" s="1"/>
@@ -8667,7 +8669,7 @@
       <c r="N358" s="1"/>
       <c r="O358" s="1"/>
       <c r="P358" s="1"/>
-      <c r="Q358" s="4"/>
+      <c r="Q358" s="6"/>
       <c r="R358" s="1"/>
     </row>
     <row r="359" ht="12.75">
@@ -8680,7 +8682,7 @@
       <c r="E359" s="1"/>
       <c r="F359" s="1"/>
       <c r="G359" s="1"/>
-      <c r="H359" s="3"/>
+      <c r="H359" s="5"/>
       <c r="I359" s="1"/>
       <c r="J359" s="1"/>
       <c r="K359" s="1"/>
@@ -8689,7 +8691,7 @@
       <c r="N359" s="1"/>
       <c r="O359" s="1"/>
       <c r="P359" s="1"/>
-      <c r="Q359" s="4"/>
+      <c r="Q359" s="6"/>
       <c r="R359" s="1"/>
     </row>
     <row r="360" ht="12.75">
@@ -8702,7 +8704,7 @@
       <c r="E360" s="1"/>
       <c r="F360" s="1"/>
       <c r="G360" s="1"/>
-      <c r="H360" s="3"/>
+      <c r="H360" s="5"/>
       <c r="I360" s="1"/>
       <c r="J360" s="1"/>
       <c r="K360" s="1"/>
@@ -8711,7 +8713,7 @@
       <c r="N360" s="1"/>
       <c r="O360" s="1"/>
       <c r="P360" s="1"/>
-      <c r="Q360" s="4"/>
+      <c r="Q360" s="6"/>
       <c r="R360" s="1"/>
     </row>
     <row r="361" ht="12.75">
@@ -8724,7 +8726,7 @@
       <c r="E361" s="1"/>
       <c r="F361" s="1"/>
       <c r="G361" s="1"/>
-      <c r="H361" s="3"/>
+      <c r="H361" s="5"/>
       <c r="I361" s="1"/>
       <c r="J361" s="1"/>
       <c r="K361" s="1"/>
@@ -8733,7 +8735,7 @@
       <c r="N361" s="1"/>
       <c r="O361" s="1"/>
       <c r="P361" s="1"/>
-      <c r="Q361" s="4"/>
+      <c r="Q361" s="6"/>
       <c r="R361" s="1"/>
     </row>
     <row r="362" ht="12.75">
@@ -8746,7 +8748,7 @@
       <c r="E362" s="1"/>
       <c r="F362" s="1"/>
       <c r="G362" s="1"/>
-      <c r="H362" s="3"/>
+      <c r="H362" s="5"/>
       <c r="I362" s="1"/>
       <c r="J362" s="1"/>
       <c r="K362" s="1"/>
@@ -8755,7 +8757,7 @@
       <c r="N362" s="1"/>
       <c r="O362" s="1"/>
       <c r="P362" s="1"/>
-      <c r="Q362" s="4"/>
+      <c r="Q362" s="6"/>
       <c r="R362" s="1"/>
     </row>
     <row r="363" ht="12.75">
@@ -8768,7 +8770,7 @@
       <c r="E363" s="1"/>
       <c r="F363" s="1"/>
       <c r="G363" s="1"/>
-      <c r="H363" s="3"/>
+      <c r="H363" s="5"/>
       <c r="I363" s="1"/>
       <c r="J363" s="1"/>
       <c r="K363" s="1"/>
@@ -8777,7 +8779,7 @@
       <c r="N363" s="1"/>
       <c r="O363" s="1"/>
       <c r="P363" s="1"/>
-      <c r="Q363" s="4"/>
+      <c r="Q363" s="6"/>
       <c r="R363" s="1"/>
     </row>
     <row r="364" ht="12.75">
@@ -8790,7 +8792,7 @@
       <c r="E364" s="1"/>
       <c r="F364" s="1"/>
       <c r="G364" s="1"/>
-      <c r="H364" s="3"/>
+      <c r="H364" s="5"/>
       <c r="I364" s="1"/>
       <c r="J364" s="1"/>
       <c r="K364" s="1"/>
@@ -8799,7 +8801,7 @@
       <c r="N364" s="1"/>
       <c r="O364" s="1"/>
       <c r="P364" s="1"/>
-      <c r="Q364" s="4"/>
+      <c r="Q364" s="6"/>
       <c r="R364" s="1"/>
     </row>
     <row r="365" ht="12.75">
@@ -8812,7 +8814,7 @@
       <c r="E365" s="1"/>
       <c r="F365" s="1"/>
       <c r="G365" s="1"/>
-      <c r="H365" s="3"/>
+      <c r="H365" s="5"/>
       <c r="I365" s="1"/>
       <c r="J365" s="1"/>
       <c r="K365" s="1"/>
@@ -8821,7 +8823,7 @@
       <c r="N365" s="1"/>
       <c r="O365" s="1"/>
       <c r="P365" s="1"/>
-      <c r="Q365" s="4"/>
+      <c r="Q365" s="6"/>
       <c r="R365" s="1"/>
     </row>
     <row r="366" ht="12.75">
@@ -8834,7 +8836,7 @@
       <c r="E366" s="1"/>
       <c r="F366" s="1"/>
       <c r="G366" s="1"/>
-      <c r="H366" s="3"/>
+      <c r="H366" s="5"/>
       <c r="I366" s="1"/>
       <c r="J366" s="1"/>
       <c r="K366" s="1"/>
@@ -8843,7 +8845,7 @@
       <c r="N366" s="1"/>
       <c r="O366" s="1"/>
       <c r="P366" s="1"/>
-      <c r="Q366" s="4"/>
+      <c r="Q366" s="6"/>
       <c r="R366" s="1"/>
     </row>
     <row r="367" ht="12.75">
@@ -8856,7 +8858,7 @@
       <c r="E367" s="1"/>
       <c r="F367" s="1"/>
       <c r="G367" s="1"/>
-      <c r="H367" s="3"/>
+      <c r="H367" s="5"/>
       <c r="I367" s="1"/>
       <c r="J367" s="1"/>
       <c r="K367" s="1"/>
@@ -8865,7 +8867,7 @@
       <c r="N367" s="1"/>
       <c r="O367" s="1"/>
       <c r="P367" s="1"/>
-      <c r="Q367" s="4"/>
+      <c r="Q367" s="6"/>
       <c r="R367" s="1"/>
     </row>
     <row r="368" ht="12.75">
@@ -8878,7 +8880,7 @@
       <c r="E368" s="1"/>
       <c r="F368" s="1"/>
       <c r="G368" s="1"/>
-      <c r="H368" s="3"/>
+      <c r="H368" s="5"/>
       <c r="I368" s="1"/>
       <c r="J368" s="1"/>
       <c r="K368" s="1"/>
@@ -8887,7 +8889,7 @@
       <c r="N368" s="1"/>
       <c r="O368" s="1"/>
       <c r="P368" s="1"/>
-      <c r="Q368" s="4"/>
+      <c r="Q368" s="6"/>
       <c r="R368" s="1"/>
     </row>
     <row r="369" ht="12.75">
@@ -8900,7 +8902,7 @@
       <c r="E369" s="1"/>
       <c r="F369" s="1"/>
       <c r="G369" s="1"/>
-      <c r="H369" s="3"/>
+      <c r="H369" s="5"/>
       <c r="I369" s="1"/>
       <c r="J369" s="1"/>
       <c r="K369" s="1"/>
@@ -8909,7 +8911,7 @@
       <c r="N369" s="1"/>
       <c r="O369" s="1"/>
       <c r="P369" s="1"/>
-      <c r="Q369" s="4"/>
+      <c r="Q369" s="6"/>
       <c r="R369" s="1"/>
     </row>
     <row r="370" ht="12.75">
@@ -8922,7 +8924,7 @@
       <c r="E370" s="1"/>
       <c r="F370" s="1"/>
       <c r="G370" s="1"/>
-      <c r="H370" s="3"/>
+      <c r="H370" s="5"/>
       <c r="I370" s="1"/>
       <c r="J370" s="1"/>
       <c r="K370" s="1"/>
@@ -8931,7 +8933,7 @@
       <c r="N370" s="1"/>
       <c r="O370" s="1"/>
       <c r="P370" s="1"/>
-      <c r="Q370" s="4"/>
+      <c r="Q370" s="6"/>
       <c r="R370" s="1"/>
     </row>
     <row r="371" ht="12.75">
@@ -8944,7 +8946,7 @@
       <c r="E371" s="1"/>
       <c r="F371" s="1"/>
       <c r="G371" s="1"/>
-      <c r="H371" s="3"/>
+      <c r="H371" s="5"/>
       <c r="I371" s="1"/>
       <c r="J371" s="1"/>
       <c r="K371" s="1"/>
@@ -8953,7 +8955,7 @@
       <c r="N371" s="1"/>
       <c r="O371" s="1"/>
       <c r="P371" s="1"/>
-      <c r="Q371" s="4"/>
+      <c r="Q371" s="6"/>
       <c r="R371" s="1"/>
     </row>
     <row r="372" ht="12.75">
@@ -8966,7 +8968,7 @@
       <c r="E372" s="1"/>
       <c r="F372" s="1"/>
       <c r="G372" s="1"/>
-      <c r="H372" s="3"/>
+      <c r="H372" s="5"/>
       <c r="I372" s="1"/>
       <c r="J372" s="1"/>
       <c r="K372" s="1"/>
@@ -8975,7 +8977,7 @@
       <c r="N372" s="1"/>
       <c r="O372" s="1"/>
       <c r="P372" s="1"/>
-      <c r="Q372" s="4"/>
+      <c r="Q372" s="6"/>
       <c r="R372" s="1"/>
     </row>
     <row r="373" ht="12.75">
@@ -8988,7 +8990,7 @@
       <c r="E373" s="1"/>
       <c r="F373" s="1"/>
       <c r="G373" s="1"/>
-      <c r="H373" s="3"/>
+      <c r="H373" s="5"/>
       <c r="I373" s="1"/>
       <c r="J373" s="1"/>
       <c r="K373" s="1"/>
@@ -8997,7 +8999,7 @@
       <c r="N373" s="1"/>
       <c r="O373" s="1"/>
       <c r="P373" s="1"/>
-      <c r="Q373" s="4"/>
+      <c r="Q373" s="6"/>
       <c r="R373" s="1"/>
     </row>
     <row r="374" ht="12.75">
@@ -9010,7 +9012,7 @@
       <c r="E374" s="1"/>
       <c r="F374" s="1"/>
       <c r="G374" s="1"/>
-      <c r="H374" s="3"/>
+      <c r="H374" s="5"/>
       <c r="I374" s="1"/>
       <c r="J374" s="1"/>
       <c r="K374" s="1"/>
@@ -9019,7 +9021,7 @@
       <c r="N374" s="1"/>
       <c r="O374" s="1"/>
       <c r="P374" s="1"/>
-      <c r="Q374" s="4"/>
+      <c r="Q374" s="6"/>
       <c r="R374" s="1"/>
     </row>
     <row r="375" ht="12.75">
@@ -9032,7 +9034,7 @@
       <c r="E375" s="1"/>
       <c r="F375" s="1"/>
       <c r="G375" s="1"/>
-      <c r="H375" s="3"/>
+      <c r="H375" s="5"/>
       <c r="I375" s="1"/>
       <c r="J375" s="1"/>
       <c r="K375" s="1"/>
@@ -9041,7 +9043,7 @@
       <c r="N375" s="1"/>
       <c r="O375" s="1"/>
       <c r="P375" s="1"/>
-      <c r="Q375" s="4"/>
+      <c r="Q375" s="6"/>
       <c r="R375" s="1"/>
     </row>
     <row r="376" ht="12.75">
@@ -9054,16 +9056,16 @@
       <c r="E376" s="1"/>
       <c r="F376" s="1"/>
       <c r="G376" s="1"/>
-      <c r="H376" s="3"/>
+      <c r="H376" s="5"/>
       <c r="I376" s="1"/>
       <c r="J376" s="1"/>
-      <c r="K376" s="5"/>
+      <c r="K376" s="7"/>
       <c r="L376" s="1"/>
       <c r="M376" s="1"/>
       <c r="N376" s="1"/>
       <c r="O376" s="1"/>
       <c r="P376" s="1"/>
-      <c r="Q376" s="4"/>
+      <c r="Q376" s="6"/>
       <c r="R376" s="1"/>
     </row>
     <row r="377" ht="12.75">
@@ -9076,7 +9078,7 @@
       <c r="E377" s="1"/>
       <c r="F377" s="1"/>
       <c r="G377" s="1"/>
-      <c r="H377" s="3"/>
+      <c r="H377" s="5"/>
       <c r="I377" s="1"/>
       <c r="J377" s="1"/>
       <c r="K377" s="1"/>
@@ -9085,7 +9087,7 @@
       <c r="N377" s="1"/>
       <c r="O377" s="1"/>
       <c r="P377" s="1"/>
-      <c r="Q377" s="4"/>
+      <c r="Q377" s="6"/>
       <c r="R377" s="1"/>
     </row>
     <row r="378" ht="12.75">
@@ -9098,16 +9100,16 @@
       <c r="E378" s="1"/>
       <c r="F378" s="1"/>
       <c r="G378" s="1"/>
-      <c r="H378" s="3"/>
+      <c r="H378" s="5"/>
       <c r="I378" s="1"/>
       <c r="J378" s="1"/>
-      <c r="K378" s="5"/>
+      <c r="K378" s="7"/>
       <c r="L378" s="1"/>
       <c r="M378" s="1"/>
       <c r="N378" s="1"/>
       <c r="O378" s="1"/>
       <c r="P378" s="1"/>
-      <c r="Q378" s="4"/>
+      <c r="Q378" s="6"/>
       <c r="R378" s="1"/>
     </row>
     <row r="379" ht="12.75">
@@ -9120,7 +9122,7 @@
       <c r="E379" s="1"/>
       <c r="F379" s="1"/>
       <c r="G379" s="1"/>
-      <c r="H379" s="3"/>
+      <c r="H379" s="5"/>
       <c r="I379" s="1"/>
       <c r="J379" s="1"/>
       <c r="K379" s="1"/>
@@ -9129,7 +9131,7 @@
       <c r="N379" s="1"/>
       <c r="O379" s="1"/>
       <c r="P379" s="1"/>
-      <c r="Q379" s="4"/>
+      <c r="Q379" s="6"/>
       <c r="R379" s="1"/>
     </row>
     <row r="380" ht="12.75">
@@ -9142,7 +9144,7 @@
       <c r="E380" s="1"/>
       <c r="F380" s="1"/>
       <c r="G380" s="1"/>
-      <c r="H380" s="3"/>
+      <c r="H380" s="5"/>
       <c r="I380" s="1"/>
       <c r="J380" s="1"/>
       <c r="K380" s="1"/>
@@ -9151,7 +9153,7 @@
       <c r="N380" s="1"/>
       <c r="O380" s="1"/>
       <c r="P380" s="1"/>
-      <c r="Q380" s="4"/>
+      <c r="Q380" s="6"/>
       <c r="R380" s="1"/>
     </row>
     <row r="381" ht="12.75">
@@ -9164,16 +9166,16 @@
       <c r="E381" s="1"/>
       <c r="F381" s="1"/>
       <c r="G381" s="1"/>
-      <c r="H381" s="3"/>
+      <c r="H381" s="5"/>
       <c r="I381" s="1"/>
       <c r="J381" s="1"/>
-      <c r="K381" s="5"/>
+      <c r="K381" s="7"/>
       <c r="L381" s="1"/>
       <c r="M381" s="1"/>
       <c r="N381" s="1"/>
       <c r="O381" s="1"/>
       <c r="P381" s="1"/>
-      <c r="Q381" s="4"/>
+      <c r="Q381" s="6"/>
       <c r="R381" s="1"/>
     </row>
     <row r="382" ht="12.75">
@@ -9186,7 +9188,7 @@
       <c r="E382" s="1"/>
       <c r="F382" s="1"/>
       <c r="G382" s="1"/>
-      <c r="H382" s="3"/>
+      <c r="H382" s="5"/>
       <c r="I382" s="1"/>
       <c r="J382" s="1"/>
       <c r="K382" s="1"/>
@@ -9195,7 +9197,7 @@
       <c r="N382" s="1"/>
       <c r="O382" s="1"/>
       <c r="P382" s="1"/>
-      <c r="Q382" s="4"/>
+      <c r="Q382" s="6"/>
       <c r="R382" s="1"/>
     </row>
     <row r="383" ht="12.75">
@@ -9208,7 +9210,7 @@
       <c r="E383" s="1"/>
       <c r="F383" s="1"/>
       <c r="G383" s="1"/>
-      <c r="H383" s="3"/>
+      <c r="H383" s="5"/>
       <c r="I383" s="1"/>
       <c r="J383" s="1"/>
       <c r="K383" s="1"/>
@@ -9217,7 +9219,7 @@
       <c r="N383" s="1"/>
       <c r="O383" s="1"/>
       <c r="P383" s="1"/>
-      <c r="Q383" s="4"/>
+      <c r="Q383" s="6"/>
       <c r="R383" s="1"/>
     </row>
     <row r="384" ht="12.75">
@@ -9230,7 +9232,7 @@
       <c r="E384" s="1"/>
       <c r="F384" s="1"/>
       <c r="G384" s="1"/>
-      <c r="H384" s="3"/>
+      <c r="H384" s="5"/>
       <c r="I384" s="1"/>
       <c r="J384" s="1"/>
       <c r="K384" s="1"/>
@@ -9239,7 +9241,7 @@
       <c r="N384" s="1"/>
       <c r="O384" s="1"/>
       <c r="P384" s="1"/>
-      <c r="Q384" s="4"/>
+      <c r="Q384" s="6"/>
       <c r="R384" s="1"/>
     </row>
     <row r="385" ht="12.75">
@@ -9252,7 +9254,7 @@
       <c r="E385" s="1"/>
       <c r="F385" s="1"/>
       <c r="G385" s="1"/>
-      <c r="H385" s="3"/>
+      <c r="H385" s="5"/>
       <c r="I385" s="1"/>
       <c r="J385" s="1"/>
       <c r="K385" s="1"/>
@@ -9261,7 +9263,7 @@
       <c r="N385" s="1"/>
       <c r="O385" s="1"/>
       <c r="P385" s="1"/>
-      <c r="Q385" s="4"/>
+      <c r="Q385" s="6"/>
       <c r="R385" s="1"/>
     </row>
     <row r="386" ht="12.75">
@@ -9274,7 +9276,7 @@
       <c r="E386" s="1"/>
       <c r="F386" s="1"/>
       <c r="G386" s="1"/>
-      <c r="H386" s="3"/>
+      <c r="H386" s="5"/>
       <c r="I386" s="1"/>
       <c r="J386" s="1"/>
       <c r="K386" s="1"/>
@@ -9283,7 +9285,7 @@
       <c r="N386" s="1"/>
       <c r="O386" s="1"/>
       <c r="P386" s="1"/>
-      <c r="Q386" s="4"/>
+      <c r="Q386" s="6"/>
       <c r="R386" s="1"/>
     </row>
     <row r="387" ht="12.75">
@@ -9296,7 +9298,7 @@
       <c r="E387" s="1"/>
       <c r="F387" s="1"/>
       <c r="G387" s="1"/>
-      <c r="H387" s="3"/>
+      <c r="H387" s="5"/>
       <c r="I387" s="1"/>
       <c r="J387" s="1"/>
       <c r="K387" s="1"/>
@@ -9305,7 +9307,7 @@
       <c r="N387" s="1"/>
       <c r="O387" s="1"/>
       <c r="P387" s="1"/>
-      <c r="Q387" s="4"/>
+      <c r="Q387" s="6"/>
       <c r="R387" s="1"/>
     </row>
     <row r="388" ht="12.75">
@@ -9318,7 +9320,7 @@
       <c r="E388" s="1"/>
       <c r="F388" s="1"/>
       <c r="G388" s="1"/>
-      <c r="H388" s="3"/>
+      <c r="H388" s="5"/>
       <c r="I388" s="1"/>
       <c r="J388" s="1"/>
       <c r="K388" s="1"/>
@@ -9327,7 +9329,7 @@
       <c r="N388" s="1"/>
       <c r="O388" s="1"/>
       <c r="P388" s="1"/>
-      <c r="Q388" s="4"/>
+      <c r="Q388" s="6"/>
       <c r="R388" s="1"/>
     </row>
     <row r="389" ht="12.75">
@@ -9340,7 +9342,7 @@
       <c r="E389" s="1"/>
       <c r="F389" s="1"/>
       <c r="G389" s="1"/>
-      <c r="H389" s="3"/>
+      <c r="H389" s="5"/>
       <c r="I389" s="1"/>
       <c r="J389" s="1"/>
       <c r="K389" s="1"/>
@@ -9349,7 +9351,7 @@
       <c r="N389" s="1"/>
       <c r="O389" s="1"/>
       <c r="P389" s="1"/>
-      <c r="Q389" s="4"/>
+      <c r="Q389" s="6"/>
       <c r="R389" s="1"/>
     </row>
     <row r="390" ht="12.75">
@@ -9362,7 +9364,7 @@
       <c r="E390" s="1"/>
       <c r="F390" s="1"/>
       <c r="G390" s="1"/>
-      <c r="H390" s="3"/>
+      <c r="H390" s="5"/>
       <c r="I390" s="1"/>
       <c r="J390" s="1"/>
       <c r="K390" s="1"/>
@@ -9371,7 +9373,7 @@
       <c r="N390" s="1"/>
       <c r="O390" s="1"/>
       <c r="P390" s="1"/>
-      <c r="Q390" s="4"/>
+      <c r="Q390" s="6"/>
       <c r="R390" s="1"/>
     </row>
     <row r="391" ht="12.75">
@@ -9384,16 +9386,16 @@
       <c r="E391" s="1"/>
       <c r="F391" s="1"/>
       <c r="G391" s="1"/>
-      <c r="H391" s="3"/>
+      <c r="H391" s="5"/>
       <c r="I391" s="1"/>
       <c r="J391" s="1"/>
-      <c r="K391" s="5"/>
+      <c r="K391" s="7"/>
       <c r="L391" s="1"/>
       <c r="M391" s="1"/>
       <c r="N391" s="1"/>
       <c r="O391" s="1"/>
       <c r="P391" s="1"/>
-      <c r="Q391" s="4"/>
+      <c r="Q391" s="6"/>
       <c r="R391" s="1"/>
     </row>
     <row r="392" ht="12.75">
@@ -9406,7 +9408,7 @@
       <c r="E392" s="1"/>
       <c r="F392" s="1"/>
       <c r="G392" s="1"/>
-      <c r="H392" s="3"/>
+      <c r="H392" s="5"/>
       <c r="I392" s="1"/>
       <c r="J392" s="1"/>
       <c r="K392" s="1"/>
@@ -9415,7 +9417,7 @@
       <c r="N392" s="1"/>
       <c r="O392" s="1"/>
       <c r="P392" s="1"/>
-      <c r="Q392" s="4"/>
+      <c r="Q392" s="6"/>
       <c r="R392" s="1"/>
     </row>
     <row r="393" ht="12.75">
@@ -9428,7 +9430,7 @@
       <c r="E393" s="1"/>
       <c r="F393" s="1"/>
       <c r="G393" s="1"/>
-      <c r="H393" s="3"/>
+      <c r="H393" s="5"/>
       <c r="I393" s="1"/>
       <c r="J393" s="1"/>
       <c r="K393" s="1"/>
@@ -9437,7 +9439,7 @@
       <c r="N393" s="1"/>
       <c r="O393" s="1"/>
       <c r="P393" s="1"/>
-      <c r="Q393" s="4"/>
+      <c r="Q393" s="6"/>
       <c r="R393" s="1"/>
     </row>
     <row r="394" ht="12.75">
@@ -9450,7 +9452,7 @@
       <c r="E394" s="1"/>
       <c r="F394" s="1"/>
       <c r="G394" s="1"/>
-      <c r="H394" s="3"/>
+      <c r="H394" s="5"/>
       <c r="I394" s="1"/>
       <c r="J394" s="1"/>
       <c r="K394" s="1"/>
@@ -9459,7 +9461,7 @@
       <c r="N394" s="1"/>
       <c r="O394" s="1"/>
       <c r="P394" s="1"/>
-      <c r="Q394" s="4"/>
+      <c r="Q394" s="6"/>
       <c r="R394" s="1"/>
     </row>
     <row r="395" ht="12.75">
@@ -9472,7 +9474,7 @@
       <c r="E395" s="1"/>
       <c r="F395" s="1"/>
       <c r="G395" s="1"/>
-      <c r="H395" s="3"/>
+      <c r="H395" s="5"/>
       <c r="I395" s="1"/>
       <c r="J395" s="1"/>
       <c r="K395" s="1"/>
@@ -9481,7 +9483,7 @@
       <c r="N395" s="1"/>
       <c r="O395" s="1"/>
       <c r="P395" s="1"/>
-      <c r="Q395" s="4"/>
+      <c r="Q395" s="6"/>
       <c r="R395" s="1"/>
     </row>
     <row r="396" ht="12.75">
@@ -9494,7 +9496,7 @@
       <c r="E396" s="1"/>
       <c r="F396" s="1"/>
       <c r="G396" s="1"/>
-      <c r="H396" s="3"/>
+      <c r="H396" s="5"/>
       <c r="I396" s="1"/>
       <c r="J396" s="1"/>
       <c r="K396" s="1"/>
@@ -9503,7 +9505,7 @@
       <c r="N396" s="1"/>
       <c r="O396" s="1"/>
       <c r="P396" s="1"/>
-      <c r="Q396" s="4"/>
+      <c r="Q396" s="6"/>
       <c r="R396" s="1"/>
     </row>
     <row r="397" ht="12.75">
@@ -9516,7 +9518,7 @@
       <c r="E397" s="1"/>
       <c r="F397" s="1"/>
       <c r="G397" s="1"/>
-      <c r="H397" s="3"/>
+      <c r="H397" s="5"/>
       <c r="I397" s="1"/>
       <c r="J397" s="1"/>
       <c r="K397" s="1"/>
@@ -9525,7 +9527,7 @@
       <c r="N397" s="1"/>
       <c r="O397" s="1"/>
       <c r="P397" s="1"/>
-      <c r="Q397" s="4"/>
+      <c r="Q397" s="6"/>
       <c r="R397" s="1"/>
     </row>
     <row r="398" ht="12.75">
@@ -9538,7 +9540,7 @@
       <c r="E398" s="1"/>
       <c r="F398" s="1"/>
       <c r="G398" s="1"/>
-      <c r="H398" s="3"/>
+      <c r="H398" s="5"/>
       <c r="I398" s="1"/>
       <c r="J398" s="1"/>
       <c r="K398" s="1"/>
@@ -9547,7 +9549,7 @@
       <c r="N398" s="1"/>
       <c r="O398" s="1"/>
       <c r="P398" s="1"/>
-      <c r="Q398" s="4"/>
+      <c r="Q398" s="6"/>
       <c r="R398" s="1"/>
     </row>
     <row r="399" ht="12.75">
@@ -9560,7 +9562,7 @@
       <c r="E399" s="1"/>
       <c r="F399" s="1"/>
       <c r="G399" s="1"/>
-      <c r="H399" s="3"/>
+      <c r="H399" s="5"/>
       <c r="I399" s="1"/>
       <c r="J399" s="1"/>
       <c r="K399" s="1"/>
@@ -9569,7 +9571,7 @@
       <c r="N399" s="1"/>
       <c r="O399" s="1"/>
       <c r="P399" s="1"/>
-      <c r="Q399" s="4"/>
+      <c r="Q399" s="6"/>
       <c r="R399" s="1"/>
     </row>
     <row r="400" ht="12.75">
@@ -9582,7 +9584,7 @@
       <c r="E400" s="1"/>
       <c r="F400" s="1"/>
       <c r="G400" s="1"/>
-      <c r="H400" s="3"/>
+      <c r="H400" s="5"/>
       <c r="I400" s="1"/>
       <c r="J400" s="1"/>
       <c r="K400" s="1"/>
@@ -9591,7 +9593,7 @@
       <c r="N400" s="1"/>
       <c r="O400" s="1"/>
       <c r="P400" s="1"/>
-      <c r="Q400" s="4"/>
+      <c r="Q400" s="6"/>
       <c r="R400" s="1"/>
     </row>
     <row r="401" ht="12.75">
@@ -9604,7 +9606,7 @@
       <c r="E401" s="1"/>
       <c r="F401" s="1"/>
       <c r="G401" s="1"/>
-      <c r="H401" s="3"/>
+      <c r="H401" s="5"/>
       <c r="I401" s="1"/>
       <c r="J401" s="1"/>
       <c r="K401" s="1"/>
@@ -9613,7 +9615,7 @@
       <c r="N401" s="1"/>
       <c r="O401" s="1"/>
       <c r="P401" s="1"/>
-      <c r="Q401" s="4"/>
+      <c r="Q401" s="6"/>
       <c r="R401" s="1"/>
     </row>
     <row r="402" ht="12.75">
@@ -9626,7 +9628,7 @@
       <c r="E402" s="1"/>
       <c r="F402" s="1"/>
       <c r="G402" s="1"/>
-      <c r="H402" s="3"/>
+      <c r="H402" s="5"/>
       <c r="I402" s="1"/>
       <c r="J402" s="1"/>
       <c r="K402" s="1"/>
@@ -9635,7 +9637,7 @@
       <c r="N402" s="1"/>
       <c r="O402" s="1"/>
       <c r="P402" s="1"/>
-      <c r="Q402" s="4"/>
+      <c r="Q402" s="6"/>
       <c r="R402" s="1"/>
     </row>
     <row r="403" ht="12.75">
@@ -9648,16 +9650,16 @@
       <c r="E403" s="1"/>
       <c r="F403" s="1"/>
       <c r="G403" s="1"/>
-      <c r="H403" s="3"/>
+      <c r="H403" s="5"/>
       <c r="I403" s="1"/>
       <c r="J403" s="1"/>
-      <c r="K403" s="5"/>
+      <c r="K403" s="7"/>
       <c r="L403" s="1"/>
       <c r="M403" s="1"/>
       <c r="N403" s="1"/>
       <c r="O403" s="1"/>
       <c r="P403" s="1"/>
-      <c r="Q403" s="4"/>
+      <c r="Q403" s="6"/>
       <c r="R403" s="1"/>
     </row>
     <row r="404" ht="12.75">
@@ -9670,7 +9672,7 @@
       <c r="E404" s="1"/>
       <c r="F404" s="1"/>
       <c r="G404" s="1"/>
-      <c r="H404" s="3"/>
+      <c r="H404" s="5"/>
       <c r="I404" s="1"/>
       <c r="J404" s="1"/>
       <c r="K404" s="1"/>
@@ -9679,7 +9681,7 @@
       <c r="N404" s="1"/>
       <c r="O404" s="1"/>
       <c r="P404" s="1"/>
-      <c r="Q404" s="4"/>
+      <c r="Q404" s="6"/>
       <c r="R404" s="1"/>
     </row>
     <row r="405" ht="12.75">
@@ -9692,16 +9694,16 @@
       <c r="E405" s="1"/>
       <c r="F405" s="1"/>
       <c r="G405" s="1"/>
-      <c r="H405" s="3"/>
+      <c r="H405" s="5"/>
       <c r="I405" s="1"/>
       <c r="J405" s="1"/>
       <c r="K405" s="1"/>
-      <c r="L405" s="5"/>
+      <c r="L405" s="7"/>
       <c r="M405" s="1"/>
       <c r="N405" s="1"/>
       <c r="O405" s="1"/>
       <c r="P405" s="1"/>
-      <c r="Q405" s="4"/>
+      <c r="Q405" s="6"/>
       <c r="R405" s="1"/>
     </row>
     <row r="406" ht="12.75">
@@ -9714,16 +9716,16 @@
       <c r="E406" s="1"/>
       <c r="F406" s="1"/>
       <c r="G406" s="1"/>
-      <c r="H406" s="3"/>
+      <c r="H406" s="5"/>
       <c r="I406" s="1"/>
       <c r="J406" s="1"/>
-      <c r="K406" s="5"/>
+      <c r="K406" s="7"/>
       <c r="L406" s="1"/>
       <c r="M406" s="1"/>
       <c r="N406" s="1"/>
       <c r="O406" s="1"/>
       <c r="P406" s="1"/>
-      <c r="Q406" s="4"/>
+      <c r="Q406" s="6"/>
       <c r="R406" s="1"/>
     </row>
     <row r="407" ht="12.75">
@@ -9736,16 +9738,16 @@
       <c r="E407" s="1"/>
       <c r="F407" s="1"/>
       <c r="G407" s="1"/>
-      <c r="H407" s="3"/>
+      <c r="H407" s="5"/>
       <c r="I407" s="1"/>
       <c r="J407" s="1"/>
-      <c r="K407" s="5"/>
+      <c r="K407" s="7"/>
       <c r="L407" s="1"/>
       <c r="M407" s="1"/>
       <c r="N407" s="1"/>
       <c r="O407" s="1"/>
       <c r="P407" s="1"/>
-      <c r="Q407" s="4"/>
+      <c r="Q407" s="6"/>
       <c r="R407" s="1"/>
     </row>
     <row r="408" ht="12.75">
@@ -9758,7 +9760,7 @@
       <c r="E408" s="1"/>
       <c r="F408" s="1"/>
       <c r="G408" s="1"/>
-      <c r="H408" s="3"/>
+      <c r="H408" s="5"/>
       <c r="I408" s="1"/>
       <c r="J408" s="1"/>
       <c r="K408" s="1"/>
@@ -9767,7 +9769,7 @@
       <c r="N408" s="1"/>
       <c r="O408" s="1"/>
       <c r="P408" s="1"/>
-      <c r="Q408" s="4"/>
+      <c r="Q408" s="6"/>
       <c r="R408" s="1"/>
     </row>
     <row r="409" ht="12.75">
@@ -9780,7 +9782,7 @@
       <c r="E409" s="1"/>
       <c r="F409" s="1"/>
       <c r="G409" s="1"/>
-      <c r="H409" s="3"/>
+      <c r="H409" s="5"/>
       <c r="I409" s="1"/>
       <c r="J409" s="1"/>
       <c r="K409" s="1"/>
@@ -9789,7 +9791,7 @@
       <c r="N409" s="1"/>
       <c r="O409" s="1"/>
       <c r="P409" s="1"/>
-      <c r="Q409" s="4"/>
+      <c r="Q409" s="6"/>
       <c r="R409" s="1"/>
     </row>
     <row r="410" ht="12.75">
@@ -9802,7 +9804,7 @@
       <c r="E410" s="1"/>
       <c r="F410" s="1"/>
       <c r="G410" s="1"/>
-      <c r="H410" s="3"/>
+      <c r="H410" s="5"/>
       <c r="I410" s="1"/>
       <c r="J410" s="1"/>
       <c r="K410" s="1"/>
@@ -9811,7 +9813,7 @@
       <c r="N410" s="1"/>
       <c r="O410" s="1"/>
       <c r="P410" s="1"/>
-      <c r="Q410" s="4"/>
+      <c r="Q410" s="6"/>
       <c r="R410" s="1"/>
     </row>
     <row r="411" ht="12.75">
@@ -9824,16 +9826,16 @@
       <c r="E411" s="1"/>
       <c r="F411" s="1"/>
       <c r="G411" s="1"/>
-      <c r="H411" s="3"/>
+      <c r="H411" s="5"/>
       <c r="I411" s="1"/>
       <c r="J411" s="1"/>
-      <c r="K411" s="5"/>
+      <c r="K411" s="7"/>
       <c r="L411" s="1"/>
       <c r="M411" s="1"/>
       <c r="N411" s="1"/>
       <c r="O411" s="1"/>
       <c r="P411" s="1"/>
-      <c r="Q411" s="4"/>
+      <c r="Q411" s="6"/>
       <c r="R411" s="1"/>
     </row>
     <row r="412" ht="12.75">
@@ -9846,7 +9848,7 @@
       <c r="E412" s="1"/>
       <c r="F412" s="1"/>
       <c r="G412" s="1"/>
-      <c r="H412" s="3"/>
+      <c r="H412" s="5"/>
       <c r="I412" s="1"/>
       <c r="J412" s="1"/>
       <c r="K412" s="1"/>
@@ -9855,7 +9857,7 @@
       <c r="N412" s="1"/>
       <c r="O412" s="1"/>
       <c r="P412" s="1"/>
-      <c r="Q412" s="4"/>
+      <c r="Q412" s="6"/>
       <c r="R412" s="1"/>
     </row>
     <row r="413" ht="12.75">
@@ -9868,7 +9870,7 @@
       <c r="E413" s="1"/>
       <c r="F413" s="1"/>
       <c r="G413" s="1"/>
-      <c r="H413" s="3"/>
+      <c r="H413" s="5"/>
       <c r="I413" s="1"/>
       <c r="J413" s="1"/>
       <c r="K413" s="1"/>
@@ -9877,7 +9879,7 @@
       <c r="N413" s="1"/>
       <c r="O413" s="1"/>
       <c r="P413" s="1"/>
-      <c r="Q413" s="4"/>
+      <c r="Q413" s="6"/>
       <c r="R413" s="1"/>
     </row>
     <row r="414" ht="12.75">
@@ -9890,7 +9892,7 @@
       <c r="E414" s="1"/>
       <c r="F414" s="1"/>
       <c r="G414" s="1"/>
-      <c r="H414" s="3"/>
+      <c r="H414" s="5"/>
       <c r="I414" s="1"/>
       <c r="J414" s="1"/>
       <c r="K414" s="1"/>
@@ -9899,7 +9901,7 @@
       <c r="N414" s="1"/>
       <c r="O414" s="1"/>
       <c r="P414" s="1"/>
-      <c r="Q414" s="4"/>
+      <c r="Q414" s="6"/>
       <c r="R414" s="1"/>
     </row>
     <row r="415" ht="12.75">
@@ -9912,16 +9914,16 @@
       <c r="E415" s="1"/>
       <c r="F415" s="1"/>
       <c r="G415" s="1"/>
-      <c r="H415" s="3"/>
+      <c r="H415" s="5"/>
       <c r="I415" s="1"/>
       <c r="J415" s="1"/>
-      <c r="K415" s="5"/>
+      <c r="K415" s="7"/>
       <c r="L415" s="1"/>
       <c r="M415" s="1"/>
       <c r="N415" s="1"/>
       <c r="O415" s="1"/>
       <c r="P415" s="1"/>
-      <c r="Q415" s="4"/>
+      <c r="Q415" s="6"/>
       <c r="R415" s="1"/>
     </row>
     <row r="416" ht="12.75">
@@ -9934,16 +9936,16 @@
       <c r="E416" s="1"/>
       <c r="F416" s="1"/>
       <c r="G416" s="1"/>
-      <c r="H416" s="3"/>
+      <c r="H416" s="5"/>
       <c r="I416" s="1"/>
       <c r="J416" s="1"/>
-      <c r="K416" s="5"/>
+      <c r="K416" s="7"/>
       <c r="L416" s="1"/>
       <c r="M416" s="1"/>
       <c r="N416" s="1"/>
       <c r="O416" s="1"/>
       <c r="P416" s="1"/>
-      <c r="Q416" s="4"/>
+      <c r="Q416" s="6"/>
       <c r="R416" s="1"/>
     </row>
     <row r="417" ht="12.75">
@@ -9956,7 +9958,7 @@
       <c r="E417" s="1"/>
       <c r="F417" s="1"/>
       <c r="G417" s="1"/>
-      <c r="H417" s="3"/>
+      <c r="H417" s="5"/>
       <c r="I417" s="1"/>
       <c r="J417" s="1"/>
       <c r="K417" s="1"/>
@@ -9965,7 +9967,7 @@
       <c r="N417" s="1"/>
       <c r="O417" s="1"/>
       <c r="P417" s="1"/>
-      <c r="Q417" s="4"/>
+      <c r="Q417" s="6"/>
       <c r="R417" s="1"/>
     </row>
     <row r="418" ht="12.75">
@@ -9978,7 +9980,7 @@
       <c r="E418" s="1"/>
       <c r="F418" s="1"/>
       <c r="G418" s="1"/>
-      <c r="H418" s="3"/>
+      <c r="H418" s="5"/>
       <c r="I418" s="1"/>
       <c r="J418" s="1"/>
       <c r="K418" s="1"/>
@@ -9987,7 +9989,7 @@
       <c r="N418" s="1"/>
       <c r="O418" s="1"/>
       <c r="P418" s="1"/>
-      <c r="Q418" s="4"/>
+      <c r="Q418" s="6"/>
       <c r="R418" s="1"/>
     </row>
     <row r="419" ht="12.75">
@@ -10000,7 +10002,7 @@
       <c r="E419" s="1"/>
       <c r="F419" s="1"/>
       <c r="G419" s="1"/>
-      <c r="H419" s="3"/>
+      <c r="H419" s="5"/>
       <c r="I419" s="1"/>
       <c r="J419" s="1"/>
       <c r="K419" s="1"/>
@@ -10009,7 +10011,7 @@
       <c r="N419" s="1"/>
       <c r="O419" s="1"/>
       <c r="P419" s="1"/>
-      <c r="Q419" s="4"/>
+      <c r="Q419" s="6"/>
       <c r="R419" s="1"/>
     </row>
     <row r="420" ht="12.75">
@@ -10022,7 +10024,7 @@
       <c r="E420" s="1"/>
       <c r="F420" s="1"/>
       <c r="G420" s="1"/>
-      <c r="H420" s="3"/>
+      <c r="H420" s="5"/>
       <c r="I420" s="1"/>
       <c r="J420" s="1"/>
       <c r="K420" s="1"/>
@@ -10031,7 +10033,7 @@
       <c r="N420" s="1"/>
       <c r="O420" s="1"/>
       <c r="P420" s="1"/>
-      <c r="Q420" s="4"/>
+      <c r="Q420" s="6"/>
       <c r="R420" s="1"/>
     </row>
     <row r="421" ht="12.75">
@@ -10044,16 +10046,16 @@
       <c r="E421" s="1"/>
       <c r="F421" s="1"/>
       <c r="G421" s="1"/>
-      <c r="H421" s="3"/>
+      <c r="H421" s="5"/>
       <c r="I421" s="1"/>
       <c r="J421" s="1"/>
-      <c r="K421" s="5"/>
+      <c r="K421" s="7"/>
       <c r="L421" s="1"/>
       <c r="M421" s="1"/>
       <c r="N421" s="1"/>
       <c r="O421" s="1"/>
       <c r="P421" s="1"/>
-      <c r="Q421" s="4"/>
+      <c r="Q421" s="6"/>
       <c r="R421" s="1"/>
     </row>
     <row r="422" ht="12.75">
@@ -10066,7 +10068,7 @@
       <c r="E422" s="1"/>
       <c r="F422" s="1"/>
       <c r="G422" s="1"/>
-      <c r="H422" s="3"/>
+      <c r="H422" s="5"/>
       <c r="I422" s="1"/>
       <c r="J422" s="1"/>
       <c r="K422" s="1"/>
@@ -10075,7 +10077,7 @@
       <c r="N422" s="1"/>
       <c r="O422" s="1"/>
       <c r="P422" s="1"/>
-      <c r="Q422" s="4"/>
+      <c r="Q422" s="6"/>
       <c r="R422" s="1"/>
     </row>
     <row r="423" ht="12.75">
@@ -10088,7 +10090,7 @@
       <c r="E423" s="1"/>
       <c r="F423" s="1"/>
       <c r="G423" s="1"/>
-      <c r="H423" s="3"/>
+      <c r="H423" s="5"/>
       <c r="I423" s="1"/>
       <c r="J423" s="1"/>
       <c r="K423" s="1"/>
@@ -10097,7 +10099,7 @@
       <c r="N423" s="1"/>
       <c r="O423" s="1"/>
       <c r="P423" s="1"/>
-      <c r="Q423" s="4"/>
+      <c r="Q423" s="6"/>
       <c r="R423" s="1"/>
     </row>
     <row r="424" ht="12.75">
@@ -10110,16 +10112,16 @@
       <c r="E424" s="1"/>
       <c r="F424" s="1"/>
       <c r="G424" s="1"/>
-      <c r="H424" s="3"/>
+      <c r="H424" s="5"/>
       <c r="I424" s="1"/>
       <c r="J424" s="1"/>
-      <c r="K424" s="5"/>
+      <c r="K424" s="7"/>
       <c r="L424" s="1"/>
       <c r="M424" s="1"/>
       <c r="N424" s="1"/>
       <c r="O424" s="1"/>
       <c r="P424" s="1"/>
-      <c r="Q424" s="4"/>
+      <c r="Q424" s="6"/>
       <c r="R424" s="1"/>
     </row>
     <row r="425" ht="12.75">
@@ -10132,7 +10134,7 @@
       <c r="E425" s="1"/>
       <c r="F425" s="1"/>
       <c r="G425" s="1"/>
-      <c r="H425" s="3"/>
+      <c r="H425" s="5"/>
       <c r="I425" s="1"/>
       <c r="J425" s="1"/>
       <c r="K425" s="1"/>
@@ -10141,7 +10143,7 @@
       <c r="N425" s="1"/>
       <c r="O425" s="1"/>
       <c r="P425" s="1"/>
-      <c r="Q425" s="4"/>
+      <c r="Q425" s="6"/>
       <c r="R425" s="1"/>
     </row>
     <row r="426" ht="12.75">
@@ -10154,16 +10156,16 @@
       <c r="E426" s="1"/>
       <c r="F426" s="1"/>
       <c r="G426" s="1"/>
-      <c r="H426" s="3"/>
+      <c r="H426" s="5"/>
       <c r="I426" s="1"/>
       <c r="J426" s="1"/>
-      <c r="K426" s="5"/>
+      <c r="K426" s="7"/>
       <c r="L426" s="1"/>
       <c r="M426" s="1"/>
       <c r="N426" s="1"/>
       <c r="O426" s="1"/>
       <c r="P426" s="1"/>
-      <c r="Q426" s="4"/>
+      <c r="Q426" s="6"/>
       <c r="R426" s="1"/>
     </row>
     <row r="427" ht="12.75">
@@ -10176,7 +10178,7 @@
       <c r="E427" s="1"/>
       <c r="F427" s="1"/>
       <c r="G427" s="1"/>
-      <c r="H427" s="3"/>
+      <c r="H427" s="5"/>
       <c r="I427" s="1"/>
       <c r="J427" s="1"/>
       <c r="K427" s="1"/>
@@ -10185,7 +10187,7 @@
       <c r="N427" s="1"/>
       <c r="O427" s="1"/>
       <c r="P427" s="1"/>
-      <c r="Q427" s="4"/>
+      <c r="Q427" s="6"/>
       <c r="R427" s="1"/>
     </row>
     <row r="428" ht="12.75">
@@ -10198,7 +10200,7 @@
       <c r="E428" s="1"/>
       <c r="F428" s="1"/>
       <c r="G428" s="1"/>
-      <c r="H428" s="3"/>
+      <c r="H428" s="5"/>
       <c r="I428" s="1"/>
       <c r="J428" s="1"/>
       <c r="K428" s="1"/>
@@ -10207,7 +10209,7 @@
       <c r="N428" s="1"/>
       <c r="O428" s="1"/>
       <c r="P428" s="1"/>
-      <c r="Q428" s="4"/>
+      <c r="Q428" s="6"/>
       <c r="R428" s="1"/>
     </row>
     <row r="429" ht="12.75">
@@ -10220,7 +10222,7 @@
       <c r="E429" s="1"/>
       <c r="F429" s="1"/>
       <c r="G429" s="1"/>
-      <c r="H429" s="3"/>
+      <c r="H429" s="5"/>
       <c r="I429" s="1"/>
       <c r="J429" s="1"/>
       <c r="K429" s="1"/>
@@ -10229,7 +10231,7 @@
       <c r="N429" s="1"/>
       <c r="O429" s="1"/>
       <c r="P429" s="1"/>
-      <c r="Q429" s="4"/>
+      <c r="Q429" s="6"/>
       <c r="R429" s="1"/>
     </row>
     <row r="430" ht="12.75">
@@ -10242,7 +10244,7 @@
       <c r="E430" s="1"/>
       <c r="F430" s="1"/>
       <c r="G430" s="1"/>
-      <c r="H430" s="3"/>
+      <c r="H430" s="5"/>
       <c r="I430" s="1"/>
       <c r="J430" s="1"/>
       <c r="K430" s="1"/>
@@ -10251,7 +10253,7 @@
       <c r="N430" s="1"/>
       <c r="O430" s="1"/>
       <c r="P430" s="1"/>
-      <c r="Q430" s="4"/>
+      <c r="Q430" s="6"/>
       <c r="R430" s="1"/>
     </row>
     <row r="431" ht="12.75">
@@ -10264,7 +10266,7 @@
       <c r="E431" s="1"/>
       <c r="F431" s="1"/>
       <c r="G431" s="1"/>
-      <c r="H431" s="3"/>
+      <c r="H431" s="5"/>
       <c r="I431" s="1"/>
       <c r="J431" s="1"/>
       <c r="K431" s="1"/>
@@ -10273,7 +10275,7 @@
       <c r="N431" s="1"/>
       <c r="O431" s="1"/>
       <c r="P431" s="1"/>
-      <c r="Q431" s="4"/>
+      <c r="Q431" s="6"/>
       <c r="R431" s="1"/>
     </row>
     <row r="432" ht="12.75">
@@ -10286,7 +10288,7 @@
       <c r="E432" s="1"/>
       <c r="F432" s="1"/>
       <c r="G432" s="1"/>
-      <c r="H432" s="3"/>
+      <c r="H432" s="5"/>
       <c r="I432" s="1"/>
       <c r="J432" s="1"/>
       <c r="K432" s="1"/>
@@ -10295,7 +10297,7 @@
       <c r="N432" s="1"/>
       <c r="O432" s="1"/>
       <c r="P432" s="1"/>
-      <c r="Q432" s="4"/>
+      <c r="Q432" s="6"/>
       <c r="R432" s="1"/>
     </row>
     <row r="433" ht="12.75">
@@ -10308,22 +10310,23 @@
       <c r="E433" s="1"/>
       <c r="F433" s="1"/>
       <c r="G433" s="1"/>
-      <c r="H433" s="3"/>
+      <c r="H433" s="5"/>
       <c r="I433" s="1"/>
       <c r="J433" s="1"/>
-      <c r="K433" s="5"/>
+      <c r="K433" s="7"/>
       <c r="L433" s="1"/>
       <c r="M433" s="1"/>
       <c r="N433" s="1"/>
       <c r="O433" s="1"/>
       <c r="P433" s="1"/>
-      <c r="Q433" s="4"/>
+      <c r="Q433" s="6"/>
       <c r="R433" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R433"/>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="Q2"/>
+    <hyperlink r:id="rId1" ref="B2"/>
+    <hyperlink r:id="rId2" ref="Q2"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
